--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pending" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -730,7 +730,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260700882</t>
+          <t>HASLS22260701906</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609171100</t>
+          <t>202609181000</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -756,27 +756,27 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -786,43 +786,45 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>CONSOLE</t>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-08-27, Return : 2026-08-28 CONSOLE</t>
+          <t xml:space="preserve">CY-RTN : 11-15/09/2026 (CONSOL) *1st cy dd.11/08/2026 (1x40'HQ)*
+CLS TIME 15/09/2026 @ 23.59
+</t>
         </is>
       </c>
       <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Y3" s="4" t="n">
         <v>0</v>
@@ -871,22 +873,22 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800724</t>
+          <t>HASLS22260800757</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609171100</t>
+          <t>202609200900</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -907,7 +909,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -932,7 +934,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-03, Return : 2026-09-04CONSOL</t>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
         </is>
       </c>
       <c r="O4" s="4" t="n">
@@ -1012,22 +1014,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801745</t>
+          <t>HASLS22260801228</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609171100</t>
+          <t>202609200900</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -1048,32 +1050,32 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>GERNARAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>CONSOL - REQUEST CLEAN AND GOOD CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-09 CONSOL </t>
+          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
@@ -1153,12 +1155,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801876</t>
+          <t>HASLS22260801441</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1168,7 +1170,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609171100</t>
+          <t>202609210600</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1179,32 +1181,32 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -1214,11 +1216,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-09 CONSOL</t>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
@@ -1294,7 +1296,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900181</t>
+          <t>HASLS22260801745</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1309,7 +1311,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609171100</t>
+          <t>202609181000</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1330,32 +1332,32 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL - REQUEST CLEAN AND GOOD CONTAINER</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-11 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-09 CONSOL </t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
@@ -1433,108 +1435,815 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801876</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-07, Return : 2026-09-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f>SUM(O8:W8)-X8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="4">
+        <f>MAX(0,O8-MAX(0,X8))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="4">
+        <f>MAX(0,P8-MAX(0,X8-SUM(O8:O8)))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="4">
+        <f>MAX(0,Q8-MAX(0,X8-SUM(O8:P8)))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="4">
+        <f>MAX(0,R8-MAX(0,X8-SUM(O8:Q8)))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="4">
+        <f>MAX(0,S8-MAX(0,X8-SUM(O8:R8)))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="4">
+        <f>MAX(0,T8-MAX(0,X8-SUM(O8:S8)))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="4">
+        <f>MAX(0,U8-MAX(0,X8-SUM(O8:T8)))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>MAX(0,V8-MAX(0,X8-SUM(O8:U8)))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="4">
+        <f>MAX(0,W8-MAX(0,X8-SUM(O8:V8)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801996</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
+[1ST CY DATE : 17/09/2026 W/O RENT]</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f>SUM(O9:W9)-X9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>MAX(0,O9-MAX(0,X9))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>MAX(0,P9-MAX(0,X9-SUM(O9:O9)))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="4">
+        <f>MAX(0,Q9-MAX(0,X9-SUM(O9:P9)))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="4">
+        <f>MAX(0,R9-MAX(0,X9-SUM(O9:Q9)))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>MAX(0,S9-MAX(0,X9-SUM(O9:R9)))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
+        <f>MAX(0,T9-MAX(0,X9-SUM(O9:S9)))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="4">
+        <f>MAX(0,U9-MAX(0,X9-SUM(O9:T9)))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>MAX(0,V9-MAX(0,X9-SUM(O9:U9)))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="4">
+        <f>MAX(0,W9-MAX(0,X9-SUM(O9:V9)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900181</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-07, Return : 2026-09-11 CONSOL</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f>SUM(O10:W10)-X10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="4">
+        <f>MAX(0,O10-MAX(0,X10))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="4">
+        <f>MAX(0,P10-MAX(0,X10-SUM(O10:O10)))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="4">
+        <f>MAX(0,Q10-MAX(0,X10-SUM(O10:P10)))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="4">
+        <f>MAX(0,R10-MAX(0,X10-SUM(O10:Q10)))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="4">
+        <f>MAX(0,S10-MAX(0,X10-SUM(O10:R10)))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="4">
+        <f>MAX(0,T10-MAX(0,X10-SUM(O10:S10)))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="4">
+        <f>MAX(0,U10-MAX(0,X10-SUM(O10:T10)))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>MAX(0,V10-MAX(0,X10-SUM(O10:U10)))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="4">
+        <f>MAX(0,W10-MAX(0,X10-SUM(O10:V10)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900184</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 10-11/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f>SUM(O11:W11)-X11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="4">
+        <f>MAX(0,O11-MAX(0,X11))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="4">
+        <f>MAX(0,P11-MAX(0,X11-SUM(O11:O11)))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="4">
+        <f>MAX(0,Q11-MAX(0,X11-SUM(O11:P11)))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="4">
+        <f>MAX(0,R11-MAX(0,X11-SUM(O11:Q11)))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="4">
+        <f>MAX(0,S11-MAX(0,X11-SUM(O11:R11)))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="4">
+        <f>MAX(0,T11-MAX(0,X11-SUM(O11:S11)))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="4">
+        <f>MAX(0,U11-MAX(0,X11-SUM(O11:T11)))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="4">
+        <f>MAX(0,V11-MAX(0,X11-SUM(O11:U11)))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="4">
+        <f>MAX(0,W11-MAX(0,X11-SUM(O11:V11)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900234</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-10, Return : 2026-09-11 CONSOL   
+[1ST CY DATE : 17/09/2026 WO RENT] </t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f>SUM(O12:W12)-X12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="4">
+        <f>MAX(0,O12-MAX(0,X12))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4">
+        <f>MAX(0,P12-MAX(0,X12-SUM(O12:O12)))</f>
+        <v/>
+      </c>
+      <c r="AC12" s="4">
+        <f>MAX(0,Q12-MAX(0,X12-SUM(O12:P12)))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="4">
+        <f>MAX(0,R12-MAX(0,X12-SUM(O12:Q12)))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="4">
+        <f>MAX(0,S12-MAX(0,X12-SUM(O12:R12)))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="4">
+        <f>MAX(0,T12-MAX(0,X12-SUM(O12:S12)))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="4">
+        <f>MAX(0,U12-MAX(0,X12-SUM(O12:T12)))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>MAX(0,V12-MAX(0,X12-SUM(O12:U12)))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="4">
+        <f>MAX(0,W12-MAX(0,X12-SUM(O12:V12)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5">
-        <f>SUM(O3:O7)</f>
-        <v/>
-      </c>
-      <c r="P8" s="5">
-        <f>SUM(P3:P7)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="5">
-        <f>SUM(Q3:Q7)</f>
-        <v/>
-      </c>
-      <c r="R8" s="5">
-        <f>SUM(R3:R7)</f>
-        <v/>
-      </c>
-      <c r="S8" s="5">
-        <f>SUM(S3:S7)</f>
-        <v/>
-      </c>
-      <c r="T8" s="5">
-        <f>SUM(T3:T7)</f>
-        <v/>
-      </c>
-      <c r="U8" s="5">
-        <f>SUM(U3:U7)</f>
-        <v/>
-      </c>
-      <c r="V8" s="5">
-        <f>SUM(V3:V7)</f>
-        <v/>
-      </c>
-      <c r="W8" s="5">
-        <f>SUM(W3:W7)</f>
-        <v/>
-      </c>
-      <c r="X8" s="5">
-        <f>SUM(X3:X7)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="5">
-        <f>SUM(Z3:Z7)</f>
-        <v/>
-      </c>
-      <c r="AA8" s="5">
-        <f>SUM(AA3:AA7)</f>
-        <v/>
-      </c>
-      <c r="AB8" s="5">
-        <f>SUM(AB3:AB7)</f>
-        <v/>
-      </c>
-      <c r="AC8" s="5">
-        <f>SUM(AC3:AC7)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="5">
-        <f>SUM(AD3:AD7)</f>
-        <v/>
-      </c>
-      <c r="AE8" s="5">
-        <f>SUM(AE3:AE7)</f>
-        <v/>
-      </c>
-      <c r="AF8" s="5">
-        <f>SUM(AF3:AF7)</f>
-        <v/>
-      </c>
-      <c r="AG8" s="5">
-        <f>SUM(AG3:AG7)</f>
-        <v/>
-      </c>
-      <c r="AH8" s="5">
-        <f>SUM(AH3:AH7)</f>
-        <v/>
-      </c>
-      <c r="AI8" s="5">
-        <f>SUM(AI3:AI7)</f>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5">
+        <f>SUM(O3:O12)</f>
+        <v/>
+      </c>
+      <c r="P13" s="5">
+        <f>SUM(P3:P12)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="5">
+        <f>SUM(Q3:Q12)</f>
+        <v/>
+      </c>
+      <c r="R13" s="5">
+        <f>SUM(R3:R12)</f>
+        <v/>
+      </c>
+      <c r="S13" s="5">
+        <f>SUM(S3:S12)</f>
+        <v/>
+      </c>
+      <c r="T13" s="5">
+        <f>SUM(T3:T12)</f>
+        <v/>
+      </c>
+      <c r="U13" s="5">
+        <f>SUM(U3:U12)</f>
+        <v/>
+      </c>
+      <c r="V13" s="5">
+        <f>SUM(V3:V12)</f>
+        <v/>
+      </c>
+      <c r="W13" s="5">
+        <f>SUM(W3:W12)</f>
+        <v/>
+      </c>
+      <c r="X13" s="5">
+        <f>SUM(X3:X12)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="5">
+        <f>SUM(Z3:Z12)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="5">
+        <f>SUM(AA3:AA12)</f>
+        <v/>
+      </c>
+      <c r="AB13" s="5">
+        <f>SUM(AB3:AB12)</f>
+        <v/>
+      </c>
+      <c r="AC13" s="5">
+        <f>SUM(AC3:AC12)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>SUM(AD3:AD12)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="5">
+        <f>SUM(AE3:AE12)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="5">
+        <f>SUM(AF3:AF12)</f>
+        <v/>
+      </c>
+      <c r="AG13" s="5">
+        <f>SUM(AG3:AG12)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="5">
+        <f>SUM(AH3:AH12)</f>
+        <v/>
+      </c>
+      <c r="AI13" s="5">
+        <f>SUM(AI3:AI12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI7"/>
+  <autoFilter ref="A2:AI12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AI1"/>
   </mergeCells>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -730,22 +730,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260701906</t>
+          <t>HASLS22260700891</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609181000</t>
+          <t>202609230700</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -756,360 +756,361 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.18/09/26 CLS TIME CFS DD.21/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>SUM(O3:W3)-X3</f>
+        <v/>
+      </c>
+      <c r="AA3" s="4">
+        <f>MAX(0,O3-MAX(0,X3))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="4">
+        <f>MAX(0,P3-MAX(0,X3-SUM(O3:O3)))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="4">
+        <f>MAX(0,Q3-MAX(0,X3-SUM(O3:P3)))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="4">
+        <f>MAX(0,R3-MAX(0,X3-SUM(O3:Q3)))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="4">
+        <f>MAX(0,S3-MAX(0,X3-SUM(O3:R3)))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="4">
+        <f>MAX(0,T3-MAX(0,X3-SUM(O3:S3)))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="4">
+        <f>MAX(0,U3-MAX(0,X3-SUM(O3:T3)))</f>
+        <v/>
+      </c>
+      <c r="AH3" s="4">
+        <f>MAX(0,V3-MAX(0,X3-SUM(O3:U3)))</f>
+        <v/>
+      </c>
+      <c r="AI3" s="4">
+        <f>MAX(0,W3-MAX(0,X3-SUM(O3:V3)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260700894</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.18/09/26 CLS TIME CFS DD.18/09/26 - 17:00HRS.</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f>SUM(O4:W4)-X4</f>
+        <v/>
+      </c>
+      <c r="AA4" s="4">
+        <f>MAX(0,O4-MAX(0,X4))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="4">
+        <f>MAX(0,P4-MAX(0,X4-SUM(O4:O4)))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="4">
+        <f>MAX(0,Q4-MAX(0,X4-SUM(O4:P4)))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="4">
+        <f>MAX(0,R4-MAX(0,X4-SUM(O4:Q4)))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="4">
+        <f>MAX(0,S4-MAX(0,X4-SUM(O4:R4)))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="4">
+        <f>MAX(0,T4-MAX(0,X4-SUM(O4:S4)))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="4">
+        <f>MAX(0,U4-MAX(0,X4-SUM(O4:T4)))</f>
+        <v/>
+      </c>
+      <c r="AH4" s="4">
+        <f>MAX(0,V4-MAX(0,X4-SUM(O4:U4)))</f>
+        <v/>
+      </c>
+      <c r="AI4" s="4">
+        <f>MAX(0,W4-MAX(0,X4-SUM(O4:V4)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260701906</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CY-RTN : 11-15/09/2026 (CONSOL) *1st cy dd.11/08/2026 (1x40'HQ)*
 CLS TIME 15/09/2026 @ 23.59
 </t>
         </is>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="4" t="n">
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4">
-        <f>SUM(O3:W3)-X3</f>
-        <v/>
-      </c>
-      <c r="AA3" s="4">
-        <f>MAX(0,O3-MAX(0,X3))</f>
-        <v/>
-      </c>
-      <c r="AB3" s="4">
-        <f>MAX(0,P3-MAX(0,X3-SUM(O3:O3)))</f>
-        <v/>
-      </c>
-      <c r="AC3" s="4">
-        <f>MAX(0,Q3-MAX(0,X3-SUM(O3:P3)))</f>
-        <v/>
-      </c>
-      <c r="AD3" s="4">
-        <f>MAX(0,R3-MAX(0,X3-SUM(O3:Q3)))</f>
-        <v/>
-      </c>
-      <c r="AE3" s="4">
-        <f>MAX(0,S3-MAX(0,X3-SUM(O3:R3)))</f>
-        <v/>
-      </c>
-      <c r="AF3" s="4">
-        <f>MAX(0,T3-MAX(0,X3-SUM(O3:S3)))</f>
-        <v/>
-      </c>
-      <c r="AG3" s="4">
-        <f>MAX(0,U3-MAX(0,X3-SUM(O3:T3)))</f>
-        <v/>
-      </c>
-      <c r="AH3" s="4">
-        <f>MAX(0,V3-MAX(0,X3-SUM(O3:U3)))</f>
-        <v/>
-      </c>
-      <c r="AI3" s="4">
-        <f>MAX(0,W3-MAX(0,X3-SUM(O3:V3)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260800757</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>20260910</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <f>SUM(O4:W4)-X4</f>
-        <v/>
-      </c>
-      <c r="AA4" s="4">
-        <f>MAX(0,O4-MAX(0,X4))</f>
-        <v/>
-      </c>
-      <c r="AB4" s="4">
-        <f>MAX(0,P4-MAX(0,X4-SUM(O4:O4)))</f>
-        <v/>
-      </c>
-      <c r="AC4" s="4">
-        <f>MAX(0,Q4-MAX(0,X4-SUM(O4:P4)))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="4">
-        <f>MAX(0,R4-MAX(0,X4-SUM(O4:Q4)))</f>
-        <v/>
-      </c>
-      <c r="AE4" s="4">
-        <f>MAX(0,S4-MAX(0,X4-SUM(O4:R4)))</f>
-        <v/>
-      </c>
-      <c r="AF4" s="4">
-        <f>MAX(0,T4-MAX(0,X4-SUM(O4:S4)))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="4">
-        <f>MAX(0,U4-MAX(0,X4-SUM(O4:T4)))</f>
-        <v/>
-      </c>
-      <c r="AH4" s="4">
-        <f>MAX(0,V4-MAX(0,X4-SUM(O4:U4)))</f>
-        <v/>
-      </c>
-      <c r="AI4" s="4">
-        <f>MAX(0,W4-MAX(0,X4-SUM(O4:V4)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260801228</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
+      <c r="Y5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Z5" s="4">
         <f>SUM(O5:W5)-X5</f>
@@ -1155,22 +1156,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801441</t>
+          <t>HASLS22260800693</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609210600</t>
+          <t>202609230700</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1181,27 +1182,27 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1211,22 +1212,22 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL - GOOD &amp; CLEAN CON</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-16, Return : 2026-09-17 CONSOL </t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>0</v>
@@ -1296,22 +1297,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801745</t>
+          <t>HASLS22260800757</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609181000</t>
+          <t>202609200900</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1322,27 +1323,27 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1352,12 +1353,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>CONSOL - REQUEST CLEAN AND GOOD CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-09 CONSOL </t>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
@@ -1367,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>0</v>
@@ -1391,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="4">
         <f>SUM(O7:W7)-X7</f>
@@ -1437,12 +1438,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801876</t>
+          <t>HASLS22260800761</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1452,7 +1453,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202609181000</t>
+          <t>202609261500</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1463,27 +1464,27 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1498,17 +1499,17 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-09 CONSOL</t>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL</t>
         </is>
       </c>
       <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>0</v>
@@ -1578,12 +1579,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801996</t>
+          <t>HASLS22260800977</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1593,7 +1594,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>202609261500</t>
+          <t>202609291200</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1604,7 +1605,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1614,17 +1615,17 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1639,8 +1640,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
-[1ST CY DATE : 17/09/2026 W/O RENT]</t>
+          <t xml:space="preserve">Pickup : 2026-09-24, Return : 2026-09-25 CONSOL </t>
         </is>
       </c>
       <c r="O9" s="4" t="n">
@@ -1720,7 +1720,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900181</t>
+          <t>HASLS22260801047</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1751,22 +1751,22 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-11 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-14, Return : 2026-09-14 CONSOL </t>
         </is>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>0</v>
@@ -1861,12 +1861,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900184</t>
+          <t>HASLS22260801208</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609181000</t>
+          <t>202609210600</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1892,22 +1892,22 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>CY-RTN : 10-11/09/2026 (CONSOL)</t>
+          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
         </is>
       </c>
       <c r="O11" s="4" t="n">
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>0</v>
@@ -2002,22 +2002,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900234</t>
+          <t>HASLS22260801209</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609261500</t>
+          <t>202609251900</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2033,217 +2033,7563 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f>SUM(O12:W12)-X12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="4">
+        <f>MAX(0,O12-MAX(0,X12))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4">
+        <f>MAX(0,P12-MAX(0,X12-SUM(O12:O12)))</f>
+        <v/>
+      </c>
+      <c r="AC12" s="4">
+        <f>MAX(0,Q12-MAX(0,X12-SUM(O12:P12)))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="4">
+        <f>MAX(0,R12-MAX(0,X12-SUM(O12:Q12)))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="4">
+        <f>MAX(0,S12-MAX(0,X12-SUM(O12:R12)))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="4">
+        <f>MAX(0,T12-MAX(0,X12-SUM(O12:S12)))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="4">
+        <f>MAX(0,U12-MAX(0,X12-SUM(O12:T12)))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>MAX(0,V12-MAX(0,X12-SUM(O12:U12)))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="4">
+        <f>MAX(0,W12-MAX(0,X12-SUM(O12:V12)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801210</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>202609291200</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f>SUM(O13:W13)-X13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="4">
+        <f>MAX(0,O13-MAX(0,X13))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4">
+        <f>MAX(0,P13-MAX(0,X13-SUM(O13:O13)))</f>
+        <v/>
+      </c>
+      <c r="AC13" s="4">
+        <f>MAX(0,Q13-MAX(0,X13-SUM(O13:P13)))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="4">
+        <f>MAX(0,R13-MAX(0,X13-SUM(O13:Q13)))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="4">
+        <f>MAX(0,S13-MAX(0,X13-SUM(O13:R13)))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="4">
+        <f>MAX(0,T13-MAX(0,X13-SUM(O13:S13)))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="4">
+        <f>MAX(0,U13-MAX(0,X13-SUM(O13:T13)))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="4">
+        <f>MAX(0,V13-MAX(0,X13-SUM(O13:U13)))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="4">
+        <f>MAX(0,W13-MAX(0,X13-SUM(O13:V13)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801228</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="4">
+        <f>SUM(O14:W14)-X14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="4">
+        <f>MAX(0,O14-MAX(0,X14))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4">
+        <f>MAX(0,P14-MAX(0,X14-SUM(O14:O14)))</f>
+        <v/>
+      </c>
+      <c r="AC14" s="4">
+        <f>MAX(0,Q14-MAX(0,X14-SUM(O14:P14)))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="4">
+        <f>MAX(0,R14-MAX(0,X14-SUM(O14:Q14)))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="4">
+        <f>MAX(0,S14-MAX(0,X14-SUM(O14:R14)))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="4">
+        <f>MAX(0,T14-MAX(0,X14-SUM(O14:S14)))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="4">
+        <f>MAX(0,U14-MAX(0,X14-SUM(O14:T14)))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="4">
+        <f>MAX(0,V14-MAX(0,X14-SUM(O14:U14)))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="4">
+        <f>MAX(0,W14-MAX(0,X14-SUM(O14:V14)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801229</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-18, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <f>SUM(O15:W15)-X15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="4">
+        <f>MAX(0,O15-MAX(0,X15))</f>
+        <v/>
+      </c>
+      <c r="AB15" s="4">
+        <f>MAX(0,P15-MAX(0,X15-SUM(O15:O15)))</f>
+        <v/>
+      </c>
+      <c r="AC15" s="4">
+        <f>MAX(0,Q15-MAX(0,X15-SUM(O15:P15)))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="4">
+        <f>MAX(0,R15-MAX(0,X15-SUM(O15:Q15)))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="4">
+        <f>MAX(0,S15-MAX(0,X15-SUM(O15:R15)))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="4">
+        <f>MAX(0,T15-MAX(0,X15-SUM(O15:S15)))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="4">
+        <f>MAX(0,U15-MAX(0,X15-SUM(O15:T15)))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="4">
+        <f>MAX(0,V15-MAX(0,X15-SUM(O15:U15)))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="4">
+        <f>MAX(0,W15-MAX(0,X15-SUM(O15:V15)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801230</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>202609301800</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <f>SUM(O16:W16)-X16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="4">
+        <f>MAX(0,O16-MAX(0,X16))</f>
+        <v/>
+      </c>
+      <c r="AB16" s="4">
+        <f>MAX(0,P16-MAX(0,X16-SUM(O16:O16)))</f>
+        <v/>
+      </c>
+      <c r="AC16" s="4">
+        <f>MAX(0,Q16-MAX(0,X16-SUM(O16:P16)))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="4">
+        <f>MAX(0,R16-MAX(0,X16-SUM(O16:Q16)))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="4">
+        <f>MAX(0,S16-MAX(0,X16-SUM(O16:R16)))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="4">
+        <f>MAX(0,T16-MAX(0,X16-SUM(O16:S16)))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="4">
+        <f>MAX(0,U16-MAX(0,X16-SUM(O16:T16)))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="4">
+        <f>MAX(0,V16-MAX(0,X16-SUM(O16:U16)))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="4">
+        <f>MAX(0,W16-MAX(0,X16-SUM(O16:V16)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801289</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="4">
+        <f>SUM(O17:W17)-X17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="4">
+        <f>MAX(0,O17-MAX(0,X17))</f>
+        <v/>
+      </c>
+      <c r="AB17" s="4">
+        <f>MAX(0,P17-MAX(0,X17-SUM(O17:O17)))</f>
+        <v/>
+      </c>
+      <c r="AC17" s="4">
+        <f>MAX(0,Q17-MAX(0,X17-SUM(O17:P17)))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="4">
+        <f>MAX(0,R17-MAX(0,X17-SUM(O17:Q17)))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="4">
+        <f>MAX(0,S17-MAX(0,X17-SUM(O17:R17)))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="4">
+        <f>MAX(0,T17-MAX(0,X17-SUM(O17:S17)))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="4">
+        <f>MAX(0,U17-MAX(0,X17-SUM(O17:T17)))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="4">
+        <f>MAX(0,V17-MAX(0,X17-SUM(O17:U17)))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="4">
+        <f>MAX(0,W17-MAX(0,X17-SUM(O17:V17)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801441</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>202609210600</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="4">
+        <f>SUM(O18:W18)-X18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="4">
+        <f>MAX(0,O18-MAX(0,X18))</f>
+        <v/>
+      </c>
+      <c r="AB18" s="4">
+        <f>MAX(0,P18-MAX(0,X18-SUM(O18:O18)))</f>
+        <v/>
+      </c>
+      <c r="AC18" s="4">
+        <f>MAX(0,Q18-MAX(0,X18-SUM(O18:P18)))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="4">
+        <f>MAX(0,R18-MAX(0,X18-SUM(O18:Q18)))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="4">
+        <f>MAX(0,S18-MAX(0,X18-SUM(O18:R18)))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="4">
+        <f>MAX(0,T18-MAX(0,X18-SUM(O18:S18)))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="4">
+        <f>MAX(0,U18-MAX(0,X18-SUM(O18:T18)))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="4">
+        <f>MAX(0,V18-MAX(0,X18-SUM(O18:U18)))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="4">
+        <f>MAX(0,W18-MAX(0,X18-SUM(O18:V18)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801442</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>202609230700</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL *EXTEND CLS TIME : 18/09/2026 @20.00*</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="4">
+        <f>SUM(O19:W19)-X19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="4">
+        <f>MAX(0,O19-MAX(0,X19))</f>
+        <v/>
+      </c>
+      <c r="AB19" s="4">
+        <f>MAX(0,P19-MAX(0,X19-SUM(O19:O19)))</f>
+        <v/>
+      </c>
+      <c r="AC19" s="4">
+        <f>MAX(0,Q19-MAX(0,X19-SUM(O19:P19)))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="4">
+        <f>MAX(0,R19-MAX(0,X19-SUM(O19:Q19)))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="4">
+        <f>MAX(0,S19-MAX(0,X19-SUM(O19:R19)))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="4">
+        <f>MAX(0,T19-MAX(0,X19-SUM(O19:S19)))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="4">
+        <f>MAX(0,U19-MAX(0,X19-SUM(O19:T19)))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="4">
+        <f>MAX(0,V19-MAX(0,X19-SUM(O19:U19)))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="4">
+        <f>MAX(0,W19-MAX(0,X19-SUM(O19:V19)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801443</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>202610020800</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="4">
+        <f>SUM(O20:W20)-X20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="4">
+        <f>MAX(0,O20-MAX(0,X20))</f>
+        <v/>
+      </c>
+      <c r="AB20" s="4">
+        <f>MAX(0,P20-MAX(0,X20-SUM(O20:O20)))</f>
+        <v/>
+      </c>
+      <c r="AC20" s="4">
+        <f>MAX(0,Q20-MAX(0,X20-SUM(O20:P20)))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="4">
+        <f>MAX(0,R20-MAX(0,X20-SUM(O20:Q20)))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="4">
+        <f>MAX(0,S20-MAX(0,X20-SUM(O20:R20)))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="4">
+        <f>MAX(0,T20-MAX(0,X20-SUM(O20:S20)))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="4">
+        <f>MAX(0,U20-MAX(0,X20-SUM(O20:T20)))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>MAX(0,V20-MAX(0,X20-SUM(O20:U20)))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="4">
+        <f>MAX(0,W20-MAX(0,X20-SUM(O20:V20)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801462</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-21, Return : 2026-09-21 CONSOL</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="4">
+        <f>SUM(O21:W21)-X21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="4">
+        <f>MAX(0,O21-MAX(0,X21))</f>
+        <v/>
+      </c>
+      <c r="AB21" s="4">
+        <f>MAX(0,P21-MAX(0,X21-SUM(O21:O21)))</f>
+        <v/>
+      </c>
+      <c r="AC21" s="4">
+        <f>MAX(0,Q21-MAX(0,X21-SUM(O21:P21)))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="4">
+        <f>MAX(0,R21-MAX(0,X21-SUM(O21:Q21)))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="4">
+        <f>MAX(0,S21-MAX(0,X21-SUM(O21:R21)))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="4">
+        <f>MAX(0,T21-MAX(0,X21-SUM(O21:S21)))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="4">
+        <f>MAX(0,U21-MAX(0,X21-SUM(O21:T21)))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>MAX(0,V21-MAX(0,X21-SUM(O21:U21)))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="4">
+        <f>MAX(0,W21-MAX(0,X21-SUM(O21:V21)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801482</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>OASIS LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>KAEN CHAROEN CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAPIOCA STARCH </t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/09/26 CLS TIME CFS DD.15/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="4">
+        <f>SUM(O22:W22)-X22</f>
+        <v/>
+      </c>
+      <c r="AA22" s="4">
+        <f>MAX(0,O22-MAX(0,X22))</f>
+        <v/>
+      </c>
+      <c r="AB22" s="4">
+        <f>MAX(0,P22-MAX(0,X22-SUM(O22:O22)))</f>
+        <v/>
+      </c>
+      <c r="AC22" s="4">
+        <f>MAX(0,Q22-MAX(0,X22-SUM(O22:P22)))</f>
+        <v/>
+      </c>
+      <c r="AD22" s="4">
+        <f>MAX(0,R22-MAX(0,X22-SUM(O22:Q22)))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="4">
+        <f>MAX(0,S22-MAX(0,X22-SUM(O22:R22)))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="4">
+        <f>MAX(0,T22-MAX(0,X22-SUM(O22:S22)))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="4">
+        <f>MAX(0,U22-MAX(0,X22-SUM(O22:T22)))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="4">
+        <f>MAX(0,V22-MAX(0,X22-SUM(O22:U22)))</f>
+        <v/>
+      </c>
+      <c r="AI22" s="4">
+        <f>MAX(0,W22-MAX(0,X22-SUM(O22:V22)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801745</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL - REQUEST CLEAN AND GOOD CONTAINER</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-09 CONSOL </t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="4">
+        <f>SUM(O23:W23)-X23</f>
+        <v/>
+      </c>
+      <c r="AA23" s="4">
+        <f>MAX(0,O23-MAX(0,X23))</f>
+        <v/>
+      </c>
+      <c r="AB23" s="4">
+        <f>MAX(0,P23-MAX(0,X23-SUM(O23:O23)))</f>
+        <v/>
+      </c>
+      <c r="AC23" s="4">
+        <f>MAX(0,Q23-MAX(0,X23-SUM(O23:P23)))</f>
+        <v/>
+      </c>
+      <c r="AD23" s="4">
+        <f>MAX(0,R23-MAX(0,X23-SUM(O23:Q23)))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="4">
+        <f>MAX(0,S23-MAX(0,X23-SUM(O23:R23)))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="4">
+        <f>MAX(0,T23-MAX(0,X23-SUM(O23:S23)))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="4">
+        <f>MAX(0,U23-MAX(0,X23-SUM(O23:T23)))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="4">
+        <f>MAX(0,V23-MAX(0,X23-SUM(O23:U23)))</f>
+        <v/>
+      </c>
+      <c r="AI23" s="4">
+        <f>MAX(0,W23-MAX(0,X23-SUM(O23:V23)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801789</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>202610011030</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.22/09/26 *CLS TIME CFS DD.23/09/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="4">
+        <f>SUM(O24:W24)-X24</f>
+        <v/>
+      </c>
+      <c r="AA24" s="4">
+        <f>MAX(0,O24-MAX(0,X24))</f>
+        <v/>
+      </c>
+      <c r="AB24" s="4">
+        <f>MAX(0,P24-MAX(0,X24-SUM(O24:O24)))</f>
+        <v/>
+      </c>
+      <c r="AC24" s="4">
+        <f>MAX(0,Q24-MAX(0,X24-SUM(O24:P24)))</f>
+        <v/>
+      </c>
+      <c r="AD24" s="4">
+        <f>MAX(0,R24-MAX(0,X24-SUM(O24:Q24)))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="4">
+        <f>MAX(0,S24-MAX(0,X24-SUM(O24:R24)))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="4">
+        <f>MAX(0,T24-MAX(0,X24-SUM(O24:S24)))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="4">
+        <f>MAX(0,U24-MAX(0,X24-SUM(O24:T24)))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="4">
+        <f>MAX(0,V24-MAX(0,X24-SUM(O24:U24)))</f>
+        <v/>
+      </c>
+      <c r="AI24" s="4">
+        <f>MAX(0,W24-MAX(0,X24-SUM(O24:V24)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801791</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>202610020800</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.24/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="4">
+        <f>SUM(O25:W25)-X25</f>
+        <v/>
+      </c>
+      <c r="AA25" s="4">
+        <f>MAX(0,O25-MAX(0,X25))</f>
+        <v/>
+      </c>
+      <c r="AB25" s="4">
+        <f>MAX(0,P25-MAX(0,X25-SUM(O25:O25)))</f>
+        <v/>
+      </c>
+      <c r="AC25" s="4">
+        <f>MAX(0,Q25-MAX(0,X25-SUM(O25:P25)))</f>
+        <v/>
+      </c>
+      <c r="AD25" s="4">
+        <f>MAX(0,R25-MAX(0,X25-SUM(O25:Q25)))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="4">
+        <f>MAX(0,S25-MAX(0,X25-SUM(O25:R25)))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="4">
+        <f>MAX(0,T25-MAX(0,X25-SUM(O25:S25)))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="4">
+        <f>MAX(0,U25-MAX(0,X25-SUM(O25:T25)))</f>
+        <v/>
+      </c>
+      <c r="AH25" s="4">
+        <f>MAX(0,V25-MAX(0,X25-SUM(O25:U25)))</f>
+        <v/>
+      </c>
+      <c r="AI25" s="4">
+        <f>MAX(0,W25-MAX(0,X25-SUM(O25:V25)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801876</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-07, Return : 2026-09-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="4">
+        <f>SUM(O26:W26)-X26</f>
+        <v/>
+      </c>
+      <c r="AA26" s="4">
+        <f>MAX(0,O26-MAX(0,X26))</f>
+        <v/>
+      </c>
+      <c r="AB26" s="4">
+        <f>MAX(0,P26-MAX(0,X26-SUM(O26:O26)))</f>
+        <v/>
+      </c>
+      <c r="AC26" s="4">
+        <f>MAX(0,Q26-MAX(0,X26-SUM(O26:P26)))</f>
+        <v/>
+      </c>
+      <c r="AD26" s="4">
+        <f>MAX(0,R26-MAX(0,X26-SUM(O26:Q26)))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="4">
+        <f>MAX(0,S26-MAX(0,X26-SUM(O26:R26)))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="4">
+        <f>MAX(0,T26-MAX(0,X26-SUM(O26:S26)))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="4">
+        <f>MAX(0,U26-MAX(0,X26-SUM(O26:T26)))</f>
+        <v/>
+      </c>
+      <c r="AH26" s="4">
+        <f>MAX(0,V26-MAX(0,X26-SUM(O26:U26)))</f>
+        <v/>
+      </c>
+      <c r="AI26" s="4">
+        <f>MAX(0,W26-MAX(0,X26-SUM(O26:V26)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801991</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>202609291200</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-25, Return : 2026-09-25  CONSOL  </t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="4">
+        <f>SUM(O27:W27)-X27</f>
+        <v/>
+      </c>
+      <c r="AA27" s="4">
+        <f>MAX(0,O27-MAX(0,X27))</f>
+        <v/>
+      </c>
+      <c r="AB27" s="4">
+        <f>MAX(0,P27-MAX(0,X27-SUM(O27:O27)))</f>
+        <v/>
+      </c>
+      <c r="AC27" s="4">
+        <f>MAX(0,Q27-MAX(0,X27-SUM(O27:P27)))</f>
+        <v/>
+      </c>
+      <c r="AD27" s="4">
+        <f>MAX(0,R27-MAX(0,X27-SUM(O27:Q27)))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="4">
+        <f>MAX(0,S27-MAX(0,X27-SUM(O27:R27)))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="4">
+        <f>MAX(0,T27-MAX(0,X27-SUM(O27:S27)))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="4">
+        <f>MAX(0,U27-MAX(0,X27-SUM(O27:T27)))</f>
+        <v/>
+      </c>
+      <c r="AH27" s="4">
+        <f>MAX(0,V27-MAX(0,X27-SUM(O27:U27)))</f>
+        <v/>
+      </c>
+      <c r="AI27" s="4">
+        <f>MAX(0,W27-MAX(0,X27-SUM(O27:V27)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801996</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
+[1ST CY DATE : 17/09/2026 W/O RENT]</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="4">
+        <f>SUM(O28:W28)-X28</f>
+        <v/>
+      </c>
+      <c r="AA28" s="4">
+        <f>MAX(0,O28-MAX(0,X28))</f>
+        <v/>
+      </c>
+      <c r="AB28" s="4">
+        <f>MAX(0,P28-MAX(0,X28-SUM(O28:O28)))</f>
+        <v/>
+      </c>
+      <c r="AC28" s="4">
+        <f>MAX(0,Q28-MAX(0,X28-SUM(O28:P28)))</f>
+        <v/>
+      </c>
+      <c r="AD28" s="4">
+        <f>MAX(0,R28-MAX(0,X28-SUM(O28:Q28)))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="4">
+        <f>MAX(0,S28-MAX(0,X28-SUM(O28:R28)))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="4">
+        <f>MAX(0,T28-MAX(0,X28-SUM(O28:S28)))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="4">
+        <f>MAX(0,U28-MAX(0,X28-SUM(O28:T28)))</f>
+        <v/>
+      </c>
+      <c r="AH28" s="4">
+        <f>MAX(0,V28-MAX(0,X28-SUM(O28:U28)))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="4">
+        <f>MAX(0,W28-MAX(0,X28-SUM(O28:V28)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802037</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>202610072300</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>ADL ASIA LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>FIVE PAGODAS PHARMACY CO.,LTD</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>YA HOM FIVE PAGODAS BRAND (MEDICINE)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="4">
+        <f>SUM(O29:W29)-X29</f>
+        <v/>
+      </c>
+      <c r="AA29" s="4">
+        <f>MAX(0,O29-MAX(0,X29))</f>
+        <v/>
+      </c>
+      <c r="AB29" s="4">
+        <f>MAX(0,P29-MAX(0,X29-SUM(O29:O29)))</f>
+        <v/>
+      </c>
+      <c r="AC29" s="4">
+        <f>MAX(0,Q29-MAX(0,X29-SUM(O29:P29)))</f>
+        <v/>
+      </c>
+      <c r="AD29" s="4">
+        <f>MAX(0,R29-MAX(0,X29-SUM(O29:Q29)))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="4">
+        <f>MAX(0,S29-MAX(0,X29-SUM(O29:R29)))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="4">
+        <f>MAX(0,T29-MAX(0,X29-SUM(O29:S29)))</f>
+        <v/>
+      </c>
+      <c r="AG29" s="4">
+        <f>MAX(0,U29-MAX(0,X29-SUM(O29:T29)))</f>
+        <v/>
+      </c>
+      <c r="AH29" s="4">
+        <f>MAX(0,V29-MAX(0,X29-SUM(O29:U29)))</f>
+        <v/>
+      </c>
+      <c r="AI29" s="4">
+        <f>MAX(0,W29-MAX(0,X29-SUM(O29:V29)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802179</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>202609241500</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="4">
+        <f>SUM(O30:W30)-X30</f>
+        <v/>
+      </c>
+      <c r="AA30" s="4">
+        <f>MAX(0,O30-MAX(0,X30))</f>
+        <v/>
+      </c>
+      <c r="AB30" s="4">
+        <f>MAX(0,P30-MAX(0,X30-SUM(O30:O30)))</f>
+        <v/>
+      </c>
+      <c r="AC30" s="4">
+        <f>MAX(0,Q30-MAX(0,X30-SUM(O30:P30)))</f>
+        <v/>
+      </c>
+      <c r="AD30" s="4">
+        <f>MAX(0,R30-MAX(0,X30-SUM(O30:Q30)))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="4">
+        <f>MAX(0,S30-MAX(0,X30-SUM(O30:R30)))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="4">
+        <f>MAX(0,T30-MAX(0,X30-SUM(O30:S30)))</f>
+        <v/>
+      </c>
+      <c r="AG30" s="4">
+        <f>MAX(0,U30-MAX(0,X30-SUM(O30:T30)))</f>
+        <v/>
+      </c>
+      <c r="AH30" s="4">
+        <f>MAX(0,V30-MAX(0,X30-SUM(O30:U30)))</f>
+        <v/>
+      </c>
+      <c r="AI30" s="4">
+        <f>MAX(0,W30-MAX(0,X30-SUM(O30:V30)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802180</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>202610072300</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="4">
+        <f>SUM(O31:W31)-X31</f>
+        <v/>
+      </c>
+      <c r="AA31" s="4">
+        <f>MAX(0,O31-MAX(0,X31))</f>
+        <v/>
+      </c>
+      <c r="AB31" s="4">
+        <f>MAX(0,P31-MAX(0,X31-SUM(O31:O31)))</f>
+        <v/>
+      </c>
+      <c r="AC31" s="4">
+        <f>MAX(0,Q31-MAX(0,X31-SUM(O31:P31)))</f>
+        <v/>
+      </c>
+      <c r="AD31" s="4">
+        <f>MAX(0,R31-MAX(0,X31-SUM(O31:Q31)))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="4">
+        <f>MAX(0,S31-MAX(0,X31-SUM(O31:R31)))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="4">
+        <f>MAX(0,T31-MAX(0,X31-SUM(O31:S31)))</f>
+        <v/>
+      </c>
+      <c r="AG31" s="4">
+        <f>MAX(0,U31-MAX(0,X31-SUM(O31:T31)))</f>
+        <v/>
+      </c>
+      <c r="AH31" s="4">
+        <f>MAX(0,V31-MAX(0,X31-SUM(O31:U31)))</f>
+        <v/>
+      </c>
+      <c r="AI31" s="4">
+        <f>MAX(0,W31-MAX(0,X31-SUM(O31:V31)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802238</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>202609251900</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>HAST LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>COTTON BALLS</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>GOOD &amp; CLEAN CNTR</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.23/09/26 *CLS TIME CFS DD.23/09/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="4">
+        <f>SUM(O32:W32)-X32</f>
+        <v/>
+      </c>
+      <c r="AA32" s="4">
+        <f>MAX(0,O32-MAX(0,X32))</f>
+        <v/>
+      </c>
+      <c r="AB32" s="4">
+        <f>MAX(0,P32-MAX(0,X32-SUM(O32:O32)))</f>
+        <v/>
+      </c>
+      <c r="AC32" s="4">
+        <f>MAX(0,Q32-MAX(0,X32-SUM(O32:P32)))</f>
+        <v/>
+      </c>
+      <c r="AD32" s="4">
+        <f>MAX(0,R32-MAX(0,X32-SUM(O32:Q32)))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="4">
+        <f>MAX(0,S32-MAX(0,X32-SUM(O32:R32)))</f>
+        <v/>
+      </c>
+      <c r="AF32" s="4">
+        <f>MAX(0,T32-MAX(0,X32-SUM(O32:S32)))</f>
+        <v/>
+      </c>
+      <c r="AG32" s="4">
+        <f>MAX(0,U32-MAX(0,X32-SUM(O32:T32)))</f>
+        <v/>
+      </c>
+      <c r="AH32" s="4">
+        <f>MAX(0,V32-MAX(0,X32-SUM(O32:U32)))</f>
+        <v/>
+      </c>
+      <c r="AI32" s="4">
+        <f>MAX(0,W32-MAX(0,X32-SUM(O32:V32)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802251</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>V.C.E. COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>TAPIOCA FLOUR</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.15/09/26 *CLS TIME CFS DD.15/09/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="4">
+        <f>SUM(O33:W33)-X33</f>
+        <v/>
+      </c>
+      <c r="AA33" s="4">
+        <f>MAX(0,O33-MAX(0,X33))</f>
+        <v/>
+      </c>
+      <c r="AB33" s="4">
+        <f>MAX(0,P33-MAX(0,X33-SUM(O33:O33)))</f>
+        <v/>
+      </c>
+      <c r="AC33" s="4">
+        <f>MAX(0,Q33-MAX(0,X33-SUM(O33:P33)))</f>
+        <v/>
+      </c>
+      <c r="AD33" s="4">
+        <f>MAX(0,R33-MAX(0,X33-SUM(O33:Q33)))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="4">
+        <f>MAX(0,S33-MAX(0,X33-SUM(O33:R33)))</f>
+        <v/>
+      </c>
+      <c r="AF33" s="4">
+        <f>MAX(0,T33-MAX(0,X33-SUM(O33:S33)))</f>
+        <v/>
+      </c>
+      <c r="AG33" s="4">
+        <f>MAX(0,U33-MAX(0,X33-SUM(O33:T33)))</f>
+        <v/>
+      </c>
+      <c r="AH33" s="4">
+        <f>MAX(0,V33-MAX(0,X33-SUM(O33:U33)))</f>
+        <v/>
+      </c>
+      <c r="AI33" s="4">
+        <f>MAX(0,W33-MAX(0,X33-SUM(O33:V33)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802382</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="4">
+        <f>SUM(O34:W34)-X34</f>
+        <v/>
+      </c>
+      <c r="AA34" s="4">
+        <f>MAX(0,O34-MAX(0,X34))</f>
+        <v/>
+      </c>
+      <c r="AB34" s="4">
+        <f>MAX(0,P34-MAX(0,X34-SUM(O34:O34)))</f>
+        <v/>
+      </c>
+      <c r="AC34" s="4">
+        <f>MAX(0,Q34-MAX(0,X34-SUM(O34:P34)))</f>
+        <v/>
+      </c>
+      <c r="AD34" s="4">
+        <f>MAX(0,R34-MAX(0,X34-SUM(O34:Q34)))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="4">
+        <f>MAX(0,S34-MAX(0,X34-SUM(O34:R34)))</f>
+        <v/>
+      </c>
+      <c r="AF34" s="4">
+        <f>MAX(0,T34-MAX(0,X34-SUM(O34:S34)))</f>
+        <v/>
+      </c>
+      <c r="AG34" s="4">
+        <f>MAX(0,U34-MAX(0,X34-SUM(O34:T34)))</f>
+        <v/>
+      </c>
+      <c r="AH34" s="4">
+        <f>MAX(0,V34-MAX(0,X34-SUM(O34:U34)))</f>
+        <v/>
+      </c>
+      <c r="AI34" s="4">
+        <f>MAX(0,W34-MAX(0,X34-SUM(O34:V34)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802450</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>202609301800</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="4">
+        <f>SUM(O35:W35)-X35</f>
+        <v/>
+      </c>
+      <c r="AA35" s="4">
+        <f>MAX(0,O35-MAX(0,X35))</f>
+        <v/>
+      </c>
+      <c r="AB35" s="4">
+        <f>MAX(0,P35-MAX(0,X35-SUM(O35:O35)))</f>
+        <v/>
+      </c>
+      <c r="AC35" s="4">
+        <f>MAX(0,Q35-MAX(0,X35-SUM(O35:P35)))</f>
+        <v/>
+      </c>
+      <c r="AD35" s="4">
+        <f>MAX(0,R35-MAX(0,X35-SUM(O35:Q35)))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="4">
+        <f>MAX(0,S35-MAX(0,X35-SUM(O35:R35)))</f>
+        <v/>
+      </c>
+      <c r="AF35" s="4">
+        <f>MAX(0,T35-MAX(0,X35-SUM(O35:S35)))</f>
+        <v/>
+      </c>
+      <c r="AG35" s="4">
+        <f>MAX(0,U35-MAX(0,X35-SUM(O35:T35)))</f>
+        <v/>
+      </c>
+      <c r="AH35" s="4">
+        <f>MAX(0,V35-MAX(0,X35-SUM(O35:U35)))</f>
+        <v/>
+      </c>
+      <c r="AI35" s="4">
+        <f>MAX(0,W35-MAX(0,X35-SUM(O35:V35)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802476</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>202609230700</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x12 </t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>CAPRICORN LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>REQUEST CONTAINER GOOD GRADE
+REQUEST CONTAINER UPGRADE 32.5 TONS</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.18/09/26 CLS TIME CFS DD.21/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="4">
+        <f>SUM(O36:W36)-X36</f>
+        <v/>
+      </c>
+      <c r="AA36" s="4">
+        <f>MAX(0,O36-MAX(0,X36))</f>
+        <v/>
+      </c>
+      <c r="AB36" s="4">
+        <f>MAX(0,P36-MAX(0,X36-SUM(O36:O36)))</f>
+        <v/>
+      </c>
+      <c r="AC36" s="4">
+        <f>MAX(0,Q36-MAX(0,X36-SUM(O36:P36)))</f>
+        <v/>
+      </c>
+      <c r="AD36" s="4">
+        <f>MAX(0,R36-MAX(0,X36-SUM(O36:Q36)))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="4">
+        <f>MAX(0,S36-MAX(0,X36-SUM(O36:R36)))</f>
+        <v/>
+      </c>
+      <c r="AF36" s="4">
+        <f>MAX(0,T36-MAX(0,X36-SUM(O36:S36)))</f>
+        <v/>
+      </c>
+      <c r="AG36" s="4">
+        <f>MAX(0,U36-MAX(0,X36-SUM(O36:T36)))</f>
+        <v/>
+      </c>
+      <c r="AH36" s="4">
+        <f>MAX(0,V36-MAX(0,X36-SUM(O36:U36)))</f>
+        <v/>
+      </c>
+      <c r="AI36" s="4">
+        <f>MAX(0,W36-MAX(0,X36-SUM(O36:V36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802541</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="4">
+        <f>SUM(O37:W37)-X37</f>
+        <v/>
+      </c>
+      <c r="AA37" s="4">
+        <f>MAX(0,O37-MAX(0,X37))</f>
+        <v/>
+      </c>
+      <c r="AB37" s="4">
+        <f>MAX(0,P37-MAX(0,X37-SUM(O37:O37)))</f>
+        <v/>
+      </c>
+      <c r="AC37" s="4">
+        <f>MAX(0,Q37-MAX(0,X37-SUM(O37:P37)))</f>
+        <v/>
+      </c>
+      <c r="AD37" s="4">
+        <f>MAX(0,R37-MAX(0,X37-SUM(O37:Q37)))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="4">
+        <f>MAX(0,S37-MAX(0,X37-SUM(O37:R37)))</f>
+        <v/>
+      </c>
+      <c r="AF37" s="4">
+        <f>MAX(0,T37-MAX(0,X37-SUM(O37:S37)))</f>
+        <v/>
+      </c>
+      <c r="AG37" s="4">
+        <f>MAX(0,U37-MAX(0,X37-SUM(O37:T37)))</f>
+        <v/>
+      </c>
+      <c r="AH37" s="4">
+        <f>MAX(0,V37-MAX(0,X37-SUM(O37:U37)))</f>
+        <v/>
+      </c>
+      <c r="AI37" s="4">
+        <f>MAX(0,W37-MAX(0,X37-SUM(O37:V37)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802559</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-16, Return : 2026-09-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="4">
+        <f>SUM(O38:W38)-X38</f>
+        <v/>
+      </c>
+      <c r="AA38" s="4">
+        <f>MAX(0,O38-MAX(0,X38))</f>
+        <v/>
+      </c>
+      <c r="AB38" s="4">
+        <f>MAX(0,P38-MAX(0,X38-SUM(O38:O38)))</f>
+        <v/>
+      </c>
+      <c r="AC38" s="4">
+        <f>MAX(0,Q38-MAX(0,X38-SUM(O38:P38)))</f>
+        <v/>
+      </c>
+      <c r="AD38" s="4">
+        <f>MAX(0,R38-MAX(0,X38-SUM(O38:Q38)))</f>
+        <v/>
+      </c>
+      <c r="AE38" s="4">
+        <f>MAX(0,S38-MAX(0,X38-SUM(O38:R38)))</f>
+        <v/>
+      </c>
+      <c r="AF38" s="4">
+        <f>MAX(0,T38-MAX(0,X38-SUM(O38:S38)))</f>
+        <v/>
+      </c>
+      <c r="AG38" s="4">
+        <f>MAX(0,U38-MAX(0,X38-SUM(O38:T38)))</f>
+        <v/>
+      </c>
+      <c r="AH38" s="4">
+        <f>MAX(0,V38-MAX(0,X38-SUM(O38:U38)))</f>
+        <v/>
+      </c>
+      <c r="AI38" s="4">
+        <f>MAX(0,W38-MAX(0,X38-SUM(O38:V38)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802588</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="4">
+        <f>SUM(O39:W39)-X39</f>
+        <v/>
+      </c>
+      <c r="AA39" s="4">
+        <f>MAX(0,O39-MAX(0,X39))</f>
+        <v/>
+      </c>
+      <c r="AB39" s="4">
+        <f>MAX(0,P39-MAX(0,X39-SUM(O39:O39)))</f>
+        <v/>
+      </c>
+      <c r="AC39" s="4">
+        <f>MAX(0,Q39-MAX(0,X39-SUM(O39:P39)))</f>
+        <v/>
+      </c>
+      <c r="AD39" s="4">
+        <f>MAX(0,R39-MAX(0,X39-SUM(O39:Q39)))</f>
+        <v/>
+      </c>
+      <c r="AE39" s="4">
+        <f>MAX(0,S39-MAX(0,X39-SUM(O39:R39)))</f>
+        <v/>
+      </c>
+      <c r="AF39" s="4">
+        <f>MAX(0,T39-MAX(0,X39-SUM(O39:S39)))</f>
+        <v/>
+      </c>
+      <c r="AG39" s="4">
+        <f>MAX(0,U39-MAX(0,X39-SUM(O39:T39)))</f>
+        <v/>
+      </c>
+      <c r="AH39" s="4">
+        <f>MAX(0,V39-MAX(0,X39-SUM(O39:U39)))</f>
+        <v/>
+      </c>
+      <c r="AI39" s="4">
+        <f>MAX(0,W39-MAX(0,X39-SUM(O39:V39)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802589</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>202609230700</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 16-17/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="4">
+        <f>SUM(O40:W40)-X40</f>
+        <v/>
+      </c>
+      <c r="AA40" s="4">
+        <f>MAX(0,O40-MAX(0,X40))</f>
+        <v/>
+      </c>
+      <c r="AB40" s="4">
+        <f>MAX(0,P40-MAX(0,X40-SUM(O40:O40)))</f>
+        <v/>
+      </c>
+      <c r="AC40" s="4">
+        <f>MAX(0,Q40-MAX(0,X40-SUM(O40:P40)))</f>
+        <v/>
+      </c>
+      <c r="AD40" s="4">
+        <f>MAX(0,R40-MAX(0,X40-SUM(O40:Q40)))</f>
+        <v/>
+      </c>
+      <c r="AE40" s="4">
+        <f>MAX(0,S40-MAX(0,X40-SUM(O40:R40)))</f>
+        <v/>
+      </c>
+      <c r="AF40" s="4">
+        <f>MAX(0,T40-MAX(0,X40-SUM(O40:S40)))</f>
+        <v/>
+      </c>
+      <c r="AG40" s="4">
+        <f>MAX(0,U40-MAX(0,X40-SUM(O40:T40)))</f>
+        <v/>
+      </c>
+      <c r="AH40" s="4">
+        <f>MAX(0,V40-MAX(0,X40-SUM(O40:U40)))</f>
+        <v/>
+      </c>
+      <c r="AI40" s="4">
+        <f>MAX(0,W40-MAX(0,X40-SUM(O40:V40)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802590</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>202610011030</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="4">
+        <f>SUM(O41:W41)-X41</f>
+        <v/>
+      </c>
+      <c r="AA41" s="4">
+        <f>MAX(0,O41-MAX(0,X41))</f>
+        <v/>
+      </c>
+      <c r="AB41" s="4">
+        <f>MAX(0,P41-MAX(0,X41-SUM(O41:O41)))</f>
+        <v/>
+      </c>
+      <c r="AC41" s="4">
+        <f>MAX(0,Q41-MAX(0,X41-SUM(O41:P41)))</f>
+        <v/>
+      </c>
+      <c r="AD41" s="4">
+        <f>MAX(0,R41-MAX(0,X41-SUM(O41:Q41)))</f>
+        <v/>
+      </c>
+      <c r="AE41" s="4">
+        <f>MAX(0,S41-MAX(0,X41-SUM(O41:R41)))</f>
+        <v/>
+      </c>
+      <c r="AF41" s="4">
+        <f>MAX(0,T41-MAX(0,X41-SUM(O41:S41)))</f>
+        <v/>
+      </c>
+      <c r="AG41" s="4">
+        <f>MAX(0,U41-MAX(0,X41-SUM(O41:T41)))</f>
+        <v/>
+      </c>
+      <c r="AH41" s="4">
+        <f>MAX(0,V41-MAX(0,X41-SUM(O41:U41)))</f>
+        <v/>
+      </c>
+      <c r="AI41" s="4">
+        <f>MAX(0,W41-MAX(0,X41-SUM(O41:V41)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802591</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>202610020800</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="4">
+        <f>SUM(O42:W42)-X42</f>
+        <v/>
+      </c>
+      <c r="AA42" s="4">
+        <f>MAX(0,O42-MAX(0,X42))</f>
+        <v/>
+      </c>
+      <c r="AB42" s="4">
+        <f>MAX(0,P42-MAX(0,X42-SUM(O42:O42)))</f>
+        <v/>
+      </c>
+      <c r="AC42" s="4">
+        <f>MAX(0,Q42-MAX(0,X42-SUM(O42:P42)))</f>
+        <v/>
+      </c>
+      <c r="AD42" s="4">
+        <f>MAX(0,R42-MAX(0,X42-SUM(O42:Q42)))</f>
+        <v/>
+      </c>
+      <c r="AE42" s="4">
+        <f>MAX(0,S42-MAX(0,X42-SUM(O42:R42)))</f>
+        <v/>
+      </c>
+      <c r="AF42" s="4">
+        <f>MAX(0,T42-MAX(0,X42-SUM(O42:S42)))</f>
+        <v/>
+      </c>
+      <c r="AG42" s="4">
+        <f>MAX(0,U42-MAX(0,X42-SUM(O42:T42)))</f>
+        <v/>
+      </c>
+      <c r="AH42" s="4">
+        <f>MAX(0,V42-MAX(0,X42-SUM(O42:U42)))</f>
+        <v/>
+      </c>
+      <c r="AI42" s="4">
+        <f>MAX(0,W42-MAX(0,X42-SUM(O42:V42)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900019</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>202609251900</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>K LINE LOGISTICS (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>SIAM TOKAI CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>BRINE CURED GINGER</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Remark: Food grade container, Good and Clean
+container, no hole, no rust, no oil stain, no
+splinter</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.23/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="4">
+        <f>SUM(O43:W43)-X43</f>
+        <v/>
+      </c>
+      <c r="AA43" s="4">
+        <f>MAX(0,O43-MAX(0,X43))</f>
+        <v/>
+      </c>
+      <c r="AB43" s="4">
+        <f>MAX(0,P43-MAX(0,X43-SUM(O43:O43)))</f>
+        <v/>
+      </c>
+      <c r="AC43" s="4">
+        <f>MAX(0,Q43-MAX(0,X43-SUM(O43:P43)))</f>
+        <v/>
+      </c>
+      <c r="AD43" s="4">
+        <f>MAX(0,R43-MAX(0,X43-SUM(O43:Q43)))</f>
+        <v/>
+      </c>
+      <c r="AE43" s="4">
+        <f>MAX(0,S43-MAX(0,X43-SUM(O43:R43)))</f>
+        <v/>
+      </c>
+      <c r="AF43" s="4">
+        <f>MAX(0,T43-MAX(0,X43-SUM(O43:S43)))</f>
+        <v/>
+      </c>
+      <c r="AG43" s="4">
+        <f>MAX(0,U43-MAX(0,X43-SUM(O43:T43)))</f>
+        <v/>
+      </c>
+      <c r="AH43" s="4">
+        <f>MAX(0,V43-MAX(0,X43-SUM(O43:U43)))</f>
+        <v/>
+      </c>
+      <c r="AI43" s="4">
+        <f>MAX(0,W43-MAX(0,X43-SUM(O43:V43)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900064</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>202609291200</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="4">
+        <f>SUM(O44:W44)-X44</f>
+        <v/>
+      </c>
+      <c r="AA44" s="4">
+        <f>MAX(0,O44-MAX(0,X44))</f>
+        <v/>
+      </c>
+      <c r="AB44" s="4">
+        <f>MAX(0,P44-MAX(0,X44-SUM(O44:O44)))</f>
+        <v/>
+      </c>
+      <c r="AC44" s="4">
+        <f>MAX(0,Q44-MAX(0,X44-SUM(O44:P44)))</f>
+        <v/>
+      </c>
+      <c r="AD44" s="4">
+        <f>MAX(0,R44-MAX(0,X44-SUM(O44:Q44)))</f>
+        <v/>
+      </c>
+      <c r="AE44" s="4">
+        <f>MAX(0,S44-MAX(0,X44-SUM(O44:R44)))</f>
+        <v/>
+      </c>
+      <c r="AF44" s="4">
+        <f>MAX(0,T44-MAX(0,X44-SUM(O44:S44)))</f>
+        <v/>
+      </c>
+      <c r="AG44" s="4">
+        <f>MAX(0,U44-MAX(0,X44-SUM(O44:T44)))</f>
+        <v/>
+      </c>
+      <c r="AH44" s="4">
+        <f>MAX(0,V44-MAX(0,X44-SUM(O44:U44)))</f>
+        <v/>
+      </c>
+      <c r="AI44" s="4">
+        <f>MAX(0,W44-MAX(0,X44-SUM(O44:V44)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900162</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>202609230700</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18  CONSOL </t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="4">
+        <f>SUM(O45:W45)-X45</f>
+        <v/>
+      </c>
+      <c r="AA45" s="4">
+        <f>MAX(0,O45-MAX(0,X45))</f>
+        <v/>
+      </c>
+      <c r="AB45" s="4">
+        <f>MAX(0,P45-MAX(0,X45-SUM(O45:O45)))</f>
+        <v/>
+      </c>
+      <c r="AC45" s="4">
+        <f>MAX(0,Q45-MAX(0,X45-SUM(O45:P45)))</f>
+        <v/>
+      </c>
+      <c r="AD45" s="4">
+        <f>MAX(0,R45-MAX(0,X45-SUM(O45:Q45)))</f>
+        <v/>
+      </c>
+      <c r="AE45" s="4">
+        <f>MAX(0,S45-MAX(0,X45-SUM(O45:R45)))</f>
+        <v/>
+      </c>
+      <c r="AF45" s="4">
+        <f>MAX(0,T45-MAX(0,X45-SUM(O45:S45)))</f>
+        <v/>
+      </c>
+      <c r="AG45" s="4">
+        <f>MAX(0,U45-MAX(0,X45-SUM(O45:T45)))</f>
+        <v/>
+      </c>
+      <c r="AH45" s="4">
+        <f>MAX(0,V45-MAX(0,X45-SUM(O45:U45)))</f>
+        <v/>
+      </c>
+      <c r="AI45" s="4">
+        <f>MAX(0,W45-MAX(0,X45-SUM(O45:V45)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900165</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>202609301800</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="4">
+        <f>SUM(O46:W46)-X46</f>
+        <v/>
+      </c>
+      <c r="AA46" s="4">
+        <f>MAX(0,O46-MAX(0,X46))</f>
+        <v/>
+      </c>
+      <c r="AB46" s="4">
+        <f>MAX(0,P46-MAX(0,X46-SUM(O46:O46)))</f>
+        <v/>
+      </c>
+      <c r="AC46" s="4">
+        <f>MAX(0,Q46-MAX(0,X46-SUM(O46:P46)))</f>
+        <v/>
+      </c>
+      <c r="AD46" s="4">
+        <f>MAX(0,R46-MAX(0,X46-SUM(O46:Q46)))</f>
+        <v/>
+      </c>
+      <c r="AE46" s="4">
+        <f>MAX(0,S46-MAX(0,X46-SUM(O46:R46)))</f>
+        <v/>
+      </c>
+      <c r="AF46" s="4">
+        <f>MAX(0,T46-MAX(0,X46-SUM(O46:S46)))</f>
+        <v/>
+      </c>
+      <c r="AG46" s="4">
+        <f>MAX(0,U46-MAX(0,X46-SUM(O46:T46)))</f>
+        <v/>
+      </c>
+      <c r="AH46" s="4">
+        <f>MAX(0,V46-MAX(0,X46-SUM(O46:U46)))</f>
+        <v/>
+      </c>
+      <c r="AI46" s="4">
+        <f>MAX(0,W46-MAX(0,X46-SUM(O46:V46)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900172</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>202609251900</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-25, Return : 2026-09-25 CONSOL </t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="4">
+        <f>SUM(O47:W47)-X47</f>
+        <v/>
+      </c>
+      <c r="AA47" s="4">
+        <f>MAX(0,O47-MAX(0,X47))</f>
+        <v/>
+      </c>
+      <c r="AB47" s="4">
+        <f>MAX(0,P47-MAX(0,X47-SUM(O47:O47)))</f>
+        <v/>
+      </c>
+      <c r="AC47" s="4">
+        <f>MAX(0,Q47-MAX(0,X47-SUM(O47:P47)))</f>
+        <v/>
+      </c>
+      <c r="AD47" s="4">
+        <f>MAX(0,R47-MAX(0,X47-SUM(O47:Q47)))</f>
+        <v/>
+      </c>
+      <c r="AE47" s="4">
+        <f>MAX(0,S47-MAX(0,X47-SUM(O47:R47)))</f>
+        <v/>
+      </c>
+      <c r="AF47" s="4">
+        <f>MAX(0,T47-MAX(0,X47-SUM(O47:S47)))</f>
+        <v/>
+      </c>
+      <c r="AG47" s="4">
+        <f>MAX(0,U47-MAX(0,X47-SUM(O47:T47)))</f>
+        <v/>
+      </c>
+      <c r="AH47" s="4">
+        <f>MAX(0,V47-MAX(0,X47-SUM(O47:U47)))</f>
+        <v/>
+      </c>
+      <c r="AI47" s="4">
+        <f>MAX(0,W47-MAX(0,X47-SUM(O47:V47)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900181</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY ACCESS GLOBAL LOGISTICS CO., LTD</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-07, Return : 2026-09-11 CONSOL</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="4">
+        <f>SUM(O48:W48)-X48</f>
+        <v/>
+      </c>
+      <c r="AA48" s="4">
+        <f>MAX(0,O48-MAX(0,X48))</f>
+        <v/>
+      </c>
+      <c r="AB48" s="4">
+        <f>MAX(0,P48-MAX(0,X48-SUM(O48:O48)))</f>
+        <v/>
+      </c>
+      <c r="AC48" s="4">
+        <f>MAX(0,Q48-MAX(0,X48-SUM(O48:P48)))</f>
+        <v/>
+      </c>
+      <c r="AD48" s="4">
+        <f>MAX(0,R48-MAX(0,X48-SUM(O48:Q48)))</f>
+        <v/>
+      </c>
+      <c r="AE48" s="4">
+        <f>MAX(0,S48-MAX(0,X48-SUM(O48:R48)))</f>
+        <v/>
+      </c>
+      <c r="AF48" s="4">
+        <f>MAX(0,T48-MAX(0,X48-SUM(O48:S48)))</f>
+        <v/>
+      </c>
+      <c r="AG48" s="4">
+        <f>MAX(0,U48-MAX(0,X48-SUM(O48:T48)))</f>
+        <v/>
+      </c>
+      <c r="AH48" s="4">
+        <f>MAX(0,V48-MAX(0,X48-SUM(O48:U48)))</f>
+        <v/>
+      </c>
+      <c r="AI48" s="4">
+        <f>MAX(0,W48-MAX(0,X48-SUM(O48:V48)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900184</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>202609181000</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 10-11/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="4">
+        <f>SUM(O49:W49)-X49</f>
+        <v/>
+      </c>
+      <c r="AA49" s="4">
+        <f>MAX(0,O49-MAX(0,X49))</f>
+        <v/>
+      </c>
+      <c r="AB49" s="4">
+        <f>MAX(0,P49-MAX(0,X49-SUM(O49:O49)))</f>
+        <v/>
+      </c>
+      <c r="AC49" s="4">
+        <f>MAX(0,Q49-MAX(0,X49-SUM(O49:P49)))</f>
+        <v/>
+      </c>
+      <c r="AD49" s="4">
+        <f>MAX(0,R49-MAX(0,X49-SUM(O49:Q49)))</f>
+        <v/>
+      </c>
+      <c r="AE49" s="4">
+        <f>MAX(0,S49-MAX(0,X49-SUM(O49:R49)))</f>
+        <v/>
+      </c>
+      <c r="AF49" s="4">
+        <f>MAX(0,T49-MAX(0,X49-SUM(O49:S49)))</f>
+        <v/>
+      </c>
+      <c r="AG49" s="4">
+        <f>MAX(0,U49-MAX(0,X49-SUM(O49:T49)))</f>
+        <v/>
+      </c>
+      <c r="AH49" s="4">
+        <f>MAX(0,V49-MAX(0,X49-SUM(O49:U49)))</f>
+        <v/>
+      </c>
+      <c r="AI49" s="4">
+        <f>MAX(0,W49-MAX(0,X49-SUM(O49:V49)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900186</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="4">
+        <f>SUM(O50:W50)-X50</f>
+        <v/>
+      </c>
+      <c r="AA50" s="4">
+        <f>MAX(0,O50-MAX(0,X50))</f>
+        <v/>
+      </c>
+      <c r="AB50" s="4">
+        <f>MAX(0,P50-MAX(0,X50-SUM(O50:O50)))</f>
+        <v/>
+      </c>
+      <c r="AC50" s="4">
+        <f>MAX(0,Q50-MAX(0,X50-SUM(O50:P50)))</f>
+        <v/>
+      </c>
+      <c r="AD50" s="4">
+        <f>MAX(0,R50-MAX(0,X50-SUM(O50:Q50)))</f>
+        <v/>
+      </c>
+      <c r="AE50" s="4">
+        <f>MAX(0,S50-MAX(0,X50-SUM(O50:R50)))</f>
+        <v/>
+      </c>
+      <c r="AF50" s="4">
+        <f>MAX(0,T50-MAX(0,X50-SUM(O50:S50)))</f>
+        <v/>
+      </c>
+      <c r="AG50" s="4">
+        <f>MAX(0,U50-MAX(0,X50-SUM(O50:T50)))</f>
+        <v/>
+      </c>
+      <c r="AH50" s="4">
+        <f>MAX(0,V50-MAX(0,X50-SUM(O50:U50)))</f>
+        <v/>
+      </c>
+      <c r="AI50" s="4">
+        <f>MAX(0,W50-MAX(0,X50-SUM(O50:V50)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900187</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="4">
+        <f>SUM(O51:W51)-X51</f>
+        <v/>
+      </c>
+      <c r="AA51" s="4">
+        <f>MAX(0,O51-MAX(0,X51))</f>
+        <v/>
+      </c>
+      <c r="AB51" s="4">
+        <f>MAX(0,P51-MAX(0,X51-SUM(O51:O51)))</f>
+        <v/>
+      </c>
+      <c r="AC51" s="4">
+        <f>MAX(0,Q51-MAX(0,X51-SUM(O51:P51)))</f>
+        <v/>
+      </c>
+      <c r="AD51" s="4">
+        <f>MAX(0,R51-MAX(0,X51-SUM(O51:Q51)))</f>
+        <v/>
+      </c>
+      <c r="AE51" s="4">
+        <f>MAX(0,S51-MAX(0,X51-SUM(O51:R51)))</f>
+        <v/>
+      </c>
+      <c r="AF51" s="4">
+        <f>MAX(0,T51-MAX(0,X51-SUM(O51:S51)))</f>
+        <v/>
+      </c>
+      <c r="AG51" s="4">
+        <f>MAX(0,U51-MAX(0,X51-SUM(O51:T51)))</f>
+        <v/>
+      </c>
+      <c r="AH51" s="4">
+        <f>MAX(0,V51-MAX(0,X51-SUM(O51:U51)))</f>
+        <v/>
+      </c>
+      <c r="AI51" s="4">
+        <f>MAX(0,W51-MAX(0,X51-SUM(O51:V51)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900188</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>202609251900</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 23-24/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="4">
+        <f>SUM(O52:W52)-X52</f>
+        <v/>
+      </c>
+      <c r="AA52" s="4">
+        <f>MAX(0,O52-MAX(0,X52))</f>
+        <v/>
+      </c>
+      <c r="AB52" s="4">
+        <f>MAX(0,P52-MAX(0,X52-SUM(O52:O52)))</f>
+        <v/>
+      </c>
+      <c r="AC52" s="4">
+        <f>MAX(0,Q52-MAX(0,X52-SUM(O52:P52)))</f>
+        <v/>
+      </c>
+      <c r="AD52" s="4">
+        <f>MAX(0,R52-MAX(0,X52-SUM(O52:Q52)))</f>
+        <v/>
+      </c>
+      <c r="AE52" s="4">
+        <f>MAX(0,S52-MAX(0,X52-SUM(O52:R52)))</f>
+        <v/>
+      </c>
+      <c r="AF52" s="4">
+        <f>MAX(0,T52-MAX(0,X52-SUM(O52:S52)))</f>
+        <v/>
+      </c>
+      <c r="AG52" s="4">
+        <f>MAX(0,U52-MAX(0,X52-SUM(O52:T52)))</f>
+        <v/>
+      </c>
+      <c r="AH52" s="4">
+        <f>MAX(0,V52-MAX(0,X52-SUM(O52:U52)))</f>
+        <v/>
+      </c>
+      <c r="AI52" s="4">
+        <f>MAX(0,W52-MAX(0,X52-SUM(O52:V52)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900189</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>202609301800</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="4">
+        <f>SUM(O53:W53)-X53</f>
+        <v/>
+      </c>
+      <c r="AA53" s="4">
+        <f>MAX(0,O53-MAX(0,X53))</f>
+        <v/>
+      </c>
+      <c r="AB53" s="4">
+        <f>MAX(0,P53-MAX(0,X53-SUM(O53:O53)))</f>
+        <v/>
+      </c>
+      <c r="AC53" s="4">
+        <f>MAX(0,Q53-MAX(0,X53-SUM(O53:P53)))</f>
+        <v/>
+      </c>
+      <c r="AD53" s="4">
+        <f>MAX(0,R53-MAX(0,X53-SUM(O53:Q53)))</f>
+        <v/>
+      </c>
+      <c r="AE53" s="4">
+        <f>MAX(0,S53-MAX(0,X53-SUM(O53:R53)))</f>
+        <v/>
+      </c>
+      <c r="AF53" s="4">
+        <f>MAX(0,T53-MAX(0,X53-SUM(O53:S53)))</f>
+        <v/>
+      </c>
+      <c r="AG53" s="4">
+        <f>MAX(0,U53-MAX(0,X53-SUM(O53:T53)))</f>
+        <v/>
+      </c>
+      <c r="AH53" s="4">
+        <f>MAX(0,V53-MAX(0,X53-SUM(O53:U53)))</f>
+        <v/>
+      </c>
+      <c r="AI53" s="4">
+        <f>MAX(0,W53-MAX(0,X53-SUM(O53:V53)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900206</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>202609291200</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="4">
+        <f>SUM(O54:W54)-X54</f>
+        <v/>
+      </c>
+      <c r="AA54" s="4">
+        <f>MAX(0,O54-MAX(0,X54))</f>
+        <v/>
+      </c>
+      <c r="AB54" s="4">
+        <f>MAX(0,P54-MAX(0,X54-SUM(O54:O54)))</f>
+        <v/>
+      </c>
+      <c r="AC54" s="4">
+        <f>MAX(0,Q54-MAX(0,X54-SUM(O54:P54)))</f>
+        <v/>
+      </c>
+      <c r="AD54" s="4">
+        <f>MAX(0,R54-MAX(0,X54-SUM(O54:Q54)))</f>
+        <v/>
+      </c>
+      <c r="AE54" s="4">
+        <f>MAX(0,S54-MAX(0,X54-SUM(O54:R54)))</f>
+        <v/>
+      </c>
+      <c r="AF54" s="4">
+        <f>MAX(0,T54-MAX(0,X54-SUM(O54:S54)))</f>
+        <v/>
+      </c>
+      <c r="AG54" s="4">
+        <f>MAX(0,U54-MAX(0,X54-SUM(O54:T54)))</f>
+        <v/>
+      </c>
+      <c r="AH54" s="4">
+        <f>MAX(0,V54-MAX(0,X54-SUM(O54:U54)))</f>
+        <v/>
+      </c>
+      <c r="AI54" s="4">
+        <f>MAX(0,W54-MAX(0,X54-SUM(O54:V54)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900234</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pickup : 2026-09-10, Return : 2026-09-11 CONSOL   
 [1ST CY DATE : 17/09/2026 WO RENT] </t>
         </is>
       </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4">
-        <f>SUM(O12:W12)-X12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="4">
-        <f>MAX(0,O12-MAX(0,X12))</f>
-        <v/>
-      </c>
-      <c r="AB12" s="4">
-        <f>MAX(0,P12-MAX(0,X12-SUM(O12:O12)))</f>
-        <v/>
-      </c>
-      <c r="AC12" s="4">
-        <f>MAX(0,Q12-MAX(0,X12-SUM(O12:P12)))</f>
-        <v/>
-      </c>
-      <c r="AD12" s="4">
-        <f>MAX(0,R12-MAX(0,X12-SUM(O12:Q12)))</f>
-        <v/>
-      </c>
-      <c r="AE12" s="4">
-        <f>MAX(0,S12-MAX(0,X12-SUM(O12:R12)))</f>
-        <v/>
-      </c>
-      <c r="AF12" s="4">
-        <f>MAX(0,T12-MAX(0,X12-SUM(O12:S12)))</f>
-        <v/>
-      </c>
-      <c r="AG12" s="4">
-        <f>MAX(0,U12-MAX(0,X12-SUM(O12:T12)))</f>
-        <v/>
-      </c>
-      <c r="AH12" s="4">
-        <f>MAX(0,V12-MAX(0,X12-SUM(O12:U12)))</f>
-        <v/>
-      </c>
-      <c r="AI12" s="4">
-        <f>MAX(0,W12-MAX(0,X12-SUM(O12:V12)))</f>
+      <c r="R55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z55" s="4">
+        <f>SUM(O55:W55)-X55</f>
+        <v/>
+      </c>
+      <c r="AA55" s="4">
+        <f>MAX(0,O55-MAX(0,X55))</f>
+        <v/>
+      </c>
+      <c r="AB55" s="4">
+        <f>MAX(0,P55-MAX(0,X55-SUM(O55:O55)))</f>
+        <v/>
+      </c>
+      <c r="AC55" s="4">
+        <f>MAX(0,Q55-MAX(0,X55-SUM(O55:P55)))</f>
+        <v/>
+      </c>
+      <c r="AD55" s="4">
+        <f>MAX(0,R55-MAX(0,X55-SUM(O55:Q55)))</f>
+        <v/>
+      </c>
+      <c r="AE55" s="4">
+        <f>MAX(0,S55-MAX(0,X55-SUM(O55:R55)))</f>
+        <v/>
+      </c>
+      <c r="AF55" s="4">
+        <f>MAX(0,T55-MAX(0,X55-SUM(O55:S55)))</f>
+        <v/>
+      </c>
+      <c r="AG55" s="4">
+        <f>MAX(0,U55-MAX(0,X55-SUM(O55:T55)))</f>
+        <v/>
+      </c>
+      <c r="AH55" s="4">
+        <f>MAX(0,V55-MAX(0,X55-SUM(O55:U55)))</f>
+        <v/>
+      </c>
+      <c r="AI55" s="4">
+        <f>MAX(0,W55-MAX(0,X55-SUM(O55:V55)))</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900262</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>202609230700</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>RAINBOW MARITIME (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>COTTON BUDS</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 22/09/26 *CLS TIME 22/09 @17.00HRS*</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="4">
+        <f>SUM(O56:W56)-X56</f>
+        <v/>
+      </c>
+      <c r="AA56" s="4">
+        <f>MAX(0,O56-MAX(0,X56))</f>
+        <v/>
+      </c>
+      <c r="AB56" s="4">
+        <f>MAX(0,P56-MAX(0,X56-SUM(O56:O56)))</f>
+        <v/>
+      </c>
+      <c r="AC56" s="4">
+        <f>MAX(0,Q56-MAX(0,X56-SUM(O56:P56)))</f>
+        <v/>
+      </c>
+      <c r="AD56" s="4">
+        <f>MAX(0,R56-MAX(0,X56-SUM(O56:Q56)))</f>
+        <v/>
+      </c>
+      <c r="AE56" s="4">
+        <f>MAX(0,S56-MAX(0,X56-SUM(O56:R56)))</f>
+        <v/>
+      </c>
+      <c r="AF56" s="4">
+        <f>MAX(0,T56-MAX(0,X56-SUM(O56:S56)))</f>
+        <v/>
+      </c>
+      <c r="AG56" s="4">
+        <f>MAX(0,U56-MAX(0,X56-SUM(O56:T56)))</f>
+        <v/>
+      </c>
+      <c r="AH56" s="4">
+        <f>MAX(0,V56-MAX(0,X56-SUM(O56:U56)))</f>
+        <v/>
+      </c>
+      <c r="AI56" s="4">
+        <f>MAX(0,W56-MAX(0,X56-SUM(O56:V56)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900309</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-15, Return : 2026-09-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="4">
+        <f>SUM(O57:W57)-X57</f>
+        <v/>
+      </c>
+      <c r="AA57" s="4">
+        <f>MAX(0,O57-MAX(0,X57))</f>
+        <v/>
+      </c>
+      <c r="AB57" s="4">
+        <f>MAX(0,P57-MAX(0,X57-SUM(O57:O57)))</f>
+        <v/>
+      </c>
+      <c r="AC57" s="4">
+        <f>MAX(0,Q57-MAX(0,X57-SUM(O57:P57)))</f>
+        <v/>
+      </c>
+      <c r="AD57" s="4">
+        <f>MAX(0,R57-MAX(0,X57-SUM(O57:Q57)))</f>
+        <v/>
+      </c>
+      <c r="AE57" s="4">
+        <f>MAX(0,S57-MAX(0,X57-SUM(O57:R57)))</f>
+        <v/>
+      </c>
+      <c r="AF57" s="4">
+        <f>MAX(0,T57-MAX(0,X57-SUM(O57:S57)))</f>
+        <v/>
+      </c>
+      <c r="AG57" s="4">
+        <f>MAX(0,U57-MAX(0,X57-SUM(O57:T57)))</f>
+        <v/>
+      </c>
+      <c r="AH57" s="4">
+        <f>MAX(0,V57-MAX(0,X57-SUM(O57:U57)))</f>
+        <v/>
+      </c>
+      <c r="AI57" s="4">
+        <f>MAX(0,W57-MAX(0,X57-SUM(O57:V57)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900323</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>202609291200</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>POLAR STAR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="4">
+        <f>SUM(O58:W58)-X58</f>
+        <v/>
+      </c>
+      <c r="AA58" s="4">
+        <f>MAX(0,O58-MAX(0,X58))</f>
+        <v/>
+      </c>
+      <c r="AB58" s="4">
+        <f>MAX(0,P58-MAX(0,X58-SUM(O58:O58)))</f>
+        <v/>
+      </c>
+      <c r="AC58" s="4">
+        <f>MAX(0,Q58-MAX(0,X58-SUM(O58:P58)))</f>
+        <v/>
+      </c>
+      <c r="AD58" s="4">
+        <f>MAX(0,R58-MAX(0,X58-SUM(O58:Q58)))</f>
+        <v/>
+      </c>
+      <c r="AE58" s="4">
+        <f>MAX(0,S58-MAX(0,X58-SUM(O58:R58)))</f>
+        <v/>
+      </c>
+      <c r="AF58" s="4">
+        <f>MAX(0,T58-MAX(0,X58-SUM(O58:S58)))</f>
+        <v/>
+      </c>
+      <c r="AG58" s="4">
+        <f>MAX(0,U58-MAX(0,X58-SUM(O58:T58)))</f>
+        <v/>
+      </c>
+      <c r="AH58" s="4">
+        <f>MAX(0,V58-MAX(0,X58-SUM(O58:U58)))</f>
+        <v/>
+      </c>
+      <c r="AI58" s="4">
+        <f>MAX(0,W58-MAX(0,X58-SUM(O58:V58)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900628</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>202609301800</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>SAHAPARA RUBBER CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>NATURAL RUBBER</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.29/09/26 *CLS TIME CFS DD.28/09/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="4">
+        <f>SUM(O59:W59)-X59</f>
+        <v/>
+      </c>
+      <c r="AA59" s="4">
+        <f>MAX(0,O59-MAX(0,X59))</f>
+        <v/>
+      </c>
+      <c r="AB59" s="4">
+        <f>MAX(0,P59-MAX(0,X59-SUM(O59:O59)))</f>
+        <v/>
+      </c>
+      <c r="AC59" s="4">
+        <f>MAX(0,Q59-MAX(0,X59-SUM(O59:P59)))</f>
+        <v/>
+      </c>
+      <c r="AD59" s="4">
+        <f>MAX(0,R59-MAX(0,X59-SUM(O59:Q59)))</f>
+        <v/>
+      </c>
+      <c r="AE59" s="4">
+        <f>MAX(0,S59-MAX(0,X59-SUM(O59:R59)))</f>
+        <v/>
+      </c>
+      <c r="AF59" s="4">
+        <f>MAX(0,T59-MAX(0,X59-SUM(O59:S59)))</f>
+        <v/>
+      </c>
+      <c r="AG59" s="4">
+        <f>MAX(0,U59-MAX(0,X59-SUM(O59:T59)))</f>
+        <v/>
+      </c>
+      <c r="AH59" s="4">
+        <f>MAX(0,V59-MAX(0,X59-SUM(O59:U59)))</f>
+        <v/>
+      </c>
+      <c r="AI59" s="4">
+        <f>MAX(0,W59-MAX(0,X59-SUM(O59:V59)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900717</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>ELC CONTAINER LINES CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>CONTAINER GRADE A</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 18/09/26 CLS TIME 21/09 @17.00HRS 
+ (1ST CFS : 18/09 W/O RENT) </t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="4">
+        <f>SUM(O60:W60)-X60</f>
+        <v/>
+      </c>
+      <c r="AA60" s="4">
+        <f>MAX(0,O60-MAX(0,X60))</f>
+        <v/>
+      </c>
+      <c r="AB60" s="4">
+        <f>MAX(0,P60-MAX(0,X60-SUM(O60:O60)))</f>
+        <v/>
+      </c>
+      <c r="AC60" s="4">
+        <f>MAX(0,Q60-MAX(0,X60-SUM(O60:P60)))</f>
+        <v/>
+      </c>
+      <c r="AD60" s="4">
+        <f>MAX(0,R60-MAX(0,X60-SUM(O60:Q60)))</f>
+        <v/>
+      </c>
+      <c r="AE60" s="4">
+        <f>MAX(0,S60-MAX(0,X60-SUM(O60:R60)))</f>
+        <v/>
+      </c>
+      <c r="AF60" s="4">
+        <f>MAX(0,T60-MAX(0,X60-SUM(O60:S60)))</f>
+        <v/>
+      </c>
+      <c r="AG60" s="4">
+        <f>MAX(0,U60-MAX(0,X60-SUM(O60:T60)))</f>
+        <v/>
+      </c>
+      <c r="AH60" s="4">
+        <f>MAX(0,V60-MAX(0,X60-SUM(O60:U60)))</f>
+        <v/>
+      </c>
+      <c r="AI60" s="4">
+        <f>MAX(0,W60-MAX(0,X60-SUM(O60:V60)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900803</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>SEA 2 SKY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>BANYAN TREE GALLERY (THAILAND) COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>HOTEL ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Requested Good &amp; Clean contr</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/09/26 CLS TIME CFS DD.18/09/26 - 17:00HRS.
+(1ST RTN DD: 17/09/26 WO/RENT)</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="4">
+        <f>SUM(O61:W61)-X61</f>
+        <v/>
+      </c>
+      <c r="AA61" s="4">
+        <f>MAX(0,O61-MAX(0,X61))</f>
+        <v/>
+      </c>
+      <c r="AB61" s="4">
+        <f>MAX(0,P61-MAX(0,X61-SUM(O61:O61)))</f>
+        <v/>
+      </c>
+      <c r="AC61" s="4">
+        <f>MAX(0,Q61-MAX(0,X61-SUM(O61:P61)))</f>
+        <v/>
+      </c>
+      <c r="AD61" s="4">
+        <f>MAX(0,R61-MAX(0,X61-SUM(O61:Q61)))</f>
+        <v/>
+      </c>
+      <c r="AE61" s="4">
+        <f>MAX(0,S61-MAX(0,X61-SUM(O61:R61)))</f>
+        <v/>
+      </c>
+      <c r="AF61" s="4">
+        <f>MAX(0,T61-MAX(0,X61-SUM(O61:S61)))</f>
+        <v/>
+      </c>
+      <c r="AG61" s="4">
+        <f>MAX(0,U61-MAX(0,X61-SUM(O61:T61)))</f>
+        <v/>
+      </c>
+      <c r="AH61" s="4">
+        <f>MAX(0,V61-MAX(0,X61-SUM(O61:U61)))</f>
+        <v/>
+      </c>
+      <c r="AI61" s="4">
+        <f>MAX(0,W61-MAX(0,X61-SUM(O61:V61)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900855</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>202609241500</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>LITTLE THAI INTERNATIONAL CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>SEASONINGS</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>REQ. FOOD GRADE CONTAINER</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING DD.22/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.22/09/2026 @ 17.00 REQ. FOOD GRADE CONTAINER </t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="4">
+        <f>SUM(O62:W62)-X62</f>
+        <v/>
+      </c>
+      <c r="AA62" s="4">
+        <f>MAX(0,O62-MAX(0,X62))</f>
+        <v/>
+      </c>
+      <c r="AB62" s="4">
+        <f>MAX(0,P62-MAX(0,X62-SUM(O62:O62)))</f>
+        <v/>
+      </c>
+      <c r="AC62" s="4">
+        <f>MAX(0,Q62-MAX(0,X62-SUM(O62:P62)))</f>
+        <v/>
+      </c>
+      <c r="AD62" s="4">
+        <f>MAX(0,R62-MAX(0,X62-SUM(O62:Q62)))</f>
+        <v/>
+      </c>
+      <c r="AE62" s="4">
+        <f>MAX(0,S62-MAX(0,X62-SUM(O62:R62)))</f>
+        <v/>
+      </c>
+      <c r="AF62" s="4">
+        <f>MAX(0,T62-MAX(0,X62-SUM(O62:S62)))</f>
+        <v/>
+      </c>
+      <c r="AG62" s="4">
+        <f>MAX(0,U62-MAX(0,X62-SUM(O62:T62)))</f>
+        <v/>
+      </c>
+      <c r="AH62" s="4">
+        <f>MAX(0,V62-MAX(0,X62-SUM(O62:U62)))</f>
+        <v/>
+      </c>
+      <c r="AI62" s="4">
+        <f>MAX(0,W62-MAX(0,X62-SUM(O62:V62)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900896</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>202610020800</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-01CONSOL</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="4">
+        <f>SUM(O63:W63)-X63</f>
+        <v/>
+      </c>
+      <c r="AA63" s="4">
+        <f>MAX(0,O63-MAX(0,X63))</f>
+        <v/>
+      </c>
+      <c r="AB63" s="4">
+        <f>MAX(0,P63-MAX(0,X63-SUM(O63:O63)))</f>
+        <v/>
+      </c>
+      <c r="AC63" s="4">
+        <f>MAX(0,Q63-MAX(0,X63-SUM(O63:P63)))</f>
+        <v/>
+      </c>
+      <c r="AD63" s="4">
+        <f>MAX(0,R63-MAX(0,X63-SUM(O63:Q63)))</f>
+        <v/>
+      </c>
+      <c r="AE63" s="4">
+        <f>MAX(0,S63-MAX(0,X63-SUM(O63:R63)))</f>
+        <v/>
+      </c>
+      <c r="AF63" s="4">
+        <f>MAX(0,T63-MAX(0,X63-SUM(O63:S63)))</f>
+        <v/>
+      </c>
+      <c r="AG63" s="4">
+        <f>MAX(0,U63-MAX(0,X63-SUM(O63:T63)))</f>
+        <v/>
+      </c>
+      <c r="AH63" s="4">
+        <f>MAX(0,V63-MAX(0,X63-SUM(O63:U63)))</f>
+        <v/>
+      </c>
+      <c r="AI63" s="4">
+        <f>MAX(0,W63-MAX(0,X63-SUM(O63:V63)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900957</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>202610020800</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>PILOT AIR CARGO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>PILOT AIR CARGO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>COW LEATHER</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.29/09/26 CLS TIME CFS DD.30/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="4">
+        <f>SUM(O64:W64)-X64</f>
+        <v/>
+      </c>
+      <c r="AA64" s="4">
+        <f>MAX(0,O64-MAX(0,X64))</f>
+        <v/>
+      </c>
+      <c r="AB64" s="4">
+        <f>MAX(0,P64-MAX(0,X64-SUM(O64:O64)))</f>
+        <v/>
+      </c>
+      <c r="AC64" s="4">
+        <f>MAX(0,Q64-MAX(0,X64-SUM(O64:P64)))</f>
+        <v/>
+      </c>
+      <c r="AD64" s="4">
+        <f>MAX(0,R64-MAX(0,X64-SUM(O64:Q64)))</f>
+        <v/>
+      </c>
+      <c r="AE64" s="4">
+        <f>MAX(0,S64-MAX(0,X64-SUM(O64:R64)))</f>
+        <v/>
+      </c>
+      <c r="AF64" s="4">
+        <f>MAX(0,T64-MAX(0,X64-SUM(O64:S64)))</f>
+        <v/>
+      </c>
+      <c r="AG64" s="4">
+        <f>MAX(0,U64-MAX(0,X64-SUM(O64:T64)))</f>
+        <v/>
+      </c>
+      <c r="AH64" s="4">
+        <f>MAX(0,V64-MAX(0,X64-SUM(O64:U64)))</f>
+        <v/>
+      </c>
+      <c r="AI64" s="4">
+        <f>MAX(0,W64-MAX(0,X64-SUM(O64:V64)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5">
-        <f>SUM(O3:O12)</f>
-        <v/>
-      </c>
-      <c r="P13" s="5">
-        <f>SUM(P3:P12)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="5">
-        <f>SUM(Q3:Q12)</f>
-        <v/>
-      </c>
-      <c r="R13" s="5">
-        <f>SUM(R3:R12)</f>
-        <v/>
-      </c>
-      <c r="S13" s="5">
-        <f>SUM(S3:S12)</f>
-        <v/>
-      </c>
-      <c r="T13" s="5">
-        <f>SUM(T3:T12)</f>
-        <v/>
-      </c>
-      <c r="U13" s="5">
-        <f>SUM(U3:U12)</f>
-        <v/>
-      </c>
-      <c r="V13" s="5">
-        <f>SUM(V3:V12)</f>
-        <v/>
-      </c>
-      <c r="W13" s="5">
-        <f>SUM(W3:W12)</f>
-        <v/>
-      </c>
-      <c r="X13" s="5">
-        <f>SUM(X3:X12)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="5" t="n"/>
-      <c r="Z13" s="5">
-        <f>SUM(Z3:Z12)</f>
-        <v/>
-      </c>
-      <c r="AA13" s="5">
-        <f>SUM(AA3:AA12)</f>
-        <v/>
-      </c>
-      <c r="AB13" s="5">
-        <f>SUM(AB3:AB12)</f>
-        <v/>
-      </c>
-      <c r="AC13" s="5">
-        <f>SUM(AC3:AC12)</f>
-        <v/>
-      </c>
-      <c r="AD13" s="5">
-        <f>SUM(AD3:AD12)</f>
-        <v/>
-      </c>
-      <c r="AE13" s="5">
-        <f>SUM(AE3:AE12)</f>
-        <v/>
-      </c>
-      <c r="AF13" s="5">
-        <f>SUM(AF3:AF12)</f>
-        <v/>
-      </c>
-      <c r="AG13" s="5">
-        <f>SUM(AG3:AG12)</f>
-        <v/>
-      </c>
-      <c r="AH13" s="5">
-        <f>SUM(AH3:AH12)</f>
-        <v/>
-      </c>
-      <c r="AI13" s="5">
-        <f>SUM(AI3:AI12)</f>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5">
+        <f>SUM(O3:O64)</f>
+        <v/>
+      </c>
+      <c r="P65" s="5">
+        <f>SUM(P3:P64)</f>
+        <v/>
+      </c>
+      <c r="Q65" s="5">
+        <f>SUM(Q3:Q64)</f>
+        <v/>
+      </c>
+      <c r="R65" s="5">
+        <f>SUM(R3:R64)</f>
+        <v/>
+      </c>
+      <c r="S65" s="5">
+        <f>SUM(S3:S64)</f>
+        <v/>
+      </c>
+      <c r="T65" s="5">
+        <f>SUM(T3:T64)</f>
+        <v/>
+      </c>
+      <c r="U65" s="5">
+        <f>SUM(U3:U64)</f>
+        <v/>
+      </c>
+      <c r="V65" s="5">
+        <f>SUM(V3:V64)</f>
+        <v/>
+      </c>
+      <c r="W65" s="5">
+        <f>SUM(W3:W64)</f>
+        <v/>
+      </c>
+      <c r="X65" s="5">
+        <f>SUM(X3:X64)</f>
+        <v/>
+      </c>
+      <c r="Y65" s="5" t="n"/>
+      <c r="Z65" s="5">
+        <f>SUM(Z3:Z64)</f>
+        <v/>
+      </c>
+      <c r="AA65" s="5">
+        <f>SUM(AA3:AA64)</f>
+        <v/>
+      </c>
+      <c r="AB65" s="5">
+        <f>SUM(AB3:AB64)</f>
+        <v/>
+      </c>
+      <c r="AC65" s="5">
+        <f>SUM(AC3:AC64)</f>
+        <v/>
+      </c>
+      <c r="AD65" s="5">
+        <f>SUM(AD3:AD64)</f>
+        <v/>
+      </c>
+      <c r="AE65" s="5">
+        <f>SUM(AE3:AE64)</f>
+        <v/>
+      </c>
+      <c r="AF65" s="5">
+        <f>SUM(AF3:AF64)</f>
+        <v/>
+      </c>
+      <c r="AG65" s="5">
+        <f>SUM(AG3:AG64)</f>
+        <v/>
+      </c>
+      <c r="AH65" s="5">
+        <f>SUM(AH3:AH64)</f>
+        <v/>
+      </c>
+      <c r="AI65" s="5">
+        <f>SUM(AI3:AI64)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI12"/>
+  <autoFilter ref="A2:AI64"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AI1"/>
   </mergeCells>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -730,22 +730,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800757</t>
+          <t>HASLS22260700891</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
+          <t>202609230900</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -756,42 +756,43 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.18/09/26 CLS TIME CFS DD.21/09/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="O3" s="4" t="n">
@@ -801,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R3" s="4" t="n">
         <v>0</v>
@@ -871,12 +872,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801208</t>
+          <t>HASLS22260700894</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -886,7 +887,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
+          <t>202609211300</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -897,42 +898,42 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.18/09/26 CLS TIME CFS DD.18/09/26 - 17:00HRS.</t>
         </is>
       </c>
       <c r="O4" s="4" t="n">
@@ -942,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" s="4" t="n">
         <v>0</v>
@@ -1012,22 +1013,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801228</t>
+          <t>HASLS22260800693</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
+          <t>202609230900</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -1038,27 +1039,27 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1068,12 +1069,12 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL - GOOD &amp; CLEAN CON</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-16, Return : 2026-09-17 CONSOL </t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
@@ -1083,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>0</v>
@@ -1153,25 +1154,25 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801441</t>
+          <t>HASLS22260800757</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1184,7 +1185,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -1194,12 +1195,12 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1218,13 +1219,13 @@
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>0</v>
@@ -1294,248 +1295,3214 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>HASLS22260801208</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f>SUM(O7:W7)-X7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="4">
+        <f>MAX(0,O7-MAX(0,X7))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="4">
+        <f>MAX(0,P7-MAX(0,X7-SUM(O7:O7)))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="4">
+        <f>MAX(0,Q7-MAX(0,X7-SUM(O7:P7)))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="4">
+        <f>MAX(0,R7-MAX(0,X7-SUM(O7:Q7)))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="4">
+        <f>MAX(0,S7-MAX(0,X7-SUM(O7:R7)))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="4">
+        <f>MAX(0,T7-MAX(0,X7-SUM(O7:S7)))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="4">
+        <f>MAX(0,U7-MAX(0,X7-SUM(O7:T7)))</f>
+        <v/>
+      </c>
+      <c r="AH7" s="4">
+        <f>MAX(0,V7-MAX(0,X7-SUM(O7:U7)))</f>
+        <v/>
+      </c>
+      <c r="AI7" s="4">
+        <f>MAX(0,W7-MAX(0,X7-SUM(O7:V7)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801209</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f>SUM(O8:W8)-X8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="4">
+        <f>MAX(0,O8-MAX(0,X8))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="4">
+        <f>MAX(0,P8-MAX(0,X8-SUM(O8:O8)))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="4">
+        <f>MAX(0,Q8-MAX(0,X8-SUM(O8:P8)))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="4">
+        <f>MAX(0,R8-MAX(0,X8-SUM(O8:Q8)))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="4">
+        <f>MAX(0,S8-MAX(0,X8-SUM(O8:R8)))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="4">
+        <f>MAX(0,T8-MAX(0,X8-SUM(O8:S8)))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="4">
+        <f>MAX(0,U8-MAX(0,X8-SUM(O8:T8)))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>MAX(0,V8-MAX(0,X8-SUM(O8:U8)))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="4">
+        <f>MAX(0,W8-MAX(0,X8-SUM(O8:V8)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801228</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f>SUM(O9:W9)-X9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>MAX(0,O9-MAX(0,X9))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>MAX(0,P9-MAX(0,X9-SUM(O9:O9)))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="4">
+        <f>MAX(0,Q9-MAX(0,X9-SUM(O9:P9)))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="4">
+        <f>MAX(0,R9-MAX(0,X9-SUM(O9:Q9)))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>MAX(0,S9-MAX(0,X9-SUM(O9:R9)))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
+        <f>MAX(0,T9-MAX(0,X9-SUM(O9:S9)))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="4">
+        <f>MAX(0,U9-MAX(0,X9-SUM(O9:T9)))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>MAX(0,V9-MAX(0,X9-SUM(O9:U9)))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="4">
+        <f>MAX(0,W9-MAX(0,X9-SUM(O9:V9)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801229</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-18, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f>SUM(O10:W10)-X10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="4">
+        <f>MAX(0,O10-MAX(0,X10))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="4">
+        <f>MAX(0,P10-MAX(0,X10-SUM(O10:O10)))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="4">
+        <f>MAX(0,Q10-MAX(0,X10-SUM(O10:P10)))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="4">
+        <f>MAX(0,R10-MAX(0,X10-SUM(O10:Q10)))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="4">
+        <f>MAX(0,S10-MAX(0,X10-SUM(O10:R10)))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="4">
+        <f>MAX(0,T10-MAX(0,X10-SUM(O10:S10)))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="4">
+        <f>MAX(0,U10-MAX(0,X10-SUM(O10:T10)))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>MAX(0,V10-MAX(0,X10-SUM(O10:U10)))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="4">
+        <f>MAX(0,W10-MAX(0,X10-SUM(O10:V10)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801441</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f>SUM(O11:W11)-X11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="4">
+        <f>MAX(0,O11-MAX(0,X11))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="4">
+        <f>MAX(0,P11-MAX(0,X11-SUM(O11:O11)))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="4">
+        <f>MAX(0,Q11-MAX(0,X11-SUM(O11:P11)))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="4">
+        <f>MAX(0,R11-MAX(0,X11-SUM(O11:Q11)))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="4">
+        <f>MAX(0,S11-MAX(0,X11-SUM(O11:R11)))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="4">
+        <f>MAX(0,T11-MAX(0,X11-SUM(O11:S11)))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="4">
+        <f>MAX(0,U11-MAX(0,X11-SUM(O11:T11)))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="4">
+        <f>MAX(0,V11-MAX(0,X11-SUM(O11:U11)))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="4">
+        <f>MAX(0,W11-MAX(0,X11-SUM(O11:V11)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801442</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL *EXTEND CLS TIME : 18/09/2026 @20.00*</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f>SUM(O12:W12)-X12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="4">
+        <f>MAX(0,O12-MAX(0,X12))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4">
+        <f>MAX(0,P12-MAX(0,X12-SUM(O12:O12)))</f>
+        <v/>
+      </c>
+      <c r="AC12" s="4">
+        <f>MAX(0,Q12-MAX(0,X12-SUM(O12:P12)))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="4">
+        <f>MAX(0,R12-MAX(0,X12-SUM(O12:Q12)))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="4">
+        <f>MAX(0,S12-MAX(0,X12-SUM(O12:R12)))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="4">
+        <f>MAX(0,T12-MAX(0,X12-SUM(O12:S12)))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="4">
+        <f>MAX(0,U12-MAX(0,X12-SUM(O12:T12)))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>MAX(0,V12-MAX(0,X12-SUM(O12:U12)))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="4">
+        <f>MAX(0,W12-MAX(0,X12-SUM(O12:V12)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801482</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>202609181130</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>OASIS LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>KAEN CHAROEN CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAPIOCA STARCH </t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/09/26 CLS TIME CFS DD.15/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f>SUM(O13:W13)-X13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="4">
+        <f>MAX(0,O13-MAX(0,X13))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4">
+        <f>MAX(0,P13-MAX(0,X13-SUM(O13:O13)))</f>
+        <v/>
+      </c>
+      <c r="AC13" s="4">
+        <f>MAX(0,Q13-MAX(0,X13-SUM(O13:P13)))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="4">
+        <f>MAX(0,R13-MAX(0,X13-SUM(O13:Q13)))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="4">
+        <f>MAX(0,S13-MAX(0,X13-SUM(O13:R13)))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="4">
+        <f>MAX(0,T13-MAX(0,X13-SUM(O13:S13)))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="4">
+        <f>MAX(0,U13-MAX(0,X13-SUM(O13:T13)))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="4">
+        <f>MAX(0,V13-MAX(0,X13-SUM(O13:U13)))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="4">
+        <f>MAX(0,W13-MAX(0,X13-SUM(O13:V13)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>HASLS22260801996</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>202609271700</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
 [1ST CY DATE : 17/09/2026 W/O RENT]</t>
         </is>
       </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <f>SUM(O7:W7)-X7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="4">
-        <f>MAX(0,O7-MAX(0,X7))</f>
-        <v/>
-      </c>
-      <c r="AB7" s="4">
-        <f>MAX(0,P7-MAX(0,X7-SUM(O7:O7)))</f>
-        <v/>
-      </c>
-      <c r="AC7" s="4">
-        <f>MAX(0,Q7-MAX(0,X7-SUM(O7:P7)))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="4">
-        <f>MAX(0,R7-MAX(0,X7-SUM(O7:Q7)))</f>
-        <v/>
-      </c>
-      <c r="AE7" s="4">
-        <f>MAX(0,S7-MAX(0,X7-SUM(O7:R7)))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="4">
-        <f>MAX(0,T7-MAX(0,X7-SUM(O7:S7)))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="4">
-        <f>MAX(0,U7-MAX(0,X7-SUM(O7:T7)))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="4">
-        <f>MAX(0,V7-MAX(0,X7-SUM(O7:U7)))</f>
-        <v/>
-      </c>
-      <c r="AI7" s="4">
-        <f>MAX(0,W7-MAX(0,X7-SUM(O7:V7)))</f>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <f>SUM(O14:W14)-X14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="4">
+        <f>MAX(0,O14-MAX(0,X14))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4">
+        <f>MAX(0,P14-MAX(0,X14-SUM(O14:O14)))</f>
+        <v/>
+      </c>
+      <c r="AC14" s="4">
+        <f>MAX(0,Q14-MAX(0,X14-SUM(O14:P14)))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="4">
+        <f>MAX(0,R14-MAX(0,X14-SUM(O14:Q14)))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="4">
+        <f>MAX(0,S14-MAX(0,X14-SUM(O14:R14)))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="4">
+        <f>MAX(0,T14-MAX(0,X14-SUM(O14:S14)))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="4">
+        <f>MAX(0,U14-MAX(0,X14-SUM(O14:T14)))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="4">
+        <f>MAX(0,V14-MAX(0,X14-SUM(O14:U14)))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="4">
+        <f>MAX(0,W14-MAX(0,X14-SUM(O14:V14)))</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802179</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>202609240800</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <f>SUM(O15:W15)-X15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="4">
+        <f>MAX(0,O15-MAX(0,X15))</f>
+        <v/>
+      </c>
+      <c r="AB15" s="4">
+        <f>MAX(0,P15-MAX(0,X15-SUM(O15:O15)))</f>
+        <v/>
+      </c>
+      <c r="AC15" s="4">
+        <f>MAX(0,Q15-MAX(0,X15-SUM(O15:P15)))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="4">
+        <f>MAX(0,R15-MAX(0,X15-SUM(O15:Q15)))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="4">
+        <f>MAX(0,S15-MAX(0,X15-SUM(O15:R15)))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="4">
+        <f>MAX(0,T15-MAX(0,X15-SUM(O15:S15)))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="4">
+        <f>MAX(0,U15-MAX(0,X15-SUM(O15:T15)))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="4">
+        <f>MAX(0,V15-MAX(0,X15-SUM(O15:U15)))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="4">
+        <f>MAX(0,W15-MAX(0,X15-SUM(O15:V15)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802251</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>V.C.E. COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>TAPIOCA FLOUR</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.16/09/26 *CLS TIME CFS DD.16/09/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <f>SUM(O16:W16)-X16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="4">
+        <f>MAX(0,O16-MAX(0,X16))</f>
+        <v/>
+      </c>
+      <c r="AB16" s="4">
+        <f>MAX(0,P16-MAX(0,X16-SUM(O16:O16)))</f>
+        <v/>
+      </c>
+      <c r="AC16" s="4">
+        <f>MAX(0,Q16-MAX(0,X16-SUM(O16:P16)))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="4">
+        <f>MAX(0,R16-MAX(0,X16-SUM(O16:Q16)))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="4">
+        <f>MAX(0,S16-MAX(0,X16-SUM(O16:R16)))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="4">
+        <f>MAX(0,T16-MAX(0,X16-SUM(O16:S16)))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="4">
+        <f>MAX(0,U16-MAX(0,X16-SUM(O16:T16)))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="4">
+        <f>MAX(0,V16-MAX(0,X16-SUM(O16:U16)))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="4">
+        <f>MAX(0,W16-MAX(0,X16-SUM(O16:V16)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802382</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="4">
+        <f>SUM(O17:W17)-X17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="4">
+        <f>MAX(0,O17-MAX(0,X17))</f>
+        <v/>
+      </c>
+      <c r="AB17" s="4">
+        <f>MAX(0,P17-MAX(0,X17-SUM(O17:O17)))</f>
+        <v/>
+      </c>
+      <c r="AC17" s="4">
+        <f>MAX(0,Q17-MAX(0,X17-SUM(O17:P17)))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="4">
+        <f>MAX(0,R17-MAX(0,X17-SUM(O17:Q17)))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="4">
+        <f>MAX(0,S17-MAX(0,X17-SUM(O17:R17)))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="4">
+        <f>MAX(0,T17-MAX(0,X17-SUM(O17:S17)))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="4">
+        <f>MAX(0,U17-MAX(0,X17-SUM(O17:T17)))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="4">
+        <f>MAX(0,V17-MAX(0,X17-SUM(O17:U17)))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="4">
+        <f>MAX(0,W17-MAX(0,X17-SUM(O17:V17)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802476</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x12 </t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>CAPRICORN LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>REQUEST CONTAINER GOOD GRADE
+REQUEST CONTAINER UPGRADE 32.5 TONS</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.18/09/26 CLS TIME CFS DD.21/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="4">
+        <f>SUM(O18:W18)-X18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="4">
+        <f>MAX(0,O18-MAX(0,X18))</f>
+        <v/>
+      </c>
+      <c r="AB18" s="4">
+        <f>MAX(0,P18-MAX(0,X18-SUM(O18:O18)))</f>
+        <v/>
+      </c>
+      <c r="AC18" s="4">
+        <f>MAX(0,Q18-MAX(0,X18-SUM(O18:P18)))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="4">
+        <f>MAX(0,R18-MAX(0,X18-SUM(O18:Q18)))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="4">
+        <f>MAX(0,S18-MAX(0,X18-SUM(O18:R18)))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="4">
+        <f>MAX(0,T18-MAX(0,X18-SUM(O18:S18)))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="4">
+        <f>MAX(0,U18-MAX(0,X18-SUM(O18:T18)))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="4">
+        <f>MAX(0,V18-MAX(0,X18-SUM(O18:U18)))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="4">
+        <f>MAX(0,W18-MAX(0,X18-SUM(O18:V18)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802541</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="4">
+        <f>SUM(O19:W19)-X19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="4">
+        <f>MAX(0,O19-MAX(0,X19))</f>
+        <v/>
+      </c>
+      <c r="AB19" s="4">
+        <f>MAX(0,P19-MAX(0,X19-SUM(O19:O19)))</f>
+        <v/>
+      </c>
+      <c r="AC19" s="4">
+        <f>MAX(0,Q19-MAX(0,X19-SUM(O19:P19)))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="4">
+        <f>MAX(0,R19-MAX(0,X19-SUM(O19:Q19)))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="4">
+        <f>MAX(0,S19-MAX(0,X19-SUM(O19:R19)))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="4">
+        <f>MAX(0,T19-MAX(0,X19-SUM(O19:S19)))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="4">
+        <f>MAX(0,U19-MAX(0,X19-SUM(O19:T19)))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="4">
+        <f>MAX(0,V19-MAX(0,X19-SUM(O19:U19)))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="4">
+        <f>MAX(0,W19-MAX(0,X19-SUM(O19:V19)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802559</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-16, Return : 2026-09-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="4">
+        <f>SUM(O20:W20)-X20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="4">
+        <f>MAX(0,O20-MAX(0,X20))</f>
+        <v/>
+      </c>
+      <c r="AB20" s="4">
+        <f>MAX(0,P20-MAX(0,X20-SUM(O20:O20)))</f>
+        <v/>
+      </c>
+      <c r="AC20" s="4">
+        <f>MAX(0,Q20-MAX(0,X20-SUM(O20:P20)))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="4">
+        <f>MAX(0,R20-MAX(0,X20-SUM(O20:Q20)))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="4">
+        <f>MAX(0,S20-MAX(0,X20-SUM(O20:R20)))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="4">
+        <f>MAX(0,T20-MAX(0,X20-SUM(O20:S20)))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="4">
+        <f>MAX(0,U20-MAX(0,X20-SUM(O20:T20)))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>MAX(0,V20-MAX(0,X20-SUM(O20:U20)))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="4">
+        <f>MAX(0,W20-MAX(0,X20-SUM(O20:V20)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802588</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="4">
+        <f>SUM(O21:W21)-X21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="4">
+        <f>MAX(0,O21-MAX(0,X21))</f>
+        <v/>
+      </c>
+      <c r="AB21" s="4">
+        <f>MAX(0,P21-MAX(0,X21-SUM(O21:O21)))</f>
+        <v/>
+      </c>
+      <c r="AC21" s="4">
+        <f>MAX(0,Q21-MAX(0,X21-SUM(O21:P21)))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="4">
+        <f>MAX(0,R21-MAX(0,X21-SUM(O21:Q21)))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="4">
+        <f>MAX(0,S21-MAX(0,X21-SUM(O21:R21)))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="4">
+        <f>MAX(0,T21-MAX(0,X21-SUM(O21:S21)))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="4">
+        <f>MAX(0,U21-MAX(0,X21-SUM(O21:T21)))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>MAX(0,V21-MAX(0,X21-SUM(O21:U21)))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="4">
+        <f>MAX(0,W21-MAX(0,X21-SUM(O21:V21)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260802589</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 16-17/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="4">
+        <f>SUM(O22:W22)-X22</f>
+        <v/>
+      </c>
+      <c r="AA22" s="4">
+        <f>MAX(0,O22-MAX(0,X22))</f>
+        <v/>
+      </c>
+      <c r="AB22" s="4">
+        <f>MAX(0,P22-MAX(0,X22-SUM(O22:O22)))</f>
+        <v/>
+      </c>
+      <c r="AC22" s="4">
+        <f>MAX(0,Q22-MAX(0,X22-SUM(O22:P22)))</f>
+        <v/>
+      </c>
+      <c r="AD22" s="4">
+        <f>MAX(0,R22-MAX(0,X22-SUM(O22:Q22)))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="4">
+        <f>MAX(0,S22-MAX(0,X22-SUM(O22:R22)))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="4">
+        <f>MAX(0,T22-MAX(0,X22-SUM(O22:S22)))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="4">
+        <f>MAX(0,U22-MAX(0,X22-SUM(O22:T22)))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="4">
+        <f>MAX(0,V22-MAX(0,X22-SUM(O22:U22)))</f>
+        <v/>
+      </c>
+      <c r="AI22" s="4">
+        <f>MAX(0,W22-MAX(0,X22-SUM(O22:V22)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900162</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18  CONSOL </t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="4">
+        <f>SUM(O23:W23)-X23</f>
+        <v/>
+      </c>
+      <c r="AA23" s="4">
+        <f>MAX(0,O23-MAX(0,X23))</f>
+        <v/>
+      </c>
+      <c r="AB23" s="4">
+        <f>MAX(0,P23-MAX(0,X23-SUM(O23:O23)))</f>
+        <v/>
+      </c>
+      <c r="AC23" s="4">
+        <f>MAX(0,Q23-MAX(0,X23-SUM(O23:P23)))</f>
+        <v/>
+      </c>
+      <c r="AD23" s="4">
+        <f>MAX(0,R23-MAX(0,X23-SUM(O23:Q23)))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="4">
+        <f>MAX(0,S23-MAX(0,X23-SUM(O23:R23)))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="4">
+        <f>MAX(0,T23-MAX(0,X23-SUM(O23:S23)))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="4">
+        <f>MAX(0,U23-MAX(0,X23-SUM(O23:T23)))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="4">
+        <f>MAX(0,V23-MAX(0,X23-SUM(O23:U23)))</f>
+        <v/>
+      </c>
+      <c r="AI23" s="4">
+        <f>MAX(0,W23-MAX(0,X23-SUM(O23:V23)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900186</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="4">
+        <f>SUM(O24:W24)-X24</f>
+        <v/>
+      </c>
+      <c r="AA24" s="4">
+        <f>MAX(0,O24-MAX(0,X24))</f>
+        <v/>
+      </c>
+      <c r="AB24" s="4">
+        <f>MAX(0,P24-MAX(0,X24-SUM(O24:O24)))</f>
+        <v/>
+      </c>
+      <c r="AC24" s="4">
+        <f>MAX(0,Q24-MAX(0,X24-SUM(O24:P24)))</f>
+        <v/>
+      </c>
+      <c r="AD24" s="4">
+        <f>MAX(0,R24-MAX(0,X24-SUM(O24:Q24)))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="4">
+        <f>MAX(0,S24-MAX(0,X24-SUM(O24:R24)))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="4">
+        <f>MAX(0,T24-MAX(0,X24-SUM(O24:S24)))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="4">
+        <f>MAX(0,U24-MAX(0,X24-SUM(O24:T24)))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="4">
+        <f>MAX(0,V24-MAX(0,X24-SUM(O24:U24)))</f>
+        <v/>
+      </c>
+      <c r="AI24" s="4">
+        <f>MAX(0,W24-MAX(0,X24-SUM(O24:V24)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900187</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="4">
+        <f>SUM(O25:W25)-X25</f>
+        <v/>
+      </c>
+      <c r="AA25" s="4">
+        <f>MAX(0,O25-MAX(0,X25))</f>
+        <v/>
+      </c>
+      <c r="AB25" s="4">
+        <f>MAX(0,P25-MAX(0,X25-SUM(O25:O25)))</f>
+        <v/>
+      </c>
+      <c r="AC25" s="4">
+        <f>MAX(0,Q25-MAX(0,X25-SUM(O25:P25)))</f>
+        <v/>
+      </c>
+      <c r="AD25" s="4">
+        <f>MAX(0,R25-MAX(0,X25-SUM(O25:Q25)))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="4">
+        <f>MAX(0,S25-MAX(0,X25-SUM(O25:R25)))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="4">
+        <f>MAX(0,T25-MAX(0,X25-SUM(O25:S25)))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="4">
+        <f>MAX(0,U25-MAX(0,X25-SUM(O25:T25)))</f>
+        <v/>
+      </c>
+      <c r="AH25" s="4">
+        <f>MAX(0,V25-MAX(0,X25-SUM(O25:U25)))</f>
+        <v/>
+      </c>
+      <c r="AI25" s="4">
+        <f>MAX(0,W25-MAX(0,X25-SUM(O25:V25)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900309</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-15, Return : 2026-09-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="4">
+        <f>SUM(O26:W26)-X26</f>
+        <v/>
+      </c>
+      <c r="AA26" s="4">
+        <f>MAX(0,O26-MAX(0,X26))</f>
+        <v/>
+      </c>
+      <c r="AB26" s="4">
+        <f>MAX(0,P26-MAX(0,X26-SUM(O26:O26)))</f>
+        <v/>
+      </c>
+      <c r="AC26" s="4">
+        <f>MAX(0,Q26-MAX(0,X26-SUM(O26:P26)))</f>
+        <v/>
+      </c>
+      <c r="AD26" s="4">
+        <f>MAX(0,R26-MAX(0,X26-SUM(O26:Q26)))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="4">
+        <f>MAX(0,S26-MAX(0,X26-SUM(O26:R26)))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="4">
+        <f>MAX(0,T26-MAX(0,X26-SUM(O26:S26)))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="4">
+        <f>MAX(0,U26-MAX(0,X26-SUM(O26:T26)))</f>
+        <v/>
+      </c>
+      <c r="AH26" s="4">
+        <f>MAX(0,V26-MAX(0,X26-SUM(O26:U26)))</f>
+        <v/>
+      </c>
+      <c r="AI26" s="4">
+        <f>MAX(0,W26-MAX(0,X26-SUM(O26:V26)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900717</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>ELC CONTAINER LINES CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>CONTAINER GRADE A</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 18/09/26 CLS TIME 21/09 @17.00HRS 
+ (1ST CFS : 18/09 W/O RENT) </t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="4">
+        <f>SUM(O27:W27)-X27</f>
+        <v/>
+      </c>
+      <c r="AA27" s="4">
+        <f>MAX(0,O27-MAX(0,X27))</f>
+        <v/>
+      </c>
+      <c r="AB27" s="4">
+        <f>MAX(0,P27-MAX(0,X27-SUM(O27:O27)))</f>
+        <v/>
+      </c>
+      <c r="AC27" s="4">
+        <f>MAX(0,Q27-MAX(0,X27-SUM(O27:P27)))</f>
+        <v/>
+      </c>
+      <c r="AD27" s="4">
+        <f>MAX(0,R27-MAX(0,X27-SUM(O27:Q27)))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="4">
+        <f>MAX(0,S27-MAX(0,X27-SUM(O27:R27)))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="4">
+        <f>MAX(0,T27-MAX(0,X27-SUM(O27:S27)))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="4">
+        <f>MAX(0,U27-MAX(0,X27-SUM(O27:T27)))</f>
+        <v/>
+      </c>
+      <c r="AH27" s="4">
+        <f>MAX(0,V27-MAX(0,X27-SUM(O27:U27)))</f>
+        <v/>
+      </c>
+      <c r="AI27" s="4">
+        <f>MAX(0,W27-MAX(0,X27-SUM(O27:V27)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900803</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>SEA 2 SKY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>BANYAN TREE GALLERY (THAILAND) COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>HOTEL ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Requested Good &amp; Clean contr</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/09/26 CLS TIME CFS DD.18/09/26 - 17:00HRS.
+(1ST RTN DD: 17/09/26 WO/RENT)</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="4">
+        <f>SUM(O28:W28)-X28</f>
+        <v/>
+      </c>
+      <c r="AA28" s="4">
+        <f>MAX(0,O28-MAX(0,X28))</f>
+        <v/>
+      </c>
+      <c r="AB28" s="4">
+        <f>MAX(0,P28-MAX(0,X28-SUM(O28:O28)))</f>
+        <v/>
+      </c>
+      <c r="AC28" s="4">
+        <f>MAX(0,Q28-MAX(0,X28-SUM(O28:P28)))</f>
+        <v/>
+      </c>
+      <c r="AD28" s="4">
+        <f>MAX(0,R28-MAX(0,X28-SUM(O28:Q28)))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="4">
+        <f>MAX(0,S28-MAX(0,X28-SUM(O28:R28)))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="4">
+        <f>MAX(0,T28-MAX(0,X28-SUM(O28:S28)))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="4">
+        <f>MAX(0,U28-MAX(0,X28-SUM(O28:T28)))</f>
+        <v/>
+      </c>
+      <c r="AH28" s="4">
+        <f>MAX(0,V28-MAX(0,X28-SUM(O28:U28)))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="4">
+        <f>MAX(0,W28-MAX(0,X28-SUM(O28:V28)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5">
-        <f>SUM(O3:O7)</f>
-        <v/>
-      </c>
-      <c r="P8" s="5">
-        <f>SUM(P3:P7)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="5">
-        <f>SUM(Q3:Q7)</f>
-        <v/>
-      </c>
-      <c r="R8" s="5">
-        <f>SUM(R3:R7)</f>
-        <v/>
-      </c>
-      <c r="S8" s="5">
-        <f>SUM(S3:S7)</f>
-        <v/>
-      </c>
-      <c r="T8" s="5">
-        <f>SUM(T3:T7)</f>
-        <v/>
-      </c>
-      <c r="U8" s="5">
-        <f>SUM(U3:U7)</f>
-        <v/>
-      </c>
-      <c r="V8" s="5">
-        <f>SUM(V3:V7)</f>
-        <v/>
-      </c>
-      <c r="W8" s="5">
-        <f>SUM(W3:W7)</f>
-        <v/>
-      </c>
-      <c r="X8" s="5">
-        <f>SUM(X3:X7)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="5">
-        <f>SUM(Z3:Z7)</f>
-        <v/>
-      </c>
-      <c r="AA8" s="5">
-        <f>SUM(AA3:AA7)</f>
-        <v/>
-      </c>
-      <c r="AB8" s="5">
-        <f>SUM(AB3:AB7)</f>
-        <v/>
-      </c>
-      <c r="AC8" s="5">
-        <f>SUM(AC3:AC7)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="5">
-        <f>SUM(AD3:AD7)</f>
-        <v/>
-      </c>
-      <c r="AE8" s="5">
-        <f>SUM(AE3:AE7)</f>
-        <v/>
-      </c>
-      <c r="AF8" s="5">
-        <f>SUM(AF3:AF7)</f>
-        <v/>
-      </c>
-      <c r="AG8" s="5">
-        <f>SUM(AG3:AG7)</f>
-        <v/>
-      </c>
-      <c r="AH8" s="5">
-        <f>SUM(AH3:AH7)</f>
-        <v/>
-      </c>
-      <c r="AI8" s="5">
-        <f>SUM(AI3:AI7)</f>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5">
+        <f>SUM(O3:O28)</f>
+        <v/>
+      </c>
+      <c r="P29" s="5">
+        <f>SUM(P3:P28)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="5">
+        <f>SUM(Q3:Q28)</f>
+        <v/>
+      </c>
+      <c r="R29" s="5">
+        <f>SUM(R3:R28)</f>
+        <v/>
+      </c>
+      <c r="S29" s="5">
+        <f>SUM(S3:S28)</f>
+        <v/>
+      </c>
+      <c r="T29" s="5">
+        <f>SUM(T3:T28)</f>
+        <v/>
+      </c>
+      <c r="U29" s="5">
+        <f>SUM(U3:U28)</f>
+        <v/>
+      </c>
+      <c r="V29" s="5">
+        <f>SUM(V3:V28)</f>
+        <v/>
+      </c>
+      <c r="W29" s="5">
+        <f>SUM(W3:W28)</f>
+        <v/>
+      </c>
+      <c r="X29" s="5">
+        <f>SUM(X3:X28)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="5" t="n"/>
+      <c r="Z29" s="5">
+        <f>SUM(Z3:Z28)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="5">
+        <f>SUM(AA3:AA28)</f>
+        <v/>
+      </c>
+      <c r="AB29" s="5">
+        <f>SUM(AB3:AB28)</f>
+        <v/>
+      </c>
+      <c r="AC29" s="5">
+        <f>SUM(AC3:AC28)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>SUM(AD3:AD28)</f>
+        <v/>
+      </c>
+      <c r="AE29" s="5">
+        <f>SUM(AE3:AE28)</f>
+        <v/>
+      </c>
+      <c r="AF29" s="5">
+        <f>SUM(AF3:AF28)</f>
+        <v/>
+      </c>
+      <c r="AG29" s="5">
+        <f>SUM(AG3:AG28)</f>
+        <v/>
+      </c>
+      <c r="AH29" s="5">
+        <f>SUM(AH3:AH28)</f>
+        <v/>
+      </c>
+      <c r="AI29" s="5">
+        <f>SUM(AI3:AI28)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI7"/>
+  <autoFilter ref="A2:AI28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AI1"/>
   </mergeCells>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AH$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,16 +37,19 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +112,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -482,10 +491,10 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
@@ -496,8 +505,8 @@
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="15" customWidth="1" min="29" max="29"/>
@@ -506,10 +515,9 @@
     <col width="15" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
-    <col width="15" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BKG PENDING — PAT TERMINAL 1 &amp; 2 (PORT AUTHORITY OF THAILAND)   (BKK01+BKK04)</t>
@@ -548,9 +556,8 @@
       <c r="AF1" s="2" t="n"/>
       <c r="AG1" s="2" t="n"/>
       <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="13" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BK No</t>
@@ -598,136 +605,131 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>DOC CUST</t>
+          <t>ORG CUST</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>ORG CUST</t>
+          <t>COMMODITY</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>COMMODITY</t>
+          <t>TRAFFIC ORDER</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>TRAFFIC ORDER</t>
+          <t>COMMON REMARK</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>COMMON REMARK</t>
+          <t>GP22</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>GP22</t>
+          <t>GP42</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>GP42</t>
+          <t>GP45</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>GP45</t>
+          <t>RE22</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>RE22</t>
+          <t>RE45</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>RE45</t>
+          <t>UT22</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>UT22</t>
+          <t>UT42</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>UT42</t>
+          <t>PC22</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>PC22</t>
+          <t>PC42</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>PC42</t>
+          <t>Pickup</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>Pickup</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Balance (Booked - Pickup)</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>Balance (Booked - Pickup)</t>
+          <t>GP22 Remaining</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
-          <t>GP22 Remaining</t>
+          <t>GP42 Remaining</t>
         </is>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>GP42 Remaining</t>
+          <t>GP45 Remaining</t>
         </is>
       </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>GP45 Remaining</t>
+          <t>RE22 Remaining</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>RE22 Remaining</t>
+          <t>RE45 Remaining</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>RE45 Remaining</t>
+          <t>UT22 Remaining</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>UT22 Remaining</t>
+          <t>UT42 Remaining</t>
         </is>
       </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
-          <t>UT42 Remaining</t>
+          <t>PC22 Remaining</t>
         </is>
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>PC22 Remaining</t>
-        </is>
-      </c>
-      <c r="AI2" s="3" t="inlineStr">
-        <is>
           <t>PC42 Remaining</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="13" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>HASLS22260801208</t>
@@ -748,7 +750,7 @@
           <t>202609220800</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -776,412 +778,397 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <f>SUM(N3:V3)-W3</f>
+        <v/>
+      </c>
+      <c r="Z3" s="4">
+        <f>MAX(0,N3-MAX(0,W3))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="4">
+        <f>MAX(0,O3-MAX(0,W3-SUM(N3:N3)))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="4">
+        <f>MAX(0,P3-MAX(0,W3-SUM(N3:O3)))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="4">
+        <f>MAX(0,Q3-MAX(0,W3-SUM(N3:P3)))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="4">
+        <f>MAX(0,R3-MAX(0,W3-SUM(N3:Q3)))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="4">
+        <f>MAX(0,S3-MAX(0,W3-SUM(N3:R3)))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="4">
+        <f>MAX(0,T3-MAX(0,W3-SUM(N3:S3)))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="4">
+        <f>MAX(0,U3-MAX(0,W3-SUM(N3:T3)))</f>
+        <v/>
+      </c>
+      <c r="AH3" s="4">
+        <f>MAX(0,V3-MAX(0,W3-SUM(N3:U3)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801228</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4">
-        <f>SUM(O3:W3)-X3</f>
-        <v/>
-      </c>
-      <c r="AA3" s="4">
-        <f>MAX(0,O3-MAX(0,X3))</f>
-        <v/>
-      </c>
-      <c r="AB3" s="4">
-        <f>MAX(0,P3-MAX(0,X3-SUM(O3:O3)))</f>
-        <v/>
-      </c>
-      <c r="AC3" s="4">
-        <f>MAX(0,Q3-MAX(0,X3-SUM(O3:P3)))</f>
-        <v/>
-      </c>
-      <c r="AD3" s="4">
-        <f>MAX(0,R3-MAX(0,X3-SUM(O3:Q3)))</f>
-        <v/>
-      </c>
-      <c r="AE3" s="4">
-        <f>MAX(0,S3-MAX(0,X3-SUM(O3:R3)))</f>
-        <v/>
-      </c>
-      <c r="AF3" s="4">
-        <f>MAX(0,T3-MAX(0,X3-SUM(O3:S3)))</f>
-        <v/>
-      </c>
-      <c r="AG3" s="4">
-        <f>MAX(0,U3-MAX(0,X3-SUM(O3:T3)))</f>
-        <v/>
-      </c>
-      <c r="AH3" s="4">
-        <f>MAX(0,V3-MAX(0,X3-SUM(O3:U3)))</f>
-        <v/>
-      </c>
-      <c r="AI3" s="4">
-        <f>MAX(0,W3-MAX(0,X3-SUM(O3:V3)))</f>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <f>SUM(N4:V4)-W4</f>
+        <v/>
+      </c>
+      <c r="Z4" s="4">
+        <f>MAX(0,N4-MAX(0,W4))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="4">
+        <f>MAX(0,O4-MAX(0,W4-SUM(N4:N4)))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="4">
+        <f>MAX(0,P4-MAX(0,W4-SUM(N4:O4)))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="4">
+        <f>MAX(0,Q4-MAX(0,W4-SUM(N4:P4)))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="4">
+        <f>MAX(0,R4-MAX(0,W4-SUM(N4:Q4)))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="4">
+        <f>MAX(0,S4-MAX(0,W4-SUM(N4:R4)))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="4">
+        <f>MAX(0,T4-MAX(0,W4-SUM(N4:S4)))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="4">
+        <f>MAX(0,U4-MAX(0,W4-SUM(N4:T4)))</f>
+        <v/>
+      </c>
+      <c r="AH4" s="4">
+        <f>MAX(0,V4-MAX(0,W4-SUM(N4:U4)))</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260801228</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801441</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
+        <f>SUM(N5:V5)-W5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="4">
+        <f>MAX(0,N5-MAX(0,W5))</f>
+        <v/>
+      </c>
+      <c r="AA5" s="4">
+        <f>MAX(0,O5-MAX(0,W5-SUM(N5:N5)))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="4">
+        <f>MAX(0,P5-MAX(0,W5-SUM(N5:O5)))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="4">
+        <f>MAX(0,Q5-MAX(0,W5-SUM(N5:P5)))</f>
+        <v/>
+      </c>
+      <c r="AD5" s="4">
+        <f>MAX(0,R5-MAX(0,W5-SUM(N5:Q5)))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="4">
+        <f>MAX(0,S5-MAX(0,W5-SUM(N5:R5)))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="4">
+        <f>MAX(0,T5-MAX(0,W5-SUM(N5:S5)))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="4">
+        <f>MAX(0,U5-MAX(0,W5-SUM(N5:T5)))</f>
+        <v/>
+      </c>
+      <c r="AH5" s="4">
+        <f>MAX(0,V5-MAX(0,W5-SUM(N5:U5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801482</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <f>SUM(O4:W4)-X4</f>
-        <v/>
-      </c>
-      <c r="AA4" s="4">
-        <f>MAX(0,O4-MAX(0,X4))</f>
-        <v/>
-      </c>
-      <c r="AB4" s="4">
-        <f>MAX(0,P4-MAX(0,X4-SUM(O4:O4)))</f>
-        <v/>
-      </c>
-      <c r="AC4" s="4">
-        <f>MAX(0,Q4-MAX(0,X4-SUM(O4:P4)))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="4">
-        <f>MAX(0,R4-MAX(0,X4-SUM(O4:Q4)))</f>
-        <v/>
-      </c>
-      <c r="AE4" s="4">
-        <f>MAX(0,S4-MAX(0,X4-SUM(O4:R4)))</f>
-        <v/>
-      </c>
-      <c r="AF4" s="4">
-        <f>MAX(0,T4-MAX(0,X4-SUM(O4:S4)))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="4">
-        <f>MAX(0,U4-MAX(0,X4-SUM(O4:T4)))</f>
-        <v/>
-      </c>
-      <c r="AH4" s="4">
-        <f>MAX(0,V4-MAX(0,X4-SUM(O4:U4)))</f>
-        <v/>
-      </c>
-      <c r="AI4" s="4">
-        <f>MAX(0,W4-MAX(0,X4-SUM(O4:V4)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260801441</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>20260910</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4">
-        <f>SUM(O5:W5)-X5</f>
-        <v/>
-      </c>
-      <c r="AA5" s="4">
-        <f>MAX(0,O5-MAX(0,X5))</f>
-        <v/>
-      </c>
-      <c r="AB5" s="4">
-        <f>MAX(0,P5-MAX(0,X5-SUM(O5:O5)))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="4">
-        <f>MAX(0,Q5-MAX(0,X5-SUM(O5:P5)))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="4">
-        <f>MAX(0,R5-MAX(0,X5-SUM(O5:Q5)))</f>
-        <v/>
-      </c>
-      <c r="AE5" s="4">
-        <f>MAX(0,S5-MAX(0,X5-SUM(O5:R5)))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="4">
-        <f>MAX(0,T5-MAX(0,X5-SUM(O5:S5)))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="4">
-        <f>MAX(0,U5-MAX(0,X5-SUM(O5:T5)))</f>
-        <v/>
-      </c>
-      <c r="AH5" s="4">
-        <f>MAX(0,V5-MAX(0,X5-SUM(O5:U5)))</f>
-        <v/>
-      </c>
-      <c r="AI5" s="4">
-        <f>MAX(0,W5-MAX(0,X5-SUM(O5:V5)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260801482</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x3 </t>
@@ -1194,32 +1181,30 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>OASIS LOGISTICS CO., LTD.</t>
+          <t>KAEN CHAROEN CO.,LTD.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>KAEN CHAROEN CO.,LTD.</t>
+          <t xml:space="preserve">TAPIOCA STARCH </t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIOCA STARCH </t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/09/26 CLS TIME CFS DD.15/09/26 - 17:00HRS.
 </t>
         </is>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O6" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
@@ -1248,51 +1233,48 @@
       <c r="X6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" s="4" t="n">
-        <v>0</v>
+      <c r="Y6" s="4">
+        <f>SUM(N6:V6)-W6</f>
+        <v/>
       </c>
       <c r="Z6" s="4">
-        <f>SUM(O6:W6)-X6</f>
+        <f>MAX(0,N6-MAX(0,W6))</f>
         <v/>
       </c>
       <c r="AA6" s="4">
-        <f>MAX(0,O6-MAX(0,X6))</f>
+        <f>MAX(0,O6-MAX(0,W6-SUM(N6:N6)))</f>
         <v/>
       </c>
       <c r="AB6" s="4">
-        <f>MAX(0,P6-MAX(0,X6-SUM(O6:O6)))</f>
+        <f>MAX(0,P6-MAX(0,W6-SUM(N6:O6)))</f>
         <v/>
       </c>
       <c r="AC6" s="4">
-        <f>MAX(0,Q6-MAX(0,X6-SUM(O6:P6)))</f>
+        <f>MAX(0,Q6-MAX(0,W6-SUM(N6:P6)))</f>
         <v/>
       </c>
       <c r="AD6" s="4">
-        <f>MAX(0,R6-MAX(0,X6-SUM(O6:Q6)))</f>
+        <f>MAX(0,R6-MAX(0,W6-SUM(N6:Q6)))</f>
         <v/>
       </c>
       <c r="AE6" s="4">
-        <f>MAX(0,S6-MAX(0,X6-SUM(O6:R6)))</f>
+        <f>MAX(0,S6-MAX(0,W6-SUM(N6:R6)))</f>
         <v/>
       </c>
       <c r="AF6" s="4">
-        <f>MAX(0,T6-MAX(0,X6-SUM(O6:S6)))</f>
+        <f>MAX(0,T6-MAX(0,W6-SUM(N6:S6)))</f>
         <v/>
       </c>
       <c r="AG6" s="4">
-        <f>MAX(0,U6-MAX(0,X6-SUM(O6:T6)))</f>
+        <f>MAX(0,U6-MAX(0,W6-SUM(N6:T6)))</f>
         <v/>
       </c>
       <c r="AH6" s="4">
-        <f>MAX(0,V6-MAX(0,X6-SUM(O6:U6)))</f>
-        <v/>
-      </c>
-      <c r="AI6" s="4">
-        <f>MAX(0,W6-MAX(0,X6-SUM(O6:V6)))</f>
+        <f>MAX(0,V6-MAX(0,W6-SUM(N6:U6)))</f>
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="13" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>HASLS22260801996</t>
@@ -1313,7 +1295,7 @@
           <t>202609271700</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1341,382 +1323,367 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
 [1ST CY DATE : 17/09/2026 W/O RENT]</t>
         </is>
       </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>SUM(N7:V7)-W7</f>
+        <v/>
+      </c>
+      <c r="Z7" s="4">
+        <f>MAX(0,N7-MAX(0,W7))</f>
+        <v/>
+      </c>
+      <c r="AA7" s="4">
+        <f>MAX(0,O7-MAX(0,W7-SUM(N7:N7)))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="4">
+        <f>MAX(0,P7-MAX(0,W7-SUM(N7:O7)))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="4">
+        <f>MAX(0,Q7-MAX(0,W7-SUM(N7:P7)))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="4">
+        <f>MAX(0,R7-MAX(0,W7-SUM(N7:Q7)))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="4">
+        <f>MAX(0,S7-MAX(0,W7-SUM(N7:R7)))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="4">
+        <f>MAX(0,T7-MAX(0,W7-SUM(N7:S7)))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="4">
+        <f>MAX(0,U7-MAX(0,W7-SUM(N7:T7)))</f>
+        <v/>
+      </c>
+      <c r="AH7" s="4">
+        <f>MAX(0,V7-MAX(0,W7-SUM(N7:U7)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900186</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <f>SUM(O7:W7)-X7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="4">
-        <f>MAX(0,O7-MAX(0,X7))</f>
-        <v/>
-      </c>
-      <c r="AB7" s="4">
-        <f>MAX(0,P7-MAX(0,X7-SUM(O7:O7)))</f>
-        <v/>
-      </c>
-      <c r="AC7" s="4">
-        <f>MAX(0,Q7-MAX(0,X7-SUM(O7:P7)))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="4">
-        <f>MAX(0,R7-MAX(0,X7-SUM(O7:Q7)))</f>
-        <v/>
-      </c>
-      <c r="AE7" s="4">
-        <f>MAX(0,S7-MAX(0,X7-SUM(O7:R7)))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="4">
-        <f>MAX(0,T7-MAX(0,X7-SUM(O7:S7)))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="4">
-        <f>MAX(0,U7-MAX(0,X7-SUM(O7:T7)))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="4">
-        <f>MAX(0,V7-MAX(0,X7-SUM(O7:U7)))</f>
-        <v/>
-      </c>
-      <c r="AI7" s="4">
-        <f>MAX(0,W7-MAX(0,X7-SUM(O7:V7)))</f>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <f>SUM(N8:V8)-W8</f>
+        <v/>
+      </c>
+      <c r="Z8" s="4">
+        <f>MAX(0,N8-MAX(0,W8))</f>
+        <v/>
+      </c>
+      <c r="AA8" s="4">
+        <f>MAX(0,O8-MAX(0,W8-SUM(N8:N8)))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="4">
+        <f>MAX(0,P8-MAX(0,W8-SUM(N8:O8)))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="4">
+        <f>MAX(0,Q8-MAX(0,W8-SUM(N8:P8)))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="4">
+        <f>MAX(0,R8-MAX(0,W8-SUM(N8:Q8)))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="4">
+        <f>MAX(0,S8-MAX(0,W8-SUM(N8:R8)))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="4">
+        <f>MAX(0,T8-MAX(0,W8-SUM(N8:S8)))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="4">
+        <f>MAX(0,U8-MAX(0,W8-SUM(N8:T8)))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>MAX(0,V8-MAX(0,W8-SUM(N8:U8)))</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900186</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900309</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>KMTP</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>202609200900</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>20260915</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>(CONSOL)</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4">
-        <f>SUM(O8:W8)-X8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="4">
-        <f>MAX(0,O8-MAX(0,X8))</f>
-        <v/>
-      </c>
-      <c r="AB8" s="4">
-        <f>MAX(0,P8-MAX(0,X8-SUM(O8:O8)))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="4">
-        <f>MAX(0,Q8-MAX(0,X8-SUM(O8:P8)))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="4">
-        <f>MAX(0,R8-MAX(0,X8-SUM(O8:Q8)))</f>
-        <v/>
-      </c>
-      <c r="AE8" s="4">
-        <f>MAX(0,S8-MAX(0,X8-SUM(O8:R8)))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="4">
-        <f>MAX(0,T8-MAX(0,X8-SUM(O8:S8)))</f>
-        <v/>
-      </c>
-      <c r="AG8" s="4">
-        <f>MAX(0,U8-MAX(0,X8-SUM(O8:T8)))</f>
-        <v/>
-      </c>
-      <c r="AH8" s="4">
-        <f>MAX(0,V8-MAX(0,X8-SUM(O8:U8)))</f>
-        <v/>
-      </c>
-      <c r="AI8" s="4">
-        <f>MAX(0,W8-MAX(0,X8-SUM(O8:V8)))</f>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-15, Return : 2026-09-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <f>SUM(N9:V9)-W9</f>
+        <v/>
+      </c>
+      <c r="Z9" s="4">
+        <f>MAX(0,N9-MAX(0,W9))</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>MAX(0,O9-MAX(0,W9-SUM(N9:N9)))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>MAX(0,P9-MAX(0,W9-SUM(N9:O9)))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="4">
+        <f>MAX(0,Q9-MAX(0,W9-SUM(N9:P9)))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="4">
+        <f>MAX(0,R9-MAX(0,W9-SUM(N9:Q9)))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>MAX(0,S9-MAX(0,W9-SUM(N9:R9)))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
+        <f>MAX(0,T9-MAX(0,W9-SUM(N9:S9)))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="4">
+        <f>MAX(0,U9-MAX(0,W9-SUM(N9:T9)))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>MAX(0,V9-MAX(0,W9-SUM(N9:U9)))</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900309</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-15, Return : 2026-09-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4">
-        <f>SUM(O9:W9)-X9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="4">
-        <f>MAX(0,O9-MAX(0,X9))</f>
-        <v/>
-      </c>
-      <c r="AB9" s="4">
-        <f>MAX(0,P9-MAX(0,X9-SUM(O9:O9)))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="4">
-        <f>MAX(0,Q9-MAX(0,X9-SUM(O9:P9)))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="4">
-        <f>MAX(0,R9-MAX(0,X9-SUM(O9:Q9)))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="4">
-        <f>MAX(0,S9-MAX(0,X9-SUM(O9:R9)))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="4">
-        <f>MAX(0,T9-MAX(0,X9-SUM(O9:S9)))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="4">
-        <f>MAX(0,U9-MAX(0,X9-SUM(O9:T9)))</f>
-        <v/>
-      </c>
-      <c r="AH9" s="4">
-        <f>MAX(0,V9-MAX(0,X9-SUM(O9:U9)))</f>
-        <v/>
-      </c>
-      <c r="AI9" s="4">
-        <f>MAX(0,W9-MAX(0,X9-SUM(O9:V9)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
+    <row r="10" ht="13" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -1734,7 +1701,10 @@
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
+      <c r="N10" s="5">
+        <f>SUM(N3:N9)</f>
+        <v/>
+      </c>
       <c r="O10" s="5">
         <f>SUM(O3:O9)</f>
         <v/>
@@ -1771,11 +1741,11 @@
         <f>SUM(W3:W9)</f>
         <v/>
       </c>
-      <c r="X10" s="5">
-        <f>SUM(X3:X9)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+      <c r="Y10" s="5">
+        <f>SUM(Y3:Y9)</f>
+        <v/>
+      </c>
       <c r="Z10" s="5">
         <f>SUM(Z3:Z9)</f>
         <v/>
@@ -1812,15 +1782,67 @@
         <f>SUM(AH3:AH9)</f>
         <v/>
       </c>
-      <c r="AI10" s="5">
-        <f>SUM(AI3:AI9)</f>
-        <v/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>สรุปยอดบุ๊คทั้งหมด</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI9"/>
+  <autoFilter ref="A2:AH9"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="A1:AH1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AH$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AH$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH16"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -747,10 +747,10 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
+          <t>202609222100</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="4" t="n">
         <v>0</v>
@@ -868,25 +868,25 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801228</t>
+          <t>HASLS22260801441</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
+          <t>202609222100</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -894,22 +894,22 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -924,11 +924,11 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-12 CONSOL</t>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>0</v>
@@ -1004,12 +1004,12 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801441</t>
+          <t>HASLS22260801996</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1019,10 +1019,10 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1060,11 +1060,12 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
+[1ST CY DATE : 17/09/2026 W/O RENT]</t>
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>0</v>
@@ -1140,25 +1141,25 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801482</t>
+          <t>HASLS22260802251</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1171,22 +1172,22 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>KAEN CHAROEN CO.,LTD.</t>
+          <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIOCA STARCH </t>
+          <t>TAPIOCA FLOUR</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1196,12 +1197,11 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/09/26 CLS TIME CFS DD.15/09/26 - 17:00HRS.
-</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.16/09/26 *CLS TIME CFS DD.16/09/26 - 17:00HRS.* </t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>0</v>
@@ -1277,25 +1277,25 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801996</t>
+          <t>HASLS22260802589</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609271700</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1333,8 +1333,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
-[1ST CY DATE : 17/09/2026 W/O RENT]</t>
+          <t xml:space="preserve">CY-RTN : 16-17/09/2026 (CONSOL) *EXTEND CLS TIME : 22/09/2026 @17.00* </t>
         </is>
       </c>
       <c r="N7" s="4" t="n">
@@ -1414,7 +1413,7 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900186</t>
+          <t>HASLS22260900309</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1432,7 +1431,7 @@
           <t>202609200900</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1445,17 +1444,17 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1465,12 +1464,12 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>CY-RTN : 15-16/09/2026 (CONSOL)</t>
+          <t>Pickup : 2026-09-16, Return : 2026-09-16 CONSOL</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
@@ -1480,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>0</v>
@@ -1501,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
@@ -1548,299 +1547,163 @@
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900309</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-15, Return : 2026-09-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4">
-        <f>SUM(N9:V9)-W9</f>
-        <v/>
-      </c>
-      <c r="Z9" s="4">
-        <f>MAX(0,N9-MAX(0,W9))</f>
-        <v/>
-      </c>
-      <c r="AA9" s="4">
-        <f>MAX(0,O9-MAX(0,W9-SUM(N9:N9)))</f>
-        <v/>
-      </c>
-      <c r="AB9" s="4">
-        <f>MAX(0,P9-MAX(0,W9-SUM(N9:O9)))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="4">
-        <f>MAX(0,Q9-MAX(0,W9-SUM(N9:P9)))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="4">
-        <f>MAX(0,R9-MAX(0,W9-SUM(N9:Q9)))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="4">
-        <f>MAX(0,S9-MAX(0,W9-SUM(N9:R9)))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="4">
-        <f>MAX(0,T9-MAX(0,W9-SUM(N9:S9)))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="4">
-        <f>MAX(0,U9-MAX(0,W9-SUM(N9:T9)))</f>
-        <v/>
-      </c>
-      <c r="AH9" s="4">
-        <f>MAX(0,V9-MAX(0,W9-SUM(N9:U9)))</f>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5">
+        <f>SUM(N3:N8)</f>
+        <v/>
+      </c>
+      <c r="O9" s="5">
+        <f>SUM(O3:O8)</f>
+        <v/>
+      </c>
+      <c r="P9" s="5">
+        <f>SUM(P3:P8)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="5">
+        <f>SUM(Q3:Q8)</f>
+        <v/>
+      </c>
+      <c r="R9" s="5">
+        <f>SUM(R3:R8)</f>
+        <v/>
+      </c>
+      <c r="S9" s="5">
+        <f>SUM(S3:S8)</f>
+        <v/>
+      </c>
+      <c r="T9" s="5">
+        <f>SUM(T3:T8)</f>
+        <v/>
+      </c>
+      <c r="U9" s="5">
+        <f>SUM(U3:U8)</f>
+        <v/>
+      </c>
+      <c r="V9" s="5">
+        <f>SUM(V3:V8)</f>
+        <v/>
+      </c>
+      <c r="W9" s="5">
+        <f>SUM(W3:W8)</f>
+        <v/>
+      </c>
+      <c r="X9" s="5" t="n"/>
+      <c r="Y9" s="5">
+        <f>SUM(Y3:Y8)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="5">
+        <f>SUM(Z3:Z8)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="5">
+        <f>SUM(AA3:AA8)</f>
+        <v/>
+      </c>
+      <c r="AB9" s="5">
+        <f>SUM(AB3:AB8)</f>
+        <v/>
+      </c>
+      <c r="AC9" s="5">
+        <f>SUM(AC3:AC8)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>SUM(AD3:AD8)</f>
+        <v/>
+      </c>
+      <c r="AE9" s="5">
+        <f>SUM(AE3:AE8)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="5">
+        <f>SUM(AF3:AF8)</f>
+        <v/>
+      </c>
+      <c r="AG9" s="5">
+        <f>SUM(AG3:AG8)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="5">
+        <f>SUM(AH3:AH8)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5">
-        <f>SUM(N3:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="5">
-        <f>SUM(O3:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="5">
-        <f>SUM(P3:P9)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="5">
-        <f>SUM(Q3:Q9)</f>
-        <v/>
-      </c>
-      <c r="R10" s="5">
-        <f>SUM(R3:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="5">
-        <f>SUM(S3:S9)</f>
-        <v/>
-      </c>
-      <c r="T10" s="5">
-        <f>SUM(T3:T9)</f>
-        <v/>
-      </c>
-      <c r="U10" s="5">
-        <f>SUM(U3:U9)</f>
-        <v/>
-      </c>
-      <c r="V10" s="5">
-        <f>SUM(V3:V9)</f>
-        <v/>
-      </c>
-      <c r="W10" s="5">
-        <f>SUM(W3:W9)</f>
-        <v/>
-      </c>
-      <c r="X10" s="5" t="n"/>
-      <c r="Y10" s="5">
-        <f>SUM(Y3:Y9)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="5">
-        <f>SUM(Z3:Z9)</f>
-        <v/>
-      </c>
-      <c r="AA10" s="5">
-        <f>SUM(AA3:AA9)</f>
-        <v/>
-      </c>
-      <c r="AB10" s="5">
-        <f>SUM(AB3:AB9)</f>
-        <v/>
-      </c>
-      <c r="AC10" s="5">
-        <f>SUM(AC3:AC9)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="5">
-        <f>SUM(AD3:AD9)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="5">
-        <f>SUM(AE3:AE9)</f>
-        <v/>
-      </c>
-      <c r="AF10" s="5">
-        <f>SUM(AF3:AF9)</f>
-        <v/>
-      </c>
-      <c r="AG10" s="5">
-        <f>SUM(AG3:AG9)</f>
-        <v/>
-      </c>
-      <c r="AH10" s="5">
-        <f>SUM(AH3:AH9)</f>
-        <v/>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>15</v>
+      <c r="B15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH9"/>
+  <autoFilter ref="A2:AH8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>
   </mergeCells>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -34,19 +34,19 @@
       <sz val="13"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
+      <name val="Tahoma"/>
+      <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -103,16 +103,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,45 +497,45 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
-    <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="89" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="27" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BKG PENDING — PAT TERMINAL 1 &amp; 2 (PORT AUTHORITY OF THAILAND)   (BKK01+BKK04)</t>
+          <t>BKG PENDING   (BKK01+BKK04)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -623,47 +638,47 @@
           <t>COMMON REMARK</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>GP22</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>GP42</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>GP45</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>RE22</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>RE45</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>UT22</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>UT42</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>PC22</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>PC42</t>
         </is>
@@ -730,975 +745,975 @@
       </c>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>HASLS22260801208</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>KJT</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>202609222100</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>20260914</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
         </is>
       </c>
-      <c r="N3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
+      <c r="N3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="n">
+      <c r="Q3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="X3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="4">
+      <c r="X3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="5">
         <f>SUM(N3:V3)-W3</f>
         <v/>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3" s="5">
         <f>MAX(0,N3-MAX(0,W3))</f>
         <v/>
       </c>
-      <c r="AA3" s="4">
+      <c r="AA3" s="5">
         <f>MAX(0,O3-MAX(0,W3-SUM(N3:N3)))</f>
         <v/>
       </c>
-      <c r="AB3" s="4">
+      <c r="AB3" s="5">
         <f>MAX(0,P3-MAX(0,W3-SUM(N3:O3)))</f>
         <v/>
       </c>
-      <c r="AC3" s="4">
+      <c r="AC3" s="5">
         <f>MAX(0,Q3-MAX(0,W3-SUM(N3:P3)))</f>
         <v/>
       </c>
-      <c r="AD3" s="4">
+      <c r="AD3" s="5">
         <f>MAX(0,R3-MAX(0,W3-SUM(N3:Q3)))</f>
         <v/>
       </c>
-      <c r="AE3" s="4">
+      <c r="AE3" s="5">
         <f>MAX(0,S3-MAX(0,W3-SUM(N3:R3)))</f>
         <v/>
       </c>
-      <c r="AF3" s="4">
+      <c r="AF3" s="5">
         <f>MAX(0,T3-MAX(0,W3-SUM(N3:S3)))</f>
         <v/>
       </c>
-      <c r="AG3" s="4">
+      <c r="AG3" s="5">
         <f>MAX(0,U3-MAX(0,W3-SUM(N3:T3)))</f>
         <v/>
       </c>
-      <c r="AH3" s="4">
+      <c r="AH3" s="5">
         <f>MAX(0,V3-MAX(0,W3-SUM(N3:U3)))</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>HASLS22260801441</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>KJT</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>202609222100</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
         </is>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
+      <c r="O4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4">
+      <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5">
         <f>SUM(N4:V4)-W4</f>
         <v/>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4" s="5">
         <f>MAX(0,N4-MAX(0,W4))</f>
         <v/>
       </c>
-      <c r="AA4" s="4">
+      <c r="AA4" s="5">
         <f>MAX(0,O4-MAX(0,W4-SUM(N4:N4)))</f>
         <v/>
       </c>
-      <c r="AB4" s="4">
+      <c r="AB4" s="5">
         <f>MAX(0,P4-MAX(0,W4-SUM(N4:O4)))</f>
         <v/>
       </c>
-      <c r="AC4" s="4">
+      <c r="AC4" s="5">
         <f>MAX(0,Q4-MAX(0,W4-SUM(N4:P4)))</f>
         <v/>
       </c>
-      <c r="AD4" s="4">
+      <c r="AD4" s="5">
         <f>MAX(0,R4-MAX(0,W4-SUM(N4:Q4)))</f>
         <v/>
       </c>
-      <c r="AE4" s="4">
+      <c r="AE4" s="5">
         <f>MAX(0,S4-MAX(0,W4-SUM(N4:R4)))</f>
         <v/>
       </c>
-      <c r="AF4" s="4">
+      <c r="AF4" s="5">
         <f>MAX(0,T4-MAX(0,W4-SUM(N4:S4)))</f>
         <v/>
       </c>
-      <c r="AG4" s="4">
+      <c r="AG4" s="5">
         <f>MAX(0,U4-MAX(0,W4-SUM(N4:T4)))</f>
         <v/>
       </c>
-      <c r="AH4" s="4">
+      <c r="AH4" s="5">
         <f>MAX(0,V4-MAX(0,W4-SUM(N4:U4)))</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>HASLS22260801996</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>202609271700</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
 [1ST CY DATE : 17/09/2026 W/O RENT]</t>
         </is>
       </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
+      <c r="N5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4">
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="5">
         <f>SUM(N5:V5)-W5</f>
         <v/>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5" s="5">
         <f>MAX(0,N5-MAX(0,W5))</f>
         <v/>
       </c>
-      <c r="AA5" s="4">
+      <c r="AA5" s="5">
         <f>MAX(0,O5-MAX(0,W5-SUM(N5:N5)))</f>
         <v/>
       </c>
-      <c r="AB5" s="4">
+      <c r="AB5" s="5">
         <f>MAX(0,P5-MAX(0,W5-SUM(N5:O5)))</f>
         <v/>
       </c>
-      <c r="AC5" s="4">
+      <c r="AC5" s="5">
         <f>MAX(0,Q5-MAX(0,W5-SUM(N5:P5)))</f>
         <v/>
       </c>
-      <c r="AD5" s="4">
+      <c r="AD5" s="5">
         <f>MAX(0,R5-MAX(0,W5-SUM(N5:Q5)))</f>
         <v/>
       </c>
-      <c r="AE5" s="4">
+      <c r="AE5" s="5">
         <f>MAX(0,S5-MAX(0,W5-SUM(N5:R5)))</f>
         <v/>
       </c>
-      <c r="AF5" s="4">
+      <c r="AF5" s="5">
         <f>MAX(0,T5-MAX(0,W5-SUM(N5:S5)))</f>
         <v/>
       </c>
-      <c r="AG5" s="4">
+      <c r="AG5" s="5">
         <f>MAX(0,U5-MAX(0,W5-SUM(N5:T5)))</f>
         <v/>
       </c>
-      <c r="AH5" s="4">
+      <c r="AH5" s="5">
         <f>MAX(0,V5-MAX(0,W5-SUM(N5:U5)))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>HASLS22260802251</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>KMTP</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>202609200900</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>TAPIOCA FLOUR</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.16/09/26 *CLS TIME CFS DD.16/09/26 - 17:00HRS.* </t>
         </is>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4">
+      <c r="O6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5">
         <f>SUM(N6:V6)-W6</f>
         <v/>
       </c>
-      <c r="Z6" s="4">
+      <c r="Z6" s="5">
         <f>MAX(0,N6-MAX(0,W6))</f>
         <v/>
       </c>
-      <c r="AA6" s="4">
+      <c r="AA6" s="5">
         <f>MAX(0,O6-MAX(0,W6-SUM(N6:N6)))</f>
         <v/>
       </c>
-      <c r="AB6" s="4">
+      <c r="AB6" s="5">
         <f>MAX(0,P6-MAX(0,W6-SUM(N6:O6)))</f>
         <v/>
       </c>
-      <c r="AC6" s="4">
+      <c r="AC6" s="5">
         <f>MAX(0,Q6-MAX(0,W6-SUM(N6:P6)))</f>
         <v/>
       </c>
-      <c r="AD6" s="4">
+      <c r="AD6" s="5">
         <f>MAX(0,R6-MAX(0,W6-SUM(N6:Q6)))</f>
         <v/>
       </c>
-      <c r="AE6" s="4">
+      <c r="AE6" s="5">
         <f>MAX(0,S6-MAX(0,W6-SUM(N6:R6)))</f>
         <v/>
       </c>
-      <c r="AF6" s="4">
+      <c r="AF6" s="5">
         <f>MAX(0,T6-MAX(0,W6-SUM(N6:S6)))</f>
         <v/>
       </c>
-      <c r="AG6" s="4">
+      <c r="AG6" s="5">
         <f>MAX(0,U6-MAX(0,W6-SUM(N6:T6)))</f>
         <v/>
       </c>
-      <c r="AH6" s="4">
+      <c r="AH6" s="5">
         <f>MAX(0,V6-MAX(0,W6-SUM(N6:U6)))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>HASLS22260802589</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SWMM</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>2609N</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>202609230900</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">CY-RTN : 16-17/09/2026 (CONSOL) *EXTEND CLS TIME : 22/09/2026 @17.00* </t>
         </is>
       </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4">
+      <c r="Q7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5">
         <f>SUM(N7:V7)-W7</f>
         <v/>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z7" s="5">
         <f>MAX(0,N7-MAX(0,W7))</f>
         <v/>
       </c>
-      <c r="AA7" s="4">
+      <c r="AA7" s="5">
         <f>MAX(0,O7-MAX(0,W7-SUM(N7:N7)))</f>
         <v/>
       </c>
-      <c r="AB7" s="4">
+      <c r="AB7" s="5">
         <f>MAX(0,P7-MAX(0,W7-SUM(N7:O7)))</f>
         <v/>
       </c>
-      <c r="AC7" s="4">
+      <c r="AC7" s="5">
         <f>MAX(0,Q7-MAX(0,W7-SUM(N7:P7)))</f>
         <v/>
       </c>
-      <c r="AD7" s="4">
+      <c r="AD7" s="5">
         <f>MAX(0,R7-MAX(0,W7-SUM(N7:Q7)))</f>
         <v/>
       </c>
-      <c r="AE7" s="4">
+      <c r="AE7" s="5">
         <f>MAX(0,S7-MAX(0,W7-SUM(N7:R7)))</f>
         <v/>
       </c>
-      <c r="AF7" s="4">
+      <c r="AF7" s="5">
         <f>MAX(0,T7-MAX(0,W7-SUM(N7:S7)))</f>
         <v/>
       </c>
-      <c r="AG7" s="4">
+      <c r="AG7" s="5">
         <f>MAX(0,U7-MAX(0,W7-SUM(N7:T7)))</f>
         <v/>
       </c>
-      <c r="AH7" s="4">
+      <c r="AH7" s="5">
         <f>MAX(0,V7-MAX(0,W7-SUM(N7:U7)))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>HASLS22260900309</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>KMTP</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>202609200900</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-16, Return : 2026-09-16 CONSOL</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4" t="n">
+      <c r="N8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="4" t="n">
+      <c r="Q8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="X8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4">
+      <c r="X8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
         <f>SUM(N8:V8)-W8</f>
         <v/>
       </c>
-      <c r="Z8" s="4">
+      <c r="Z8" s="5">
         <f>MAX(0,N8-MAX(0,W8))</f>
         <v/>
       </c>
-      <c r="AA8" s="4">
+      <c r="AA8" s="5">
         <f>MAX(0,O8-MAX(0,W8-SUM(N8:N8)))</f>
         <v/>
       </c>
-      <c r="AB8" s="4">
+      <c r="AB8" s="5">
         <f>MAX(0,P8-MAX(0,W8-SUM(N8:O8)))</f>
         <v/>
       </c>
-      <c r="AC8" s="4">
+      <c r="AC8" s="5">
         <f>MAX(0,Q8-MAX(0,W8-SUM(N8:P8)))</f>
         <v/>
       </c>
-      <c r="AD8" s="4">
+      <c r="AD8" s="5">
         <f>MAX(0,R8-MAX(0,W8-SUM(N8:Q8)))</f>
         <v/>
       </c>
-      <c r="AE8" s="4">
+      <c r="AE8" s="5">
         <f>MAX(0,S8-MAX(0,W8-SUM(N8:R8)))</f>
         <v/>
       </c>
-      <c r="AF8" s="4">
+      <c r="AF8" s="5">
         <f>MAX(0,T8-MAX(0,W8-SUM(N8:S8)))</f>
         <v/>
       </c>
-      <c r="AG8" s="4">
+      <c r="AG8" s="5">
         <f>MAX(0,U8-MAX(0,W8-SUM(N8:T8)))</f>
         <v/>
       </c>
-      <c r="AH8" s="4">
+      <c r="AH8" s="5">
         <f>MAX(0,V8-MAX(0,W8-SUM(N8:U8)))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="8">
         <f>SUM(N3:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="8">
         <f>SUM(O3:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="8">
         <f>SUM(P3:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="8">
         <f>SUM(Q3:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="5">
+      <c r="R9" s="8">
         <f>SUM(R3:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="8">
         <f>SUM(S3:S8)</f>
         <v/>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="8">
         <f>SUM(T3:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="5">
+      <c r="U9" s="8">
         <f>SUM(U3:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="5">
+      <c r="V9" s="8">
         <f>SUM(V3:V8)</f>
         <v/>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="7">
         <f>SUM(W3:W8)</f>
         <v/>
       </c>
-      <c r="X9" s="5" t="n"/>
-      <c r="Y9" s="5">
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7">
         <f>SUM(Y3:Y8)</f>
         <v/>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9" s="7">
         <f>SUM(Z3:Z8)</f>
         <v/>
       </c>
-      <c r="AA9" s="5">
+      <c r="AA9" s="7">
         <f>SUM(AA3:AA8)</f>
         <v/>
       </c>
-      <c r="AB9" s="5">
+      <c r="AB9" s="7">
         <f>SUM(AB3:AB8)</f>
         <v/>
       </c>
-      <c r="AC9" s="5">
+      <c r="AC9" s="7">
         <f>SUM(AC3:AC8)</f>
         <v/>
       </c>
-      <c r="AD9" s="5">
+      <c r="AD9" s="7">
         <f>SUM(AD3:AD8)</f>
         <v/>
       </c>
-      <c r="AE9" s="5">
+      <c r="AE9" s="7">
         <f>SUM(AE3:AE8)</f>
         <v/>
       </c>
-      <c r="AF9" s="5">
+      <c r="AF9" s="7">
         <f>SUM(AF3:AF8)</f>
         <v/>
       </c>
-      <c r="AG9" s="5">
+      <c r="AG9" s="7">
         <f>SUM(AG3:AG8)</f>
         <v/>
       </c>
-      <c r="AH9" s="5">
+      <c r="AH9" s="7">
         <f>SUM(AH3:AH8)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="7" t="n">
         <v>8</v>
       </c>
     </row>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AH$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$V$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,27 +103,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -493,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -509,27 +500,15 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="89" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="27" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
-    <col width="16" customWidth="1" min="33" max="33"/>
-    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
@@ -559,18 +538,6 @@
       <c r="T1" s="2" t="n"/>
       <c r="U1" s="2" t="n"/>
       <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -638,1089 +605,708 @@
           <t>COMMON REMARK</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>GP22</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>GP42</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>GP45</t>
-        </is>
-      </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>RE22</t>
-        </is>
-      </c>
-      <c r="R2" s="4" t="inlineStr">
-        <is>
-          <t>RE45</t>
-        </is>
-      </c>
-      <c r="S2" s="4" t="inlineStr">
-        <is>
-          <t>UT22</t>
-        </is>
-      </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>UT42</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>PC22</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>PC42</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>Pickup</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>Balance (Booked - Pickup)</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>GP22 Remaining</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>GP42 Remaining</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>GP45 Remaining</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>RE22 Remaining</t>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>RE45 Remaining</t>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>UT22 Remaining</t>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>UT42 Remaining</t>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>PC22 Remaining</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>PC42 Remaining</t>
         </is>
       </c>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>HASLS22260801208</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>KJT</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>202609222100</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>20260914</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
         </is>
       </c>
-      <c r="N3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="5">
-        <f>SUM(N3:V3)-W3</f>
-        <v/>
-      </c>
-      <c r="Z3" s="5">
-        <f>MAX(0,N3-MAX(0,W3))</f>
-        <v/>
-      </c>
-      <c r="AA3" s="5">
-        <f>MAX(0,O3-MAX(0,W3-SUM(N3:N3)))</f>
-        <v/>
-      </c>
-      <c r="AB3" s="5">
-        <f>MAX(0,P3-MAX(0,W3-SUM(N3:O3)))</f>
-        <v/>
-      </c>
-      <c r="AC3" s="5">
-        <f>MAX(0,Q3-MAX(0,W3-SUM(N3:P3)))</f>
-        <v/>
-      </c>
-      <c r="AD3" s="5">
-        <f>MAX(0,R3-MAX(0,W3-SUM(N3:Q3)))</f>
-        <v/>
-      </c>
-      <c r="AE3" s="5">
-        <f>MAX(0,S3-MAX(0,W3-SUM(N3:R3)))</f>
-        <v/>
-      </c>
-      <c r="AF3" s="5">
-        <f>MAX(0,T3-MAX(0,W3-SUM(N3:S3)))</f>
-        <v/>
-      </c>
-      <c r="AG3" s="5">
-        <f>MAX(0,U3-MAX(0,W3-SUM(N3:T3)))</f>
-        <v/>
-      </c>
-      <c r="AH3" s="5">
-        <f>MAX(0,V3-MAX(0,W3-SUM(N3:U3)))</f>
-        <v/>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>HASLS22260801441</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>KJT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>202609222100</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
         </is>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="n">
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="5">
-        <f>SUM(N4:V4)-W4</f>
-        <v/>
-      </c>
-      <c r="Z4" s="5">
-        <f>MAX(0,N4-MAX(0,W4))</f>
-        <v/>
-      </c>
-      <c r="AA4" s="5">
-        <f>MAX(0,O4-MAX(0,W4-SUM(N4:N4)))</f>
-        <v/>
-      </c>
-      <c r="AB4" s="5">
-        <f>MAX(0,P4-MAX(0,W4-SUM(N4:O4)))</f>
-        <v/>
-      </c>
-      <c r="AC4" s="5">
-        <f>MAX(0,Q4-MAX(0,W4-SUM(N4:P4)))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="5">
-        <f>MAX(0,R4-MAX(0,W4-SUM(N4:Q4)))</f>
-        <v/>
-      </c>
-      <c r="AE4" s="5">
-        <f>MAX(0,S4-MAX(0,W4-SUM(N4:R4)))</f>
-        <v/>
-      </c>
-      <c r="AF4" s="5">
-        <f>MAX(0,T4-MAX(0,W4-SUM(N4:S4)))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="5">
-        <f>MAX(0,U4-MAX(0,W4-SUM(N4:T4)))</f>
-        <v/>
-      </c>
-      <c r="AH4" s="5">
-        <f>MAX(0,V4-MAX(0,W4-SUM(N4:U4)))</f>
-        <v/>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>HASLS22260801996</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>202609271700</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
 [1ST CY DATE : 17/09/2026 W/O RENT]</t>
         </is>
       </c>
-      <c r="N5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6" t="n">
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="5">
-        <f>SUM(N5:V5)-W5</f>
-        <v/>
-      </c>
-      <c r="Z5" s="5">
-        <f>MAX(0,N5-MAX(0,W5))</f>
-        <v/>
-      </c>
-      <c r="AA5" s="5">
-        <f>MAX(0,O5-MAX(0,W5-SUM(N5:N5)))</f>
-        <v/>
-      </c>
-      <c r="AB5" s="5">
-        <f>MAX(0,P5-MAX(0,W5-SUM(N5:O5)))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="5">
-        <f>MAX(0,Q5-MAX(0,W5-SUM(N5:P5)))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="5">
-        <f>MAX(0,R5-MAX(0,W5-SUM(N5:Q5)))</f>
-        <v/>
-      </c>
-      <c r="AE5" s="5">
-        <f>MAX(0,S5-MAX(0,W5-SUM(N5:R5)))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="5">
-        <f>MAX(0,T5-MAX(0,W5-SUM(N5:S5)))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="5">
-        <f>MAX(0,U5-MAX(0,W5-SUM(N5:T5)))</f>
-        <v/>
-      </c>
-      <c r="AH5" s="5">
-        <f>MAX(0,V5-MAX(0,W5-SUM(N5:U5)))</f>
-        <v/>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>HASLS22260802251</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>KMTP</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>202609200900</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>TAPIOCA FLOUR</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.16/09/26 *CLS TIME CFS DD.16/09/26 - 17:00HRS.* </t>
         </is>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="5">
-        <f>SUM(N6:V6)-W6</f>
-        <v/>
-      </c>
-      <c r="Z6" s="5">
-        <f>MAX(0,N6-MAX(0,W6))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="5">
-        <f>MAX(0,O6-MAX(0,W6-SUM(N6:N6)))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="5">
-        <f>MAX(0,P6-MAX(0,W6-SUM(N6:O6)))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="5">
-        <f>MAX(0,Q6-MAX(0,W6-SUM(N6:P6)))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="5">
-        <f>MAX(0,R6-MAX(0,W6-SUM(N6:Q6)))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="5">
-        <f>MAX(0,S6-MAX(0,W6-SUM(N6:R6)))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="5">
-        <f>MAX(0,T6-MAX(0,W6-SUM(N6:S6)))</f>
-        <v/>
-      </c>
-      <c r="AG6" s="5">
-        <f>MAX(0,U6-MAX(0,W6-SUM(N6:T6)))</f>
-        <v/>
-      </c>
-      <c r="AH6" s="5">
-        <f>MAX(0,V6-MAX(0,W6-SUM(N6:U6)))</f>
-        <v/>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>HASLS22260802589</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>SWMM</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>2609N</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>202609230900</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CY-RTN : 16-17/09/2026 (CONSOL) *EXTEND CLS TIME : 22/09/2026 @17.00* </t>
         </is>
       </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="n">
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="5">
-        <f>SUM(N7:V7)-W7</f>
-        <v/>
-      </c>
-      <c r="Z7" s="5">
-        <f>MAX(0,N7-MAX(0,W7))</f>
-        <v/>
-      </c>
-      <c r="AA7" s="5">
-        <f>MAX(0,O7-MAX(0,W7-SUM(N7:N7)))</f>
-        <v/>
-      </c>
-      <c r="AB7" s="5">
-        <f>MAX(0,P7-MAX(0,W7-SUM(N7:O7)))</f>
-        <v/>
-      </c>
-      <c r="AC7" s="5">
-        <f>MAX(0,Q7-MAX(0,W7-SUM(N7:P7)))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="5">
-        <f>MAX(0,R7-MAX(0,W7-SUM(N7:Q7)))</f>
-        <v/>
-      </c>
-      <c r="AE7" s="5">
-        <f>MAX(0,S7-MAX(0,W7-SUM(N7:R7)))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="5">
-        <f>MAX(0,T7-MAX(0,W7-SUM(N7:S7)))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="5">
-        <f>MAX(0,U7-MAX(0,W7-SUM(N7:T7)))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="5">
-        <f>MAX(0,V7-MAX(0,W7-SUM(N7:U7)))</f>
-        <v/>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>HASLS22260900309</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>KMTP</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>202609200900</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-16, Return : 2026-09-16 CONSOL</t>
         </is>
       </c>
-      <c r="N8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="5">
-        <f>SUM(N8:V8)-W8</f>
-        <v/>
-      </c>
-      <c r="Z8" s="5">
-        <f>MAX(0,N8-MAX(0,W8))</f>
-        <v/>
-      </c>
-      <c r="AA8" s="5">
-        <f>MAX(0,O8-MAX(0,W8-SUM(N8:N8)))</f>
-        <v/>
-      </c>
-      <c r="AB8" s="5">
-        <f>MAX(0,P8-MAX(0,W8-SUM(N8:O8)))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="5">
-        <f>MAX(0,Q8-MAX(0,W8-SUM(N8:P8)))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="5">
-        <f>MAX(0,R8-MAX(0,W8-SUM(N8:Q8)))</f>
-        <v/>
-      </c>
-      <c r="AE8" s="5">
-        <f>MAX(0,S8-MAX(0,W8-SUM(N8:R8)))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="5">
-        <f>MAX(0,T8-MAX(0,W8-SUM(N8:S8)))</f>
-        <v/>
-      </c>
-      <c r="AG8" s="5">
-        <f>MAX(0,U8-MAX(0,W8-SUM(N8:T8)))</f>
-        <v/>
-      </c>
-      <c r="AH8" s="5">
-        <f>MAX(0,V8-MAX(0,W8-SUM(N8:U8)))</f>
-        <v/>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="8">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5">
         <f>SUM(N3:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="5">
         <f>SUM(O3:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="5">
         <f>SUM(P3:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="5">
         <f>SUM(Q3:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="5">
         <f>SUM(R3:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="5">
         <f>SUM(S3:S8)</f>
         <v/>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="5">
         <f>SUM(T3:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="5">
         <f>SUM(U3:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="5">
         <f>SUM(V3:V8)</f>
         <v/>
       </c>
-      <c r="W9" s="7">
-        <f>SUM(W3:W8)</f>
-        <v/>
-      </c>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7">
-        <f>SUM(Y3:Y8)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="7">
-        <f>SUM(Z3:Z8)</f>
-        <v/>
-      </c>
-      <c r="AA9" s="7">
-        <f>SUM(AA3:AA8)</f>
-        <v/>
-      </c>
-      <c r="AB9" s="7">
-        <f>SUM(AB3:AB8)</f>
-        <v/>
-      </c>
-      <c r="AC9" s="7">
-        <f>SUM(AC3:AC8)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="7">
-        <f>SUM(AD3:AD8)</f>
-        <v/>
-      </c>
-      <c r="AE9" s="7">
-        <f>SUM(AE3:AE8)</f>
-        <v/>
-      </c>
-      <c r="AF9" s="7">
-        <f>SUM(AF3:AF8)</f>
-        <v/>
-      </c>
-      <c r="AG9" s="7">
-        <f>SUM(AG3:AG8)</f>
-        <v/>
-      </c>
-      <c r="AH9" s="7">
-        <f>SUM(AH3:AH8)</f>
-        <v/>
-      </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH8"/>
+  <autoFilter ref="A2:V8"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -500,15 +500,15 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="89" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
@@ -607,47 +607,47 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>GP22 Remaining</t>
+          <t>GP22</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>GP42 Remaining</t>
+          <t>GP42</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>GP45 Remaining</t>
+          <t>GP45</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>RE22 Remaining</t>
+          <t>RE22</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>RE45 Remaining</t>
+          <t>RE45</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>UT22 Remaining</t>
+          <t>UT22</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>UT42 Remaining</t>
+          <t>UT42</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>PC22 Remaining</t>
+          <t>PC22</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>PC42 Remaining</t>
+          <t>PC42</t>
         </is>
       </c>
     </row>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$V$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$V$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="89" customWidth="1" min="13" max="13"/>
+    <col width="125" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -654,12 +654,12 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801208</t>
+          <t>HASLS22260801996</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -669,10 +669,10 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
+          <t>202609290000</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -685,17 +685,17 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -710,7 +710,8 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-14, Return : 2026-09-15 CONSOL</t>
+          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
+[1ST CY DATE : 17/09/2026 W/O RENT]</t>
         </is>
       </c>
       <c r="N3" s="4" t="n">
@@ -720,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>0</v>
@@ -744,25 +745,25 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801441</t>
+          <t>HASLS22260802179</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
+          <t>202609262030</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -775,17 +776,17 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -800,17 +801,18 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-10, Return : 2026-09-11 CONSOL</t>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL
+(1ST CY 23/09/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>0</v>
@@ -834,7 +836,7 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801996</t>
+          <t>HASLS22260802382</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -849,10 +851,10 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609271700</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
+          <t>202609290000</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -865,17 +867,17 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -890,8 +892,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
-[1ST CY DATE : 17/09/2026 W/O RENT]</t>
+          <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
         </is>
       </c>
       <c r="N5" s="4" t="n">
@@ -901,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>0</v>
@@ -925,25 +926,25 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802251</t>
+          <t>HASLS22260900187</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
+          <t>202609290000</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -956,42 +957,42 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>V.C.E. COMPANY LIMITED</t>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>TAPIOCA FLOUR</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.16/09/26 *CLS TIME CFS DD.16/09/26 - 17:00HRS.* </t>
+          <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
         <v>0</v>
@@ -1015,25 +1016,25 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802589</t>
+          <t>HASLS22260900803</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1046,42 +1047,43 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>BANYAN TREE GALLERY (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>HOTEL ACCESSORIES</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>Requested Good &amp; Clean contr</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 16-17/09/2026 (CONSOL) *EXTEND CLS TIME : 22/09/2026 @17.00* </t>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.17/09/26 CLS TIME CFS DD.18/09/26 - 17:00HRS.
+(1ST CFS DD: 17/09/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>0</v>
@@ -1103,208 +1105,118 @@
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900309</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>20260916</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-16, Return : 2026-09-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>0</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5">
+        <f>SUM(N3:N7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
+        <f>SUM(O3:O7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="5">
+        <f>SUM(P3:P7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="5">
+        <f>SUM(Q3:Q7)</f>
+        <v/>
+      </c>
+      <c r="R8" s="5">
+        <f>SUM(R3:R7)</f>
+        <v/>
+      </c>
+      <c r="S8" s="5">
+        <f>SUM(S3:S7)</f>
+        <v/>
+      </c>
+      <c r="T8" s="5">
+        <f>SUM(T3:T7)</f>
+        <v/>
+      </c>
+      <c r="U8" s="5">
+        <f>SUM(U3:U7)</f>
+        <v/>
+      </c>
+      <c r="V8" s="5">
+        <f>SUM(V3:V7)</f>
+        <v/>
       </c>
     </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5">
-        <f>SUM(N3:N8)</f>
-        <v/>
-      </c>
-      <c r="O9" s="5">
-        <f>SUM(O3:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="5">
-        <f>SUM(P3:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="5">
-        <f>SUM(Q3:Q8)</f>
-        <v/>
-      </c>
-      <c r="R9" s="5">
-        <f>SUM(R3:R8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="5">
-        <f>SUM(S3:S8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="5">
-        <f>SUM(T3:T8)</f>
-        <v/>
-      </c>
-      <c r="U9" s="5">
-        <f>SUM(U3:U8)</f>
-        <v/>
-      </c>
-      <c r="V9" s="5">
-        <f>SUM(V3:V8)</f>
-        <v/>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>สรุปยอดบุ๊คทั้งหมด</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>สรุปยอดบุ๊คทั้งหมด</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>8</v>
+      <c r="C14" s="5" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V8"/>
+  <autoFilter ref="A2:V7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -487,28 +487,28 @@
   <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="125" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="124" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -613,22 +613,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801996</t>
+          <t>HASLS22260700891</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202609290000</t>
+          <t>202610051100</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -649,28 +649,28 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-11, Return : 2026-09-11 CONSOL 
-[1ST CY DATE : 17/09/2026 W/O RENT]</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.02/10/26 - 17:00HRS.*
+[1ST CFS DATE : 01/10/2026 W/O RENT]</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -704,22 +704,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802179</t>
+          <t>HASLS22260800761</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202609262030</t>
+          <t>202609282100</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -730,452 +730,5241 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-24, Return : 2026-09-26 
+ CLS TIME 25/09 @23.59 
+ </t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801149</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>202610192000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>PET FOOD</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801150</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>202610192000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>PET FOOD</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801209</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801210</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202610030330</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801229</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-18, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801230</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801443</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>202610030700</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801462</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801786</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610030700</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 28/09/26 CLS TIME 29/07 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801789</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.22/09/26 *CLS TIME CFS DD.23/09/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801791</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610030700</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.24/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801991</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801996</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-25, Return : 2026-09-25 CONSOL 
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802037</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202610101000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>FIVE PAGODAS PHARMACY CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>YA HOM FIVE PAGODAS BRAND (MEDICINE)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802179</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL
 (1ST CY 23/09/26 WO/RENT)</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="n">
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802180</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202610101000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802238</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>COTTON BALLS</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>GOOD &amp; CLEAN CNTR</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+ </t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>HASLS22260802382</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>202609290000</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802450</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802541</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802590</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802591</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>202610030700</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900019</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>SIAM TOKAI CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>BRINE CURED GINGER</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Remark: Food grade container, Good and Clean
+container, no hole, no rust, no oil stain, no
+splinter</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.23/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900064</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>202610030330</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900165</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900172</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-25, Return : 2026-09-25 CONSOL </t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>HASLS22260900187</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>202609290000</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>(CONSOL)</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900803</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900188</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>202609261500</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 23-24/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900189</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900201</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>202610171400</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09CONSOL</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900206</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>202610030330</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900207</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>202610192000</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900262</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>202609241400</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>COTTON BUDS</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 22/09/26 *CLS TIME 22/09 @17.00HRS*</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900323</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>202610030330</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900717</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>CONTAINER GRADE A</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-23, Return : 2026-09-23 </t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900780</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>202610030330</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL FOODS SUPPLY CO., LTD</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SYRUP</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST : The container is in good condition, with no signs of rust or leakage.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING DD.25/09/2026  @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.28/09/2026 @ 17.00 (1ST CFS DD.25/09/2026)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900789</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>202610142100</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>MIX-LOAD</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900855</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>202609242350</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>LITTLE THAI INTERNATIONAL CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SEASONINGS</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>REQ. FOOD GRADE CONTAINER</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING DD.22/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.22/09/2026 @ 17.00 REQ. FOOD GRADE CONTAINER </t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900896</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>202610030700</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-01CONSOL</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901096</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.28/09/26 CLS TIME CFS DD.28/09/26- 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901130</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>202610101000</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901132</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SWIC</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>202610140000</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901157</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>202610101000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901158</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>202610110700</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901170</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901291</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>202610110700</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901391</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>202609211300</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>V.C.E. COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>TAPIOCA STARCH</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901414</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>202610142100</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901553</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>202610110700</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901567</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>202610042000</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901602</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901603</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202610110700</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901753</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901755</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>202610140000</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901803</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>202610030330</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20260917</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>BANYAN TREE GALLERY (THAILAND) COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>HOTEL ACCESSORIES</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Requested Good &amp; Clean contr</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.17/09/26 CLS TIME CFS DD.18/09/26 - 17:00HRS.
-(1ST CFS DD: 17/09/26 WO/RENT)</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>WISUNO ELECTRONICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>TRANSFORMER</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="O58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901816</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>202610142100</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3">
-        <f>SUM(N2:N6)</f>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3">
+        <f>SUM(N2:N59)</f>
         <v/>
       </c>
-      <c r="O7" s="3">
-        <f>SUM(O2:O6)</f>
+      <c r="O60" s="3">
+        <f>SUM(O2:O59)</f>
         <v/>
       </c>
-      <c r="P7" s="3">
-        <f>SUM(P2:P6)</f>
+      <c r="P60" s="3">
+        <f>SUM(P2:P59)</f>
         <v/>
       </c>
-      <c r="Q7" s="3">
-        <f>SUM(Q2:Q6)</f>
+      <c r="Q60" s="3">
+        <f>SUM(Q2:Q59)</f>
         <v/>
       </c>
-      <c r="R7" s="3">
-        <f>SUM(R2:R6)</f>
+      <c r="R60" s="3">
+        <f>SUM(R2:R59)</f>
         <v/>
       </c>
-      <c r="S7" s="3">
-        <f>SUM(S2:S6)</f>
+      <c r="S60" s="3">
+        <f>SUM(S2:S59)</f>
         <v/>
       </c>
-      <c r="T7" s="3">
-        <f>SUM(T2:T6)</f>
+      <c r="T60" s="3">
+        <f>SUM(T2:T59)</f>
         <v/>
       </c>
-      <c r="U7" s="3">
-        <f>SUM(U2:U6)</f>
+      <c r="U60" s="3">
+        <f>SUM(U2:U59)</f>
         <v/>
       </c>
-      <c r="V7" s="3">
-        <f>SUM(V2:V6)</f>
+      <c r="V60" s="3">
+        <f>SUM(V2:V59)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="B64" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B65" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>9</v>
+      <c r="B66" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V6"/>
+  <autoFilter ref="A1:V59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,12 +481,12 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="111" customWidth="1" min="13" max="13"/>
+    <col width="109" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -613,22 +613,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801229</t>
+          <t>HASLS22260700891</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610051100</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -649,27 +649,28 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-18, Return : 2026-09-18 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.02/10/26 *CLS TIME CFS DD.02/10/26 - 17:00HRS.*
+</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -703,22 +704,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802179</t>
+          <t>HASLS22260800761</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202609261500</t>
+          <t>202609282100</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,632 +730,5425 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-24, Return : 2026-09-25 CONSOL 
+</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801149</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>202610192000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>PET FOOD</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801150</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>202610192000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>PET FOOD</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801209</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801210</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202610030500</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801229</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-18, Return : 2026-09-18 CONSOL</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801230</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801443</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>202610031300</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801462</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801786</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610031300</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.29/09/26 CLS TIME CFS DD.30/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801789</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.02/10/26 *CLS TIME CFS DD.02/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801791</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610031300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.30/09/26 CLS TIME CFS DD.01/10/26 - 17:00HRS. 
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801991</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260801996</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-25, Return : 2026-09-25 CONSOL 
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802179</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202609270130</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL
 (1ST CY 23/09/26 WO/RENT)</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="n">
+      <c r="N17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802180</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202610100900</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802238</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>COTTON BALLS</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>GOOD &amp; CLEAN CNTR</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+ </t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>HASLS22260802382</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>202609282100</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
+      <c r="N20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802450</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>HASLS22260802541</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>202609282100</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>CNTAO</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>20260918</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802590</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802591</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>202610031300</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900019</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>202609270130</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>SIAM TOKAI CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>BRINE CURED GINGER</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Remark: Food grade container, Good and Clean
+container, no hole, no rust, no oil stain, no
+splinter</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.23/09/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900064</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>202610030500</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900165</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>HASLS22260900187</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>KMGY</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>202609282100</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>(CONSOL)</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900262</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900201</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>202610172300</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09CONSOL</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900206</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>202610030500</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
+ EXTEND CLS TIME : 30/09 @23.59 </t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900207</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>202610192000</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900323</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900717</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>CONTAINER GRADE A</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 23/09/26 CLS TIME 24/09 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900780</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL FOODS SUPPLY CO., LTD</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SYRUP</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST : The container is in good condition, with no signs of rust or leakage.</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900789</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>MIX-LOAD</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900896</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>202610031300</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-01CONSOL</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901096</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.28/09/26 CLS TIME CFS DD.28/09/26- 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901130</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>202610100900</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901132</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>202610122300</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901157</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>202610100900</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901158</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901170</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2609N</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>202609241400</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901291</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901391</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20260922</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>COTTON BUDS</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 22/09/26 *CLS TIME 22/09 @17.00HRS*</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>V.C.E. COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>TAPIOCA STARCH</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900855</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>202609242350</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901414</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901553</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901567</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>202610061900</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901602</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901603</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901655</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>202610122300</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20260922</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>LITTLE THAI INTERNATIONAL CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SEASONINGS</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>REQ. FOOD GRADE CONTAINER</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING DD.22/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
-CLS TIME DD.22/09/2026 @ 17.00 REQ. FOOD GRADE CONTAINER </t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>MRD-ECC CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901753</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>202610051100</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901755</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>202610122300</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901803</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>202610030500</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>WISUNO ELECTRONICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>TRANSFORMER</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901816</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901881</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202609270130</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-09-24, Return : 2026-09-24 CONSOL
+*1ST CY CNTR DD.23/09/2026* 
+</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901887</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>202610100900</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
+**1ST RETURN CNTR DD.07/10/2026**</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901979</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901980</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902097</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>202610122300</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902170</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902198</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3">
-        <f>SUM(N2:N8)</f>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3">
+        <f>SUM(N2:N61)</f>
         <v/>
       </c>
-      <c r="O9" s="3">
-        <f>SUM(O2:O8)</f>
+      <c r="O62" s="3">
+        <f>SUM(O2:O61)</f>
         <v/>
       </c>
-      <c r="P9" s="3">
-        <f>SUM(P2:P8)</f>
+      <c r="P62" s="3">
+        <f>SUM(P2:P61)</f>
         <v/>
       </c>
-      <c r="Q9" s="3">
-        <f>SUM(Q2:Q8)</f>
+      <c r="Q62" s="3">
+        <f>SUM(Q2:Q61)</f>
         <v/>
       </c>
-      <c r="R9" s="3">
-        <f>SUM(R2:R8)</f>
+      <c r="R62" s="3">
+        <f>SUM(R2:R61)</f>
         <v/>
       </c>
-      <c r="S9" s="3">
-        <f>SUM(S2:S8)</f>
+      <c r="S62" s="3">
+        <f>SUM(S2:S61)</f>
         <v/>
       </c>
-      <c r="T9" s="3">
-        <f>SUM(T2:T8)</f>
+      <c r="T62" s="3">
+        <f>SUM(T2:T61)</f>
         <v/>
       </c>
-      <c r="U9" s="3">
-        <f>SUM(U2:U8)</f>
+      <c r="U62" s="3">
+        <f>SUM(U2:U61)</f>
         <v/>
       </c>
-      <c r="V9" s="3">
-        <f>SUM(V2:V8)</f>
+      <c r="V62" s="3">
+        <f>SUM(V2:V61)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B66" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B67" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>11</v>
+      <c r="B68" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V8"/>
+  <autoFilter ref="A1:V61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802179</t>
+          <t>HASLS22260802180</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202609270130</t>
+          <t>202610100900</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2024,8 +2024,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL
-(1ST CY 23/09/26 WO/RENT)</t>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
@@ -2035,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>0</v>
@@ -2059,22 +2058,22 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802180</t>
+          <t>HASLS22260802238</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202609282100</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2085,47 +2084,48 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>COTTON BALLS</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD &amp; CLEAN CNTR</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+ </t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0</v>
@@ -2149,7 +2149,7 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802238</t>
+          <t>HASLS22260802382</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2180,43 +2180,42 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>COTTON BALLS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>GOOD &amp; CLEAN CNTR</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
- </t>
+          <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0</v>
@@ -2240,12 +2239,12 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802382</t>
+          <t>HASLS22260802450</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2255,7 +2254,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610061900</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2266,7 +2265,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2276,12 +2275,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2296,7 +2295,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
@@ -2330,12 +2329,12 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802450</t>
+          <t>HASLS22260802541</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2345,7 +2344,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202609282100</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2356,22 +2355,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2386,17 +2385,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>0</v>
@@ -2420,22 +2419,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802541</t>
+          <t>HASLS22260802590</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610051100</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2446,27 +2445,27 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO / CONSOL</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2476,17 +2475,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
+          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>0</v>
@@ -2510,22 +2509,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802590</t>
+          <t>HASLS22260802591</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610031300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2546,7 +2545,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2566,7 +2565,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
+          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
@@ -2600,7 +2599,7 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802591</t>
+          <t>HASLS22260900019</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2626,134 +2625,134 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPKCZ</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>SIAM TOKAI CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>BRINE CURED GINGER</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900019</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SKOR</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>202609270130</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>JPKCZ</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x3 </t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>SIAM TOKAI CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>BRINE CURED GINGER</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Remark: Food grade container, Good and Clean
 container, no hole, no rust, no oil stain, no
 splinter</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.23/09/26 - 17:00HRS.
 </t>
         </is>
       </c>
+      <c r="N24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900064</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>202610030500</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-30, Return : 2026-09-30 CONSOL</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>0</v>
@@ -2783,12 +2782,12 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900064</t>
+          <t>HASLS22260900165</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2798,7 +2797,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610061900</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2809,7 +2808,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2873,12 +2872,12 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900165</t>
+          <t>HASLS22260900187</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2888,7 +2887,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202609282100</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2899,22 +2898,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2924,22 +2923,22 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>0</v>
@@ -2963,22 +2962,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900187</t>
+          <t>HASLS22260900201</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610172300</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2989,22 +2988,22 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3014,12 +3013,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09CONSOL</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
@@ -3029,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>0</v>
@@ -3053,22 +3052,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900201</t>
+          <t>HASLS22260900206</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610030500</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -3079,22 +3078,22 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3109,7 +3108,8 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
+ EXTEND CLS TIME : 30/09 @23.59 </t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="2" t="n">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900206</t>
+          <t>HASLS22260900207</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610192000</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3199,8 +3199,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
- EXTEND CLS TIME : 30/09 @23.59 </t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
@@ -3234,7 +3233,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900207</t>
+          <t>HASLS22260900323</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3244,12 +3243,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610192000</t>
+          <t>202609282100</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3260,47 +3259,48 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+</t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="2" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900323</t>
+          <t>HASLS22260900717</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3355,134 +3355,134 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>CONTAINER GRADE A</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 23/09/26 CLS TIME 24/09 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900780</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>202609282100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>20260925</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>NOODLE</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL FOODS SUPPLY CO., LTD</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SYRUP</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST : The container is in good condition, with no signs of rust or leakage.</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900717</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KMGY</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>202609282100</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>THAI ARROW PRODUCTS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>RAW MATERIAL</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>CONTAINER GRADE A</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 23/09/26 CLS TIME 24/09 @17.00HRS 
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>0</v>
@@ -3506,22 +3506,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900780</t>
+          <t>HASLS22260900789</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3537,43 +3537,42 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>INDUSTRIAL FOODS SUPPLY CO., LTD</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>SYRUP</t>
+          <t>MIX-LOAD</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>REQUEST : The container is in good condition, with no signs of rust or leakage.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>0</v>
@@ -3597,12 +3596,12 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900789</t>
+          <t>HASLS22260900896</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3612,7 +3611,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610031300</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3623,27 +3622,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>MIX-LOAD</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3653,17 +3652,17 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-01CONSOL</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>0</v>
@@ -3687,22 +3686,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900896</t>
+          <t>HASLS22260901096</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610061900</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3713,7 +3712,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3723,27 +3722,28 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-01CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.28/09/26 CLS TIME CFS DD.28/09/26- 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
@@ -3777,22 +3777,22 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901096</t>
+          <t>HASLS22260901130</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610100900</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3803,48 +3803,48 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.28/09/26 CLS TIME CFS DD.28/09/26- 17:00HRS.
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901130</t>
+          <t>HASLS22260901132</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202610122300</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -3959,12 +3959,12 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901132</t>
+          <t>HASLS22260901157</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610122300</t>
+          <t>202610100900</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -4010,13 +4010,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
@@ -4050,22 +4049,22 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901157</t>
+          <t>HASLS22260901158</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202610112300</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -4086,7 +4085,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4106,7 +4105,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
@@ -4140,22 +4139,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901158</t>
+          <t>HASLS22260901170</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610051100</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -4166,22 +4165,22 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -4196,7 +4195,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
@@ -4206,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="2" t="n">
         <v>0</v>
@@ -4230,22 +4229,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901170</t>
+          <t>HASLS22260901291</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610112300</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4256,7 +4255,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4266,17 +4265,17 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>GRANDLINK LOGISTICS CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4286,7 +4285,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
@@ -4320,22 +4319,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901291</t>
+          <t>HASLS22260901391</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610061900</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4351,42 +4350,42 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>0</v>
@@ -4410,22 +4409,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901391</t>
+          <t>HASLS22260901414</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4441,42 +4440,42 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>V.C.E. COMPANY LIMITED</t>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>TAPIOCA STARCH</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q44" s="2" t="n">
         <v>0</v>
@@ -4500,22 +4499,22 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901414</t>
+          <t>HASLS22260901553</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610112300</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4531,32 +4530,33 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>0</v>
@@ -4590,22 +4590,22 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901553</t>
+          <t>HASLS22260901567</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610061900</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4621,33 +4621,32 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>CONSOL
-CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
@@ -4657,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>0</v>
@@ -4681,22 +4680,22 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901567</t>
+          <t>HASLS22260901602</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610051100</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4707,12 +4706,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -4722,12 +4721,12 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -4741,13 +4740,13 @@
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="2" t="n">
         <v>0</v>
@@ -4771,22 +4770,22 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901602</t>
+          <t>HASLS22260901603</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610112300</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4807,7 +4806,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4827,7 +4826,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
@@ -4861,22 +4860,22 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901603</t>
+          <t>HASLS22260901655</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610122300</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -4887,12 +4886,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4902,22 +4901,22 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>MRD-ECC CO.,LTD.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>BALL CLAY</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
         </is>
       </c>
       <c r="N49" s="2" t="n">
@@ -4927,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>0</v>
@@ -4951,7 +4950,7 @@
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901655</t>
+          <t>HASLS22260901755</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4982,42 +4981,43 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>MRD-ECC CO.,LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>BALL CLAY</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q50" s="2" t="n">
         <v>0</v>
@@ -5041,22 +5041,22 @@
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901753</t>
+          <t>HASLS22260901803</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610030500</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -5067,48 +5067,48 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>WISUNO ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>TRANSFORMER</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26 - 17:00HRS.
-</t>
+          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>0</v>
@@ -5132,12 +5132,12 @@
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901755</t>
+          <t>HASLS22260901816</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>202610122300</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -5173,33 +5173,32 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="2" t="n">
         <v>0</v>
@@ -5223,22 +5222,22 @@
     <row r="53" ht="13" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901803</t>
+          <t>HASLS22260901887</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610100900</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -5259,28 +5258,28 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>WISUNO ELECTRONICS CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>TRANSFORMER</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
-CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
+**1ST RETURN CNTR DD.07/10/2026**</t>
         </is>
       </c>
       <c r="N53" s="2" t="n">
@@ -5314,22 +5313,22 @@
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901816</t>
+          <t>HASLS22260901979</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610112300</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -5345,17 +5344,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -5365,22 +5364,23 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q54" s="2" t="n">
         <v>0</v>
@@ -5404,12 +5404,12 @@
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901881</t>
+          <t>HASLS22260901980</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>202609270130</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -5435,17 +5435,17 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -5455,24 +5455,23 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-24, Return : 2026-09-24 CONSOL
-*1ST CY CNTR DD.23/09/2026* 
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
       <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q55" s="2" t="n">
         <v>0</v>
@@ -5496,12 +5495,12 @@
     <row r="56" ht="13" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901887</t>
+          <t>HASLS22260902097</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5511,7 +5510,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202610122300</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -5522,17 +5521,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -5542,7 +5541,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5552,18 +5551,17 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
-**1ST RETURN CNTR DD.07/10/2026**</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q56" s="2" t="n">
         <v>0</v>
@@ -5587,22 +5585,22 @@
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901979</t>
+          <t>HASLS22260902170</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -5613,48 +5611,47 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FOOD STUFFS</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
-</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
         </is>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="2" t="n">
         <v>0</v>
@@ -5678,22 +5675,22 @@
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901980</t>
+          <t>HASLS22260902198</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610112300</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -5709,17 +5706,17 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -5729,13 +5726,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
-</t>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
@@ -5745,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="2" t="n">
         <v>0</v>
@@ -5769,12 +5765,12 @@
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902097</t>
+          <t>HASLS22260902237</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5784,7 +5780,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>202610122300</t>
+          <t>202609270130</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -5795,27 +5791,27 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -5825,17 +5821,18 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL
+(1ST CY 23/09/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="2" t="n">
         <v>0</v>
@@ -5857,298 +5854,118 @@
       </c>
     </row>
     <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902170</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFFS</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902198</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>202610112300</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="n"/>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3">
-        <f>SUM(N2:N61)</f>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3">
+        <f>SUM(N2:N59)</f>
         <v/>
       </c>
-      <c r="O62" s="3">
-        <f>SUM(O2:O61)</f>
+      <c r="O60" s="3">
+        <f>SUM(O2:O59)</f>
         <v/>
       </c>
-      <c r="P62" s="3">
-        <f>SUM(P2:P61)</f>
+      <c r="P60" s="3">
+        <f>SUM(P2:P59)</f>
         <v/>
       </c>
-      <c r="Q62" s="3">
-        <f>SUM(Q2:Q61)</f>
+      <c r="Q60" s="3">
+        <f>SUM(Q2:Q59)</f>
         <v/>
       </c>
-      <c r="R62" s="3">
-        <f>SUM(R2:R61)</f>
+      <c r="R60" s="3">
+        <f>SUM(R2:R59)</f>
         <v/>
       </c>
-      <c r="S62" s="3">
-        <f>SUM(S2:S61)</f>
+      <c r="S60" s="3">
+        <f>SUM(S2:S59)</f>
         <v/>
       </c>
-      <c r="T62" s="3">
-        <f>SUM(T2:T61)</f>
+      <c r="T60" s="3">
+        <f>SUM(T2:T59)</f>
         <v/>
       </c>
-      <c r="U62" s="3">
-        <f>SUM(U2:U61)</f>
+      <c r="U60" s="3">
+        <f>SUM(U2:U59)</f>
         <v/>
       </c>
-      <c r="V62" s="3">
-        <f>SUM(V2:V61)</f>
+      <c r="V60" s="3">
+        <f>SUM(V2:V59)</f>
         <v/>
       </c>
     </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
     <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>86</v>
+      <c r="B66" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V61"/>
+  <autoFilter ref="A1:V59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="109" customWidth="1" min="13" max="13"/>
+    <col width="119" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -704,7 +704,7 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260800761</t>
+          <t>HASLS22260801149</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -735,43 +735,42 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>PET FOOD</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-24, Return : 2026-09-25 CONSOL 
-</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -795,7 +794,7 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801149</t>
+          <t>HASLS22260801150</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -810,7 +809,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610192000</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -885,22 +884,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801150</t>
+          <t>HASLS22260801209</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610192000</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -911,47 +910,47 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>PET FOOD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
@@ -975,12 +974,12 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801209</t>
+          <t>HASLS22260801210</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -990,7 +989,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1011,7 +1010,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1031,7 +1030,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
@@ -1065,12 +1064,12 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801210</t>
+          <t>HASLS22260801230</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1080,7 +1079,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1096,22 +1095,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1121,7 +1120,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
@@ -1131,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
@@ -1155,22 +1154,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801229</t>
+          <t>HASLS22260801789</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610130700</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1181,7 +1180,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1191,27 +1190,28 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-18, Return : 2026-09-18 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
@@ -1245,22 +1245,22 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801230</t>
+          <t>HASLS22260801791</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610030900</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1281,27 +1281,28 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.01/10/26 CLS TIME CFS DD.01/10/26 - 17:00HRS. 
+</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
@@ -1335,22 +1336,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801443</t>
+          <t>HASLS22260801991</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1361,7 +1362,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1371,17 +1372,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1391,7 +1392,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
@@ -1425,7 +1426,7 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801462</t>
+          <t>HASLS22260802037</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1435,12 +1436,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1456,32 +1457,33 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>FIVE PAGODAS PHARMACY CO.,LTD</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>YA HOM FIVE PAGODAS BRAND (MEDICINE)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/11/26 CLS TIME CFS DD.16/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
@@ -1491,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -1515,12 +1517,12 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801786</t>
+          <t>HASLS22260802180</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1530,7 +1532,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610110900</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1541,38 +1543,37 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.29/09/26 CLS TIME CFS DD.30/09/26 - 17:00HRS.
-</t>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
@@ -1582,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>0</v>
@@ -1606,22 +1607,22 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801789</t>
+          <t>HASLS22260802450</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1632,37 +1633,37 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.02/10/26 *CLS TIME CFS DD.02/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
@@ -1672,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0</v>
@@ -1696,22 +1697,22 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801791</t>
+          <t>HASLS22260802590</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1732,28 +1733,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO / CONSOL</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.30/09/26 CLS TIME CFS DD.01/10/26 - 17:00HRS. 
-</t>
+          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
@@ -1787,22 +1787,22 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801991</t>
+          <t>HASLS22260802591</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610030900</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO / CONSOL</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-01 CONSOL</t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0</v>
@@ -1877,12 +1877,12 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801996</t>
+          <t>HASLS22260900064</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1933,8 +1933,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-25, Return : 2026-09-25 CONSOL 
-</t>
+          <t>Pickup : 2026-09-30, Return : 2026-09-30 CONSOL</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
@@ -1968,22 +1967,22 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802180</t>
+          <t>HASLS22260900165</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1999,17 +1998,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2024,17 +2023,17 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>0</v>
@@ -2058,12 +2057,12 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802238</t>
+          <t>HASLS22260900201</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2073,7 +2072,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610210400</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2084,48 +2083,47 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>PERM POON PATANA INDUSTRY CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>COTTON BALLS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>GOOD &amp; CLEAN CNTR</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
- </t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0</v>
@@ -2149,22 +2147,22 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802382</t>
+          <t>HASLS22260900204</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610282200</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2175,7 +2173,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2185,12 +2183,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2205,7 +2203,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-17, Return : 2026-09-18  CONSOL </t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
@@ -2239,12 +2237,12 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802450</t>
+          <t>HASLS22260900206</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2254,7 +2252,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2265,22 +2263,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2295,7 +2293,8 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
+ EXTEND CLS TIME : 30/09 @23.59 </t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
@@ -2305,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="2" t="n">
         <v>0</v>
@@ -2329,7 +2328,7 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802541</t>
+          <t>HASLS22260900207</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2339,12 +2338,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2355,22 +2354,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2385,17 +2384,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-18, Return : 2026-09-18 CONSOL </t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>0</v>
@@ -2419,22 +2418,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802590</t>
+          <t>HASLS22260900628</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2445,47 +2444,48 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>SAHAPARA RUBBER CO.,LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>NATURAL RUBBER</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.13/10/26 - 17:00HRS.*.
+(1ST CFS 12/10/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>0</v>
@@ -2509,12 +2509,12 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802591</t>
+          <t>HASLS22260900691</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610270900</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2545,17 +2545,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 24-25/09/2026 (CONSOL)</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
@@ -2599,12 +2599,12 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900019</t>
+          <t>HASLS22260900789</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2625,50 +2625,47 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>JPKCZ</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>SIAM TOKAI CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>BRINE CURED GINGER</t>
+          <t>MIX-LOAD</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Remark: Food grade container, Good and Clean
-container, no hole, no rust, no oil stain, no
-splinter</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/09/26 CLS TIME CFS DD.23/09/26 - 17:00HRS.
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>0</v>
@@ -2692,22 +2689,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900064</t>
+          <t>HASLS22260900896</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610030900</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2718,7 +2715,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2733,12 +2730,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2748,7 +2745,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-09-30 CONSOL</t>
+          <t>Pickup : 2026-09-30, Return : 2026-10-01CONSOL</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
@@ -2782,12 +2779,12 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900165</t>
+          <t>HASLS22260900901</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2797,7 +2794,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610210400</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2808,22 +2805,22 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2838,17 +2835,17 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>0</v>
@@ -2872,12 +2869,12 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900187</t>
+          <t>HASLS22260901096</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2887,7 +2884,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2903,42 +2900,43 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 17-18/09/2026 (CONSOL)</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>0</v>
@@ -2962,22 +2960,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900201</t>
+          <t>HASLS22260901130</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610110900</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2993,17 +2991,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3013,12 +3011,13 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
@@ -3028,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>0</v>
@@ -3052,22 +3051,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900206</t>
+          <t>HASLS22260901132</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610130700</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -3078,7 +3077,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3088,12 +3087,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3103,13 +3102,13 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
- EXTEND CLS TIME : 30/09 @23.59 </t>
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
@@ -3143,22 +3142,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900207</t>
+          <t>HASLS22260901133</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610192000</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3169,7 +3168,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3179,12 +3178,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3194,12 +3193,13 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
@@ -3233,22 +3233,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900323</t>
+          <t>HASLS22260901134</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610172300</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3259,48 +3259,48 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q31" s="2" t="n">
         <v>0</v>
@@ -3324,22 +3324,22 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900717</t>
+          <t>HASLS22260901157</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610110900</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3360,28 +3360,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>RAW MATERIAL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER GRADE A</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 23/09/26 CLS TIME 24/09 @17.00HRS 
-</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
@@ -3415,22 +3414,22 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900780</t>
+          <t>HASLS22260901158</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202609282100</t>
+          <t>202610120800</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3446,43 +3445,42 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>INDUSTRIAL FOODS SUPPLY CO., LTD</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>SYRUP</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>REQUEST : The container is in good condition, with no signs of rust or leakage.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 25/09/26 CLS TIME 25/09 @17.00HRS 
-</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>0</v>
@@ -3506,22 +3504,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900789</t>
+          <t>HASLS22260901159</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3542,7 +3540,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3552,7 +3550,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>MIX-LOAD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3562,7 +3560,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
@@ -3596,22 +3594,22 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900896</t>
+          <t>HASLS22260901170</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610031300</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3622,27 +3620,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3652,17 +3650,17 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-01CONSOL</t>
+          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>0</v>
@@ -3686,22 +3684,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901096</t>
+          <t>HASLS22260901291</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610120800</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3717,43 +3715,42 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.28/09/26 CLS TIME CFS DD.28/09/26- 17:00HRS.
-</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>0</v>
@@ -3777,12 +3774,12 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901130</t>
+          <t>HASLS22260901292</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3792,7 +3789,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3803,7 +3800,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3813,28 +3810,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
@@ -3868,22 +3864,22 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901132</t>
+          <t>HASLS22260901391</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610122300</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3894,48 +3890,47 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
-</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="2" t="n">
         <v>0</v>
@@ -3959,22 +3954,22 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901157</t>
+          <t>HASLS22260901507</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610100900</t>
+          <t>202610211800</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3985,22 +3980,22 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -4015,7 +4010,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
@@ -4025,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>0</v>
@@ -4049,7 +4044,7 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901158</t>
+          <t>HASLS22260901553</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4064,7 +4059,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610120800</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -4080,7 +4075,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4090,22 +4085,23 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
@@ -4115,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q40" s="2" t="n">
         <v>0</v>
@@ -4139,22 +4135,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901170</t>
+          <t>HASLS22260901556</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -4165,37 +4161,37 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>GRANDLINK LOGISTICS CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
@@ -4205,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q41" s="2" t="n">
         <v>0</v>
@@ -4229,22 +4225,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901291</t>
+          <t>HASLS22260901557</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>TSXM</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610192100</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4260,32 +4256,33 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL 
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
@@ -4295,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>0</v>
@@ -4319,7 +4316,7 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901391</t>
+          <t>HASLS22260901567</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -4334,7 +4331,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610071700</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4350,42 +4347,42 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>V.C.E. COMPANY LIMITED</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>TAPIOCA STARCH</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>0</v>
@@ -4409,22 +4406,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901414</t>
+          <t>HASLS22260901602</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4435,27 +4432,27 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4465,11 +4462,11 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>0</v>
@@ -4499,7 +4496,7 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901553</t>
+          <t>HASLS22260901603</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -4514,7 +4511,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610120800</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4525,12 +4522,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -4540,18 +4537,17 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CONSOL
-CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -4560,13 +4556,13 @@
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>0</v>
@@ -4590,12 +4586,12 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901567</t>
+          <t>HASLS22260901604</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4605,7 +4601,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610061900</t>
+          <t>202610210400</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4616,27 +4612,27 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4646,17 +4642,17 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>0</v>
@@ -4680,22 +4676,22 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901602</t>
+          <t>HASLS22260901654</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202610051100</t>
+          <t>202610210400</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4706,47 +4702,49 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>MINERAL RESOURCES DEVELOPMENT CO., LTD.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>KAOLIN</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 
+CLS TIME CFS DD.16/10/26 - 17:00HRS. *1ST CFS DD.15/10/2026*
+</t>
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="2" t="n">
         <v>0</v>
@@ -4770,22 +4768,22 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901603</t>
+          <t>HASLS22260901655</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610130700</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4796,12 +4794,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -4811,22 +4809,22 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>MRD-ECC CO.,LTD.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>BALL CLAY</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
@@ -4836,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="2" t="n">
         <v>0</v>
@@ -4860,22 +4858,22 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901655</t>
+          <t>HASLS22260901752</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>202610122300</t>
+          <t>202610172300</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -4886,7 +4884,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4896,27 +4894,27 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>MRD-ECC CO.,LTD.</t>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>BALL CLAY</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N49" s="2" t="n">
@@ -4965,7 +4963,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>202610122300</t>
+          <t>202610130700</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -5041,12 +5039,12 @@
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901803</t>
+          <t>HASLS22260901756</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -5056,7 +5054,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>202610030500</t>
+          <t>202610210400</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -5067,591 +5065,593 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901758</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>202610211800</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901803</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>202610060900</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>WISUNO ELECTRONICS CO., LTD.</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>TRANSFORMER</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
 CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
         </is>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="N53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>HASLS22260901816</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>KJT</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>202610141800</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>20261009</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="N54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>HASLS22260901887</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SWSR</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>202610100900</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202610110900</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>20261005</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
 **1ST RETURN CNTR DD.07/10/2026**</t>
         </is>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="N55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>HASLS22260901979</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>KMTP</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>2612N</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>202610112300</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>202610120800</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>20261008</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>(CONSOL)</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
-      <c r="N54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="n">
+      <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>HASLS22260901980</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>KJT</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>202610141800</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>20261009</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>(CONSOL)</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
-      <c r="N55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="n">
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902097</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>202610122300</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902170</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFFS</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q57" s="2" t="n">
         <v>0</v>
@@ -5675,22 +5675,22 @@
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902198</t>
+          <t>HASLS22260902097</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>202610112300</t>
+          <t>202610130700</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -5701,27 +5701,27 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="2" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902237</t>
+          <t>HASLS22260902130</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>202609270130</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -5791,181 +5791,1265 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902170</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902198</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>202610120800</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902264</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>20260917</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902282</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>202610210400</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-17, Return : 2026-09-18 CONSOL
-(1ST CY 23/09/26 WO/RENT)</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="n">
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-      <c r="J60" s="3" t="n"/>
-      <c r="K60" s="3" t="n"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3">
-        <f>SUM(N2:N59)</f>
-        <v/>
-      </c>
-      <c r="O60" s="3">
-        <f>SUM(O2:O59)</f>
-        <v/>
-      </c>
-      <c r="P60" s="3">
-        <f>SUM(P2:P59)</f>
-        <v/>
-      </c>
-      <c r="Q60" s="3">
-        <f>SUM(Q2:Q59)</f>
-        <v/>
-      </c>
-      <c r="R60" s="3">
-        <f>SUM(R2:R59)</f>
-        <v/>
-      </c>
-      <c r="S60" s="3">
-        <f>SUM(S2:S59)</f>
-        <v/>
-      </c>
-      <c r="T60" s="3">
-        <f>SUM(T2:T59)</f>
-        <v/>
-      </c>
-      <c r="U60" s="3">
-        <f>SUM(U2:U59)</f>
-        <v/>
-      </c>
-      <c r="V60" s="3">
-        <f>SUM(V2:V59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>29</v>
+          <t>HASLS22260902324</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>202610172300</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>HASLS22260902404</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>202610211800</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x12 </t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 19/10 @17.00HRS 
+ 1ST CFS : 16/10 W/O RENT</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902431</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFF</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
+ CARGO G.W. : 4.5 TONS </t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902434</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>202610282200</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902453</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902454</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>202610172300</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
+ CLS TIME 15/10 @23.59 </t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="13" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902455</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>202610210400</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="13" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902575</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>202610030900</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>**DO NOT RELEASE CTNR PLS WAIT APPROVAL**DG45GPx1 (CLS 8 / UN 1903)</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>**DO NOT RELEASE CTNR PLS WAIT APPROVAL**
+Pickup : 2026-10-01, Return : 2026-10-01 DG45GPx1 (CLS 8 / UN 1903) CONSOL</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="13" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3">
+        <f>SUM(N2:N71)</f>
+        <v/>
+      </c>
+      <c r="O72" s="3">
+        <f>SUM(O2:O71)</f>
+        <v/>
+      </c>
+      <c r="P72" s="3">
+        <f>SUM(P2:P71)</f>
+        <v/>
+      </c>
+      <c r="Q72" s="3">
+        <f>SUM(Q2:Q71)</f>
+        <v/>
+      </c>
+      <c r="R72" s="3">
+        <f>SUM(R2:R71)</f>
+        <v/>
+      </c>
+      <c r="S72" s="3">
+        <f>SUM(S2:S71)</f>
+        <v/>
+      </c>
+      <c r="T72" s="3">
+        <f>SUM(T2:T71)</f>
+        <v/>
+      </c>
+      <c r="U72" s="3">
+        <f>SUM(U2:U71)</f>
+        <v/>
+      </c>
+      <c r="V72" s="3">
+        <f>SUM(V2:V71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="13" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="13" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="77" ht="13" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
           <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="B77" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" ht="13" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>84</v>
+      <c r="B78" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V59"/>
+  <autoFilter ref="A1:V71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.02/10/26 *CLS TIME CFS DD.02/10/26 - 17:00HRS.*
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.05/10/26 *CLS TIME CFS DD.05/10/26 - 17:00HRS.*
 </t>
         </is>
       </c>
@@ -704,22 +704,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801149</t>
+          <t>HASLS22260801209</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -730,47 +730,47 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>PET FOOD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -794,22 +794,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801150</t>
+          <t>HASLS22260801210</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -820,47 +820,47 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CHOTIWAT MANUFACTURING PUBLIC COMPANY LIMITED</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PET FOOD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801209</t>
+          <t>HASLS22260801230</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -915,22 +915,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
@@ -974,22 +974,22 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801210</t>
+          <t>HASLS22260801789</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610140400</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1000,37 +1000,38 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
@@ -1040,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1064,22 +1065,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801230</t>
+          <t>HASLS22260801791</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610032000</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1100,27 +1101,28 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.01/10/26 CLS TIME CFS DD.01/10/26 - 17:00HRS. 
+</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
@@ -1154,22 +1156,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801789</t>
+          <t>HASLS22260801991</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610130700</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1180,42 +1182,41 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
-</t>
+          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>0</v>
@@ -1245,22 +1246,22 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801791</t>
+          <t>HASLS22260802037</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610030900</t>
+          <t>202610172300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1271,48 +1272,48 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>FIVE PAGODAS PHARMACY CO.,LTD</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>YA HOM FIVE PAGODAS BRAND (MEDICINE)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.01/10/26 CLS TIME CFS DD.01/10/26 - 17:00HRS. 
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -1336,22 +1337,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801991</t>
+          <t>HASLS22260802180</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610112200</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1362,22 +1363,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1392,17 +1393,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1426,22 +1427,22 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802037</t>
+          <t>HASLS22260802450</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1452,48 +1453,47 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>FIVE PAGODAS PHARMACY CO.,LTD</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>YA HOM FIVE PAGODAS BRAND (MEDICINE)</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/11/26 CLS TIME CFS DD.16/10/26 - 17:00HRS.
-</t>
+          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -1517,22 +1517,22 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802180</t>
+          <t>HASLS22260802590</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202610110900</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO / CONSOL</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802450</t>
+          <t>HASLS22260802591</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610032000</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1633,27 +1633,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO / CONSOL</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-01 CONSOL</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0</v>
@@ -1697,22 +1697,22 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802590</t>
+          <t>HASLS22260900064</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1723,27 +1723,27 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1753,17 +1753,17 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
+          <t>Pickup : 2026-09-30, Return : 2026-09-30 CONSOL</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
         <v>0</v>
@@ -1787,22 +1787,22 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802591</t>
+          <t>HASLS22260900165</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610030900</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1813,27 +1813,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-01 CONSOL</t>
+          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0</v>
@@ -1877,12 +1877,12 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900064</t>
+          <t>HASLS22260900201</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1903,22 +1903,22 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1933,17 +1933,17 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-09-30 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900165</t>
+          <t>HASLS22260900204</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610290800</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2023,17 +2023,17 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>0</v>
@@ -2057,12 +2057,12 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900201</t>
+          <t>HASLS22260900206</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610210400</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2113,7 +2113,8 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
+ EXTEND CLS TIME : 30/09 @23.59 </t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
@@ -2123,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0</v>
@@ -2147,12 +2148,12 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900204</t>
+          <t>HASLS22260900207</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2162,7 +2163,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610282200</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2173,17 +2174,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2203,7 +2204,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
@@ -2213,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0</v>
@@ -2237,22 +2238,22 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900206</t>
+          <t>HASLS22260900628</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2263,48 +2264,48 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>SAHAPARA RUBBER CO.,LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NATURAL RUBBER</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
- EXTEND CLS TIME : 30/09 @23.59 </t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.13/10/26 - 17:00HRS.*.
+(1ST CFS 12/10/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
         <v>0</v>
@@ -2328,12 +2329,12 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900207</t>
+          <t>HASLS22260900691</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2343,7 +2344,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610270900</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2364,7 +2365,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2384,7 +2385,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
@@ -2418,7 +2419,7 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900628</t>
+          <t>HASLS22260900789</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2444,48 +2445,47 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>SAHAPARA RUBBER CO.,LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER</t>
+          <t>MIX-LOAD</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.13/10/26 - 17:00HRS.*.
-(1ST CFS 12/10/26 WO/RENT)</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>0</v>
@@ -2509,12 +2509,12 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900691</t>
+          <t>HASLS22260900896</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610270900</t>
+          <t>202610032000</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2535,27 +2535,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-09-30, Return : 2026-10-01CONSOL</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>0</v>
@@ -2599,22 +2599,22 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900789</t>
+          <t>HASLS22260900901</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2625,27 +2625,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>MIX-LOAD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>0</v>
@@ -2689,22 +2689,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900896</t>
+          <t>HASLS22260901096</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610030900</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2725,27 +2725,28 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-10-01CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
@@ -2779,22 +2780,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900901</t>
+          <t>HASLS22260901130</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610210400</t>
+          <t>202610112200</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2805,22 +2806,22 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2830,12 +2831,13 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
@@ -2845,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>0</v>
@@ -2869,22 +2871,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901096</t>
+          <t>HASLS22260901132</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610140400</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2895,48 +2897,48 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>0</v>
@@ -2960,22 +2962,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901130</t>
+          <t>HASLS22260901133</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610110900</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2996,7 +2998,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3016,7 +3018,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -3051,22 +3053,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901132</t>
+          <t>HASLS22260901134</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610130700</t>
+          <t>202610172300</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -3087,7 +3089,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3107,7 +3109,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -3142,22 +3144,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901133</t>
+          <t>HASLS22260901157</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610112200</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3168,7 +3170,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3178,12 +3180,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3193,13 +3195,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
@@ -3233,22 +3234,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901134</t>
+          <t>HASLS22260901158</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3259,7 +3260,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3269,12 +3270,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -3284,13 +3285,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
@@ -3324,22 +3324,22 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901157</t>
+          <t>HASLS22260901159</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202610110900</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
@@ -3414,22 +3414,22 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901158</t>
+          <t>HASLS22260901170</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202610120800</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3440,22 +3440,22 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N33" s="2" t="n">
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>0</v>
@@ -3504,12 +3504,12 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901159</t>
+          <t>HASLS22260901291</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3535,22 +3535,22 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>0</v>
@@ -3594,22 +3594,22 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901170</t>
+          <t>HASLS22260901292</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610201000</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3620,27 +3620,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>GRANDLINK LOGISTICS CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-29, Return : 2026-09-30 CONSOL</t>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>0</v>
@@ -3684,22 +3684,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901291</t>
+          <t>HASLS22260901391</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610120800</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3715,42 +3715,42 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>0</v>
@@ -3774,22 +3774,22 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901292</t>
+          <t>HASLS22260901507</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610211800</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3800,27 +3800,27 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>0</v>
@@ -3864,22 +3864,22 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901391</t>
+          <t>HASLS22260901553</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3895,42 +3895,43 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>V.C.E. COMPANY LIMITED</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>TAPIOCA STARCH</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q38" s="2" t="n">
         <v>0</v>
@@ -3954,12 +3955,12 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901507</t>
+          <t>HASLS22260901556</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3969,7 +3970,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610211800</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3980,37 +3981,37 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
@@ -4020,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>0</v>
@@ -4044,22 +4045,22 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901553</t>
+          <t>HASLS22260901557</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>TSXM</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610120800</t>
+          <t>202610252200</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -4080,7 +4081,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4095,13 +4096,13 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>CONSOL
+          <t>CONSOL 
 CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
@@ -4135,22 +4136,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901556</t>
+          <t>HASLS22260901567</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610080400</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -4166,32 +4167,32 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
@@ -4201,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="2" t="n">
         <v>0</v>
@@ -4225,22 +4226,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901557</t>
+          <t>HASLS22260901602</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610192100</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4251,48 +4252,47 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>CONSOL 
-CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
+          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901567</t>
+          <t>HASLS22260901603</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610071700</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4342,27 +4342,27 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -4372,17 +4372,17 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>0</v>
@@ -4406,22 +4406,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901602</t>
+          <t>HASLS22260901604</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
@@ -4496,22 +4496,22 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901603</t>
+          <t>HASLS22260901654</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202610120800</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4522,223 +4522,223 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>MINERAL RESOURCES DEVELOPMENT CO., LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>KAOLIN</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901604</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>202610210400</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO CONSOL</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901654</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>202610210400</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x4 </t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>MINERAL RESOURCES DEVELOPMENT CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>KAOLIN</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 
 CLS TIME CFS DD.16/10/26 - 17:00HRS. *1ST CFS DD.15/10/2026*
 </t>
         </is>
       </c>
+      <c r="N45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901655</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>202610140400</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>MRD-ECC CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901752</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>202610172300</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901655</t>
+          <t>HASLS22260901755</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610130700</t>
+          <t>202610140400</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4799,42 +4799,43 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>MRD-ECC CO.,LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>BALL CLAY</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q48" s="2" t="n">
         <v>0</v>
@@ -4858,22 +4859,22 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901752</t>
+          <t>HASLS22260901756</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -4884,12 +4885,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4899,32 +4900,33 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>0</v>
@@ -4948,22 +4950,22 @@
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901755</t>
+          <t>HASLS22260901758</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>202610130700</t>
+          <t>202610211800</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -4984,7 +4986,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5004,7 +5006,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
@@ -5039,12 +5041,12 @@
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901756</t>
+          <t>HASLS22260901803</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -5054,7 +5056,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>202610210400</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -5065,48 +5067,48 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>WISUNO ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>TRANSFORMER</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
-</t>
+          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>0</v>
@@ -5130,22 +5132,22 @@
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901758</t>
+          <t>HASLS22260901816</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>202610211800</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -5156,48 +5158,47 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="2" t="n">
         <v>0</v>
@@ -5221,22 +5222,22 @@
     <row r="53" ht="13" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901803</t>
+          <t>HASLS22260901887</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610112200</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -5257,28 +5258,28 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>WISUNO ELECTRONICS CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>TRANSFORMER</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
-CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
+**1ST RETURN CNTR DD.07/10/2026**</t>
         </is>
       </c>
       <c r="N53" s="2" t="n">
@@ -5312,22 +5313,22 @@
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901816</t>
+          <t>HASLS22260901979</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -5343,17 +5344,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -5363,22 +5364,23 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q54" s="2" t="n">
         <v>0</v>
@@ -5402,12 +5404,12 @@
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901887</t>
+          <t>HASLS22260901980</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5417,7 +5419,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>202610110900</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -5433,17 +5435,17 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -5453,23 +5455,23 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
-**1ST RETURN CNTR DD.07/10/2026**</t>
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q55" s="2" t="n">
         <v>0</v>
@@ -5493,22 +5495,22 @@
     <row r="56" ht="13" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901979</t>
+          <t>HASLS22260902097</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>202610120800</t>
+          <t>202610140400</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -5519,7 +5521,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -5529,28 +5531,27 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
@@ -5584,22 +5585,22 @@
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901980</t>
+          <t>HASLS22260902130</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -5620,28 +5621,27 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
         </is>
       </c>
       <c r="N57" s="2" t="n">
@@ -5675,12 +5675,12 @@
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902097</t>
+          <t>HASLS22260902170</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>202610130700</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -5701,47 +5701,47 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>FOOD STUFFS</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="2" t="n">
         <v>0</v>
@@ -5765,12 +5765,12 @@
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902130</t>
+          <t>HASLS22260902198</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -5791,27 +5791,27 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N59" s="2" t="n">
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="2" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="60" ht="13" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902170</t>
+          <t>HASLS22260902264</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
+          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -5911,7 +5911,8 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.09/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
@@ -5945,22 +5946,22 @@
     <row r="61" ht="13" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902198</t>
+          <t>HASLS22260902282</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>202610120800</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -5971,27 +5972,27 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -6001,7 +6002,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
         </is>
       </c>
       <c r="N61" s="2" t="n">
@@ -6011,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="2" t="n">
         <v>0</v>
@@ -6035,22 +6036,22 @@
     <row r="62" ht="13" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902264</t>
+          <t>HASLS22260902324</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610172300</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -6071,761 +6072,761 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902404</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>202610211800</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x12 </t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 19/10 @17.00HRS 
+1ST CFS : 16/10 W/O RENT</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902431</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFF</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
+ CARGO G.W. : 4.5 TONS </t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902434</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>202610290800</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902453</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902454</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>202610172300</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
+ CLS TIME 15/10 @23.59 </t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902455</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>202610220400</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902456</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>MAC-NELS SHIPPING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-30, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="13" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902510</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
           <t>20261012</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFFS</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>THAI EASTSUN FOOD INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SALTED GINGER</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Good and clean container for food grade</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="N70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902282</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>202610210400</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902324</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>202610172300</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902404</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>202610211800</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x12 </t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>BALL CLAY</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 19/10 @17.00HRS 
- 1ST CFS : 16/10 W/O RENT</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902431</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFF</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
- CARGO G.W. : 4.5 TONS </t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902434</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>202610282200</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902453</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="13" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902454</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>202610172300</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
- CLS TIME 15/10 @23.59 </t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="13" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902455</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>202610210400</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="O70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="2" t="n">
         <v>0</v>
@@ -6864,7 +6865,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>202610030900</t>
+          <t>202610032000</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -7016,10 +7017,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" ht="13" customHeight="1">
@@ -7029,10 +7030,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" ht="13" customHeight="1">

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V78"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="119" customWidth="1" min="13" max="13"/>
+    <col width="115" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -899,7 +899,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610140400</t>
+          <t>202610140000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610032000</t>
+          <t>202610031700</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-01, Return : 2026-10-01 CONSOL  </t>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-02 CONSOL </t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610191600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610112200</t>
+          <t>202610120700</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-24, Return : 2026-09-25 CONSOL</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-05 CONSOL</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>CY-RTN : 02/10/2026 (CONSOL)</t>
+          <t>CY-RTN : 06/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610032000</t>
+          <t>202610031700</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1787,12 +1787,12 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900165</t>
+          <t>HASLS22260900201</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900201</t>
+          <t>HASLS22260900204</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610220400</t>
+          <t>202610290800</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
@@ -1967,22 +1967,22 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900204</t>
+          <t>HASLS22260900206</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
+          <t>202610060900</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1993,22 +1993,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2023,7 +2023,8 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
+ EXTEND CLS TIME : 30/09 @23.59 </t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
@@ -2033,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>0</v>
@@ -2057,22 +2058,22 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900206</t>
+          <t>HASLS22260900207</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610201500</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2083,7 +2084,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2093,12 +2094,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2113,8 +2114,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
- EXTEND CLS TIME : 30/09 @23.59 </t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
@@ -2148,12 +2148,12 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900207</t>
+          <t>HASLS22260900628</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2174,47 +2174,48 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>SAHAPARA RUBBER CO.,LTD.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NATURAL RUBBER</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.13/10/26 - 17:00HRS.*.
+(1ST CFS 12/10/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0</v>
@@ -2238,12 +2239,12 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900628</t>
+          <t>HASLS22260900691</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2253,7 +2254,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610270900</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2264,48 +2265,47 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>SAHAPARA RUBBER CO.,LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.13/10/26 - 17:00HRS.*.
-(1ST CFS 12/10/26 WO/RENT)</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
         <v>0</v>
@@ -2329,12 +2329,12 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900691</t>
+          <t>HASLS22260900789</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610270900</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>MIX-LOAD</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
@@ -2419,22 +2419,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900789</t>
+          <t>HASLS22260900901</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610141800</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2445,27 +2445,27 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>MIX-LOAD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>0</v>
@@ -2509,22 +2509,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900896</t>
+          <t>HASLS22260901096</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610032000</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2545,27 +2545,28 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-10-01CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
@@ -2599,22 +2600,22 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900901</t>
+          <t>HASLS22260901130</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610220400</t>
+          <t>202610120700</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2625,22 +2626,22 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2650,12 +2651,13 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
@@ -2665,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>0</v>
@@ -2689,22 +2691,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901096</t>
+          <t>HASLS22260901132</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610140000</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2715,48 +2717,48 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0</v>
@@ -2780,22 +2782,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901130</t>
+          <t>HASLS22260901133</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610112200</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2816,7 +2818,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2836,7 +2838,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -2871,22 +2873,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901132</t>
+          <t>HASLS22260901134</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610140400</t>
+          <t>202610191600</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2907,7 +2909,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2927,7 +2929,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -2962,22 +2964,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901133</t>
+          <t>HASLS22260901157</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610120700</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2988,7 +2990,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2998,12 +3000,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3013,13 +3015,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
@@ -3053,22 +3054,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901134</t>
+          <t>HASLS22260901158</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -3079,7 +3080,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3089,12 +3090,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3104,13 +3105,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
@@ -3144,22 +3144,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901157</t>
+          <t>HASLS22260901159</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610112200</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
@@ -3234,22 +3234,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901158</t>
+          <t>HASLS22260901170</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610131500</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3260,22 +3260,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="2" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901159</t>
+          <t>HASLS22260901291</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3355,22 +3355,22 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="2" t="n">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901170</t>
+          <t>HASLS22260901292</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610201500</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3440,27 +3440,27 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>GRANDLINK LOGISTICS CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-02, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N33" s="2" t="n">
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>0</v>
@@ -3504,22 +3504,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901291</t>
+          <t>HASLS22260901391</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610131500</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3535,42 +3535,42 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>V.C.E. COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>0</v>
@@ -3594,22 +3594,22 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901292</t>
+          <t>HASLS22260901507</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610201000</t>
+          <t>202610221900</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3620,27 +3620,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>0</v>
@@ -3684,22 +3684,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901391</t>
+          <t>HASLS22260901553</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3715,42 +3715,43 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>V.C.E. COMPANY LIMITED</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>TAPIOCA STARCH</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.30/09/26 *CLS TIME CFS DD.01/10/26 - 17:00HRS.*</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>0</v>
@@ -3774,12 +3775,12 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901507</t>
+          <t>HASLS22260901556</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3789,7 +3790,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610211800</t>
+          <t>202610181700</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3800,37 +3801,37 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
@@ -3840,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>0</v>
@@ -3864,22 +3865,22 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901553</t>
+          <t>HASLS22260901557</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>TSXM</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610131500</t>
+          <t>202610252200</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3900,7 +3901,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3915,13 +3916,13 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>CONSOL
+          <t>CONSOL 
 CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
@@ -3955,22 +3956,22 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901556</t>
+          <t>HASLS22260901567</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610181700</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3986,32 +3987,32 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
+          <t>Pickup : 2026-10-02, Return : 2026-10-05 CONSOL</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
@@ -4021,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>0</v>
@@ -4045,22 +4046,22 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901557</t>
+          <t>HASLS22260901603</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610252200</t>
+          <t>202610131500</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -4071,48 +4072,47 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>CONSOL 
-CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="2" t="n">
         <v>0</v>
@@ -4136,12 +4136,12 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901567</t>
+          <t>HASLS22260901604</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610080400</t>
+          <t>202610220400</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -4162,27 +4162,27 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4192,17 +4192,17 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="2" t="n">
         <v>0</v>
@@ -4226,22 +4226,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901602</t>
+          <t>HASLS22260901655</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610140000</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4252,37 +4252,37 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>MRD-ECC CO.,LTD.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>BALL CLAY</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901603</t>
+          <t>HASLS22260901752</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610131500</t>
+          <t>202610191600</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4342,37 +4342,37 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
@@ -4382,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>0</v>
@@ -4406,22 +4406,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901604</t>
+          <t>HASLS22260901755</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610220400</t>
+          <t>202610140000</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4432,41 +4432,42 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>0</v>
@@ -4496,7 +4497,7 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901654</t>
+          <t>HASLS22260901756</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -4527,44 +4528,43 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>MINERAL RESOURCES DEVELOPMENT CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>KAOLIN</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 
-CLS TIME CFS DD.16/10/26 - 17:00HRS. *1ST CFS DD.15/10/2026*
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>0</v>
@@ -4588,22 +4588,22 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901655</t>
+          <t>HASLS22260901758</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610140400</t>
+          <t>202610221900</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4619,42 +4619,43 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>MRD-ECC CO.,LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>BALL CLAY</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.08/10/26 *CLS TIME CFS DD.09/10/26 - 17:00HRS.*  </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>0</v>
@@ -4678,22 +4679,22 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901752</t>
+          <t>HASLS22260901816</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202610172300</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4714,7 +4715,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4729,12 +4730,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N47" s="2" t="n">
@@ -4768,12 +4769,12 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901755</t>
+          <t>HASLS22260901887</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4783,7 +4784,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610140400</t>
+          <t>202610120700</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4794,1948 +4795,1946 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
+**1ST RETURN CNTR DD.07/10/2026**</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901979</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>202610131500</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901980</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902097</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>202610140000</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>20261009</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>FISHING NETS</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902130</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>202610181700</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902170</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902198</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>202610131500</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902264</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902282</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>202610220400</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902324</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>202610191600</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902404</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>202610221900</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x12 </t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 19/10 @17.00HRS 
+1ST CFS : 16/10 W/O RENT</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902431</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFF</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
+ CARGO G.W. : 4.5 TONS </t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902434</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>202610290800</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902453</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902454</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>202610191600</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
+ CLS TIME 15/10 @23.59 </t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902455</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>202610220400</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902456</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>MAC-NELS SHIPPING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-30, Return : 2026-10-02 CONSOL</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902510</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>202610141800</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>THAI EASTSUN FOOD INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SALTED GINGER</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Good and clean container for food grade</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902769</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>202610120700</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902771</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>202610181700</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902815</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>202610201500</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902833</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>202610140000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>SOMPHOL BEDDING AND MATTRESS INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>MATTRESS</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.09/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
+      <c r="N69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901756</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>202610220400</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>FISHING NETS</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
-</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901758</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>202610211800</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>FISHING NETS</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
-</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901803</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>SWDN</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>202610060900</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>WISUNO ELECTRONICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>TRANSFORMER</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>STUFFING DD.29/09/2026 @ PAT (SPORTLIGHT TOWER NO.2)
-CLS TIME DD.30/09/2026 @ 17.00 *1ST CFS DD.29/09/2026**</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901816</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901887</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SWSR</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>202610112200</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL
-**1ST RETURN CNTR DD.07/10/2026**</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901979</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>202610131500</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>(CONSOL)</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
-</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901980</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>(CONSOL)</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
-</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902097</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>202610140400</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902130</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SKOR</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>202610181700</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902170</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFFS</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902198</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>202610131500</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902264</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFFS</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
-</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902282</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>202610220400</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902324</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>202610172300</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902404</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>202610211800</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x12 </t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>BALL CLAY</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 19/10 @17.00HRS 
-1ST CFS : 16/10 W/O RENT</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902431</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFF</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
- CARGO G.W. : 4.5 TONS </t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902434</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>202610290800</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902453</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902454</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>202610172300</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
- CLS TIME 15/10 @23.59 </t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902455</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>202610220400</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="13" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902456</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>SWSP</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>202610071530</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>MAC-NELS SHIPPING (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-30, Return : 2026-10-02 CONSOL</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="O69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="2" t="n">
         <v>0</v>
@@ -6757,300 +6756,118 @@
       </c>
     </row>
     <row r="70" ht="13" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902510</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>202610141800</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>JPKCZ</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>THAI EASTSUN FOOD INDUSTRY CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>SALTED GINGER</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>Good and clean container for food grade</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
-</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="13" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902575</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>202610032000</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>**DO NOT RELEASE CTNR PLS WAIT APPROVAL**DG45GPx1 (CLS 8 / UN 1903)</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>**DO NOT RELEASE CTNR PLS WAIT APPROVAL**
-Pickup : 2026-10-01, Return : 2026-10-01 DG45GPx1 (CLS 8 / UN 1903) CONSOL</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="13" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3">
-        <f>SUM(N2:N71)</f>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+      <c r="M70" s="3" t="n"/>
+      <c r="N70" s="3">
+        <f>SUM(N2:N69)</f>
         <v/>
       </c>
-      <c r="O72" s="3">
-        <f>SUM(O2:O71)</f>
+      <c r="O70" s="3">
+        <f>SUM(O2:O69)</f>
         <v/>
       </c>
-      <c r="P72" s="3">
-        <f>SUM(P2:P71)</f>
+      <c r="P70" s="3">
+        <f>SUM(P2:P69)</f>
         <v/>
       </c>
-      <c r="Q72" s="3">
-        <f>SUM(Q2:Q71)</f>
+      <c r="Q70" s="3">
+        <f>SUM(Q2:Q69)</f>
         <v/>
       </c>
-      <c r="R72" s="3">
-        <f>SUM(R2:R71)</f>
+      <c r="R70" s="3">
+        <f>SUM(R2:R69)</f>
         <v/>
       </c>
-      <c r="S72" s="3">
-        <f>SUM(S2:S71)</f>
+      <c r="S70" s="3">
+        <f>SUM(S2:S69)</f>
         <v/>
       </c>
-      <c r="T72" s="3">
-        <f>SUM(T2:T71)</f>
+      <c r="T70" s="3">
+        <f>SUM(T2:T69)</f>
         <v/>
       </c>
-      <c r="U72" s="3">
-        <f>SUM(U2:U71)</f>
+      <c r="U70" s="3">
+        <f>SUM(U2:U69)</f>
         <v/>
       </c>
-      <c r="V72" s="3">
-        <f>SUM(V2:V71)</f>
+      <c r="V70" s="3">
+        <f>SUM(V2:V69)</f>
         <v/>
       </c>
     </row>
+    <row r="73" ht="13" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="13" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
     <row r="75" ht="13" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="76" ht="13" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" ht="13" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" ht="13" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>120</v>
+      <c r="B76" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V71"/>
+  <autoFilter ref="A1:V69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="95" customWidth="1" min="13" max="13"/>
+    <col width="93" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -613,7 +613,7 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801209</t>
+          <t>HASLS22260801230</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -644,22 +644,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-10-01 CONSOL</t>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801210</t>
+          <t>HASLS22260802180</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,7 +729,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-01, Return : 2026-10-02 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -793,22 +793,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801230</t>
+          <t>HASLS22260802590</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610062230</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -819,27 +819,27 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO / CONSOL</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-25, Return : 2026-09-25 CONSOL</t>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL *EXTEND CLS TIME : 05/10/2026 @23.59*</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
@@ -883,22 +883,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801791</t>
+          <t>HASLS22260901096</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610031700</t>
+          <t>202610080800</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -909,48 +909,48 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.01/10/26 CLS TIME CFS DD.01/10/26 - 17:00HRS. 
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
@@ -974,22 +974,22 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900064</t>
+          <t>HASLS22260901130</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1000,17 +1000,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1025,22 +1025,23 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-30, Return : 2026-09-30 CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1064,22 +1065,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900206</t>
+          <t>HASLS22260902434</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610290800</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1100,12 +1101,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1120,8 +1121,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-30, Return : 2026-09-30 CONSOL
- EXTEND CLS TIME : 30/09 @23.59 </t>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
@@ -1153,299 +1153,118 @@
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901130</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SWSR</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>202610121830</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>(CONSOL)</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3">
+        <f>SUM(N2:N7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="3">
+        <f>SUM(O2:O7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="3">
+        <f>SUM(P2:P7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="3">
+        <f>SUM(Q2:Q7)</f>
+        <v/>
+      </c>
+      <c r="R8" s="3">
+        <f>SUM(R2:R7)</f>
+        <v/>
+      </c>
+      <c r="S8" s="3">
+        <f>SUM(S2:S7)</f>
+        <v/>
+      </c>
+      <c r="T8" s="3">
+        <f>SUM(T2:T7)</f>
+        <v/>
+      </c>
+      <c r="U8" s="3">
+        <f>SUM(U2:U7)</f>
+        <v/>
+      </c>
+      <c r="V8" s="3">
+        <f>SUM(V2:V7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902434</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>202610290800</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3">
-        <f>SUM(N2:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="3">
-        <f>SUM(O2:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="3">
-        <f>SUM(P2:P9)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="3">
-        <f>SUM(Q2:Q9)</f>
-        <v/>
-      </c>
-      <c r="R10" s="3">
-        <f>SUM(R2:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="3">
-        <f>SUM(S2:S9)</f>
-        <v/>
-      </c>
-      <c r="T10" s="3">
-        <f>SUM(T2:T9)</f>
-        <v/>
-      </c>
-      <c r="U10" s="3">
-        <f>SUM(U2:U9)</f>
-        <v/>
-      </c>
-      <c r="V10" s="3">
-        <f>SUM(V2:V9)</f>
-        <v/>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>11</v>
+      <c r="B14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V9"/>
+  <autoFilter ref="A1:V7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,12 +481,12 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="93" customWidth="1" min="13" max="13"/>
+    <col width="160" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -703,12 +703,12 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802180</t>
+          <t>HASLS22260801789</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610152000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,37 +729,38 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
@@ -769,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -793,22 +794,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802590</t>
+          <t>HASLS22260802037</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610062230</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -819,47 +820,48 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>FIVE PAGODAS PHARMACY CO.,LTD</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>YA HOM FIVE PAGODAS BRAND (MEDICINE)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL *EXTEND CLS TIME : 05/10/2026 @23.59*</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
@@ -883,22 +885,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901096</t>
+          <t>HASLS22260802180</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -909,362 +911,7142 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-02, Return : 2026-10-03 CONSOL  </t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260802590</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610070000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO / CONSOL</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL *EXTEND CLS TIME : 05/10/2026 @23.59*</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900201</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202610221330</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900204</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202610280100</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900207</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202610201300</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900628</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>SAHAPARA RUBBER CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>NATURAL RUBBER</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.14/10/26 - 17:00HRS.*.
+(1ST CFS 12/10/26 WO/RENT) ถ้ามีการแก้ไข CFS รบกวนแจ้งใหม่ทุกครั้งค่ะ</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900691</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900700</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202611011600</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900789</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MIX-LOAD</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260900901</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610221330</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901096</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202610080800</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>20261002</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>NOODLE</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
 </t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>HASLS22260901130</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SWSR</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>202610121900</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>(CONSOL)</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901132</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202610152000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901133</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901134</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202610200200</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901135</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :19-20/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901136</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>202611011600</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :22-22/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901157</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>202610121900</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901158</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>202610140800</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901159</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901264</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>TSXM</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>202610252200</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-20  CONSOL  </t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901291</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>202610140800</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901292</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>202610201300</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901294</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-24 CONSOL</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901507</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>202610212100</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901553</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>202610140800</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901556</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901557</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>TSXM</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>202610252200</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL 
+CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901558</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>202610290800</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL 
+CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901603</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>202610140800</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901604</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>202610221330</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901605</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>202610290800</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901655</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>202610152000</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>MRD-ECC CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901752</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>202610200200</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901755</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>202610152000</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901756</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>202610221330</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901758</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>202610212100</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901759</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS.
+(1ST CFS 21/10/26 WO/RENT)</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901760</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS.
+(1ST CFS 21/10/26 WO/RENT)</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901761</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>202610280100</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>20261023</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/10/26 CLS TIME CFS DD.23/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901816</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-12, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901878</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21CONSOL</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901979</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>202610140800</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901980</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>CARGOPORT (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>(CONSOL)</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
+</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902015</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902097</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>202610152000</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902112</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>UNITED MARINE LOGISTIC CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>MIX CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-19, Return : 2026-10-20 CONSOL</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902130</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902131</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902170</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902198</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202610140800</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902253</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>202610212100</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>JPMIZ</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x30 </t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>THAI QUALITY STARCH CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>NATIVE TAPIOCA STARCH</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING DD.19/10/2026 @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.20/10/2026 @ 17.00
+REQUEST CRANE &amp; FORKLIFT /FOOD GRADE / SMOOTH FLOOR / NO SMELL / UNDER DECK</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902264</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902282</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>202610221330</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902316</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>202610212100</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-19 CONSOL </t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902317</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902319</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>202610280100</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>20261023</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-23, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902324</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>202610200200</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902327</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902404</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>202610212100</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x8 </t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 19/10/26 CLS TIME 19/10/26 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902419</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>202610290800</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902431</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFF</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
+ CARGO G.W. : 4.5 TONS </t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>HASLS22260902434</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SWAT</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>202610290800</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>20260923</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>CONSOL</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902453</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902454</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>202610200200</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
+ CLS TIME 15/10 @23.59 </t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="13" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902455</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>202610221330</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="13" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902510</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>THAI EASTSUN FOOD INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SALTED GINGER</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Good and clean container for food grade</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="13" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902769</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>202610121900</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="13" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902771</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="13" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902815</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>202610201300</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="13" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902823</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>202610212100</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>POLAR STAR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.20/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="13" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902826</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO CONSOL</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
+ (1ST CY : 22/10 W/O RENT) </t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="13" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902833</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>202610152000</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>SOMPHOL BEDDING AND MATTRESS INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>MATTRESS</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="13" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000030</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>CONTAINER GRADE A</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 16/10/26 CLS TIME 16/10 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="13" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000043</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>202610200300</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.15/10/26 *CLS TIME CFS DD.16/10/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="13" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000088</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>202610152000</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-12, Return : 2026-10-14 CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="13" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000148</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>202610201300</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.19/10/26 CLS TIME CFS DD.19/10/26 - 12:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="13" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000165</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="13" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3">
-        <f>SUM(N2:N7)</f>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="N83" s="3">
+        <f>SUM(N2:N82)</f>
         <v/>
       </c>
-      <c r="O8" s="3">
-        <f>SUM(O2:O7)</f>
+      <c r="O83" s="3">
+        <f>SUM(O2:O82)</f>
         <v/>
       </c>
-      <c r="P8" s="3">
-        <f>SUM(P2:P7)</f>
+      <c r="P83" s="3">
+        <f>SUM(P2:P82)</f>
         <v/>
       </c>
-      <c r="Q8" s="3">
-        <f>SUM(Q2:Q7)</f>
+      <c r="Q83" s="3">
+        <f>SUM(Q2:Q82)</f>
         <v/>
       </c>
-      <c r="R8" s="3">
-        <f>SUM(R2:R7)</f>
+      <c r="R83" s="3">
+        <f>SUM(R2:R82)</f>
         <v/>
       </c>
-      <c r="S8" s="3">
-        <f>SUM(S2:S7)</f>
+      <c r="S83" s="3">
+        <f>SUM(S2:S82)</f>
         <v/>
       </c>
-      <c r="T8" s="3">
-        <f>SUM(T2:T7)</f>
+      <c r="T83" s="3">
+        <f>SUM(T2:T82)</f>
         <v/>
       </c>
-      <c r="U8" s="3">
-        <f>SUM(U2:U7)</f>
+      <c r="U83" s="3">
+        <f>SUM(U2:U82)</f>
         <v/>
       </c>
-      <c r="V8" s="3">
-        <f>SUM(V2:V7)</f>
+      <c r="V83" s="3">
+        <f>SUM(V2:V82)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="86" ht="13" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="87" ht="13" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B87" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" ht="13" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B88" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="89" ht="13" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>9</v>
+      <c r="B89" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V7"/>
+  <autoFilter ref="A1:V82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610091000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -975,22 +975,22 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802590</t>
+          <t>HASLS22260900201</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610070000</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1001,27 +1001,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO / CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-05, Return : 2026-10-05 CONSOL *EXTEND CLS TIME : 05/10/2026 @23.59*</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1065,12 +1065,12 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900201</t>
+          <t>HASLS22260900204</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
@@ -1155,22 +1155,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900204</t>
+          <t>HASLS22260900207</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610202130</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0</v>
@@ -1245,12 +1245,12 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900207</t>
+          <t>HASLS22260900628</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1271,47 +1271,48 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>SAHAPARA RUBBER CO.,LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NATURAL RUBBER</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.14/10/26 - 17:00HRS.*.
+(1ST CFS 12/10/26 WO/RENT) ถ้ามีการแก้ไข CFS รบกวนแจ้งใหม่ทุกครั้งค่ะ</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -1335,12 +1336,12 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900628</t>
+          <t>HASLS22260900691</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1350,7 +1351,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1361,48 +1362,47 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>SAHAPARA RUBBER CO.,LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Special request: FS grade Clean and good grade containers for transportation of Natural rubber (BALES)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.14/10/26 - 17:00HRS.*.
-(1ST CFS 12/10/26 WO/RENT) ถ้ามีการแก้ไข CFS รบกวนแจ้งใหม่ทุกครั้งค่ะ</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1426,22 +1426,22 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900691</t>
+          <t>HASLS22260900700</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202610281100</t>
+          <t>202611011600</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1452,17 +1452,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -1516,22 +1516,22 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900700</t>
+          <t>HASLS22260900789</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202611011600</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1542,27 +1542,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>MIX-LOAD</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>0</v>
@@ -1606,22 +1606,22 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900789</t>
+          <t>HASLS22260900901</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1632,27 +1632,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>MIX-LOAD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0</v>
@@ -1696,22 +1696,22 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900901</t>
+          <t>HASLS22260901130</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1722,22 +1722,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1747,12 +1747,13 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
@@ -1762,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="2" t="n">
         <v>0</v>
@@ -1786,22 +1787,22 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901096</t>
+          <t>HASLS22260901132</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1812,48 +1813,48 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.02/10/26 CLS TIME CFS DD.02/10/26- 17:00HRS.
+          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>0</v>
@@ -1877,22 +1878,22 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901130</t>
+          <t>HASLS22260901133</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1913,7 +1914,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1933,7 +1934,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 01-02/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -1968,22 +1969,22 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901132</t>
+          <t>HASLS22260901134</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -2004,7 +2005,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2024,7 +2025,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 08-09/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -2059,12 +2060,12 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901133</t>
+          <t>HASLS22260901135</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2074,7 +2075,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2095,7 +2096,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2115,7 +2116,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN :19-20/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -2150,22 +2151,22 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901134</t>
+          <t>HASLS22260901136</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610200200</t>
+          <t>202611011600</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2186,7 +2187,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2206,7 +2207,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN :22-22/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -2241,22 +2242,22 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901135</t>
+          <t>HASLS22260901157</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2267,7 +2268,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2277,12 +2278,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2292,13 +2293,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :19-20/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
@@ -2332,12 +2332,12 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901136</t>
+          <t>HASLS22260901158</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202611011600</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2383,13 +2383,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :22-22/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
@@ -2423,22 +2422,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901157</t>
+          <t>HASLS22260901159</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2459,7 +2458,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2479,7 +2478,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
@@ -2513,22 +2512,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901158</t>
+          <t>HASLS22260901264</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2539,27 +2538,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2569,17 +2568,18 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>Pickup : 2026-10-19, Return : 2026-10-20  CONSOL  
+ 1ST CY IN : 22/10/2026 W/O RENT</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>0</v>
@@ -2603,12 +2603,12 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901159</t>
+          <t>HASLS22260901291</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-13, Return : 2026-10-13 CONSOL</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-12 CONSOL</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>0</v>
@@ -2693,22 +2693,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901264</t>
+          <t>HASLS22260901292</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610252200</t>
+          <t>202610202130</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2719,22 +2719,22 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2749,17 +2749,17 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-20  CONSOL  </t>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901291</t>
+          <t>HASLS22260901294</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-08 CONSOL</t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-24 CONSOL</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901292</t>
+          <t>HASLS22260901507</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2899,27 +2899,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>0</v>
@@ -2963,22 +2963,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901294</t>
+          <t>HASLS22260901553</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610281100</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2994,32 +2994,33 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>THE M CORP GLOBAL CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-24 CONSOL</t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
@@ -3029,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>0</v>
@@ -3053,12 +3054,12 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901507</t>
+          <t>HASLS22260901556</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3068,7 +3069,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610212100</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -3079,37 +3080,37 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
+          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
@@ -3119,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="2" t="n">
         <v>0</v>
@@ -3143,22 +3144,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901553</t>
+          <t>HASLS22260901557</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3179,7 +3180,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3194,13 +3195,13 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>CONSOL
+          <t>CONSOL 
 CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-22, Return : 2026-10-24 CONSOL </t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
@@ -3234,22 +3235,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901556</t>
+          <t>HASLS22260901558</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610301400</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3270,7 +3271,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3285,12 +3286,13 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL 
+CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-13, Return : 2026-10-14 CONSOL</t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
@@ -3324,22 +3326,22 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901557</t>
+          <t>HASLS22260901603</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202610252200</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3350,48 +3352,47 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>CONSOL 
-CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-10-19 CONSOL </t>
+          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="2" t="n">
         <v>0</v>
@@ -3415,22 +3416,22 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901558</t>
+          <t>HASLS22260901604</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3441,48 +3442,47 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>CONSOL 
-CLEAN &amp; GOOD CONTAINERS</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>0</v>
@@ -3506,22 +3506,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901603</t>
+          <t>HASLS22260901605</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610301400</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-08, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
@@ -3596,22 +3596,22 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901604</t>
+          <t>HASLS22260901655</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3622,37 +3622,38 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>MRD-ECC CO.,LTD.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>BALL CLAY</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
@@ -3662,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>0</v>
@@ -3686,22 +3687,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901605</t>
+          <t>HASLS22260901752</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3712,37 +3713,37 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
@@ -3752,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>0</v>
@@ -3776,7 +3777,7 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901655</t>
+          <t>HASLS22260901755</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3791,7 +3792,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3807,43 +3808,43 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>MRD-ECC CO.,LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>BALL CLAY</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>0</v>
@@ -3867,22 +3868,22 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901752</t>
+          <t>HASLS22260901756</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610200200</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3893,47 +3894,48 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>FISHING NETS</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>CONSOL  GOOD AND CLEAN CONTAINER</t>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.21/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q38" s="2" t="n">
         <v>0</v>
@@ -3957,22 +3959,22 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901755</t>
+          <t>HASLS22260901758</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3993,7 +3995,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4013,7 +4015,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
@@ -4048,22 +4050,22 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901756</t>
+          <t>HASLS22260901759</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -4084,7 +4086,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4104,8 +4106,8 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.14/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
-</t>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS.
+(1ST CFS 21/10/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
@@ -4139,12 +4141,12 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901758</t>
+          <t>HASLS22260901760</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4154,7 +4156,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610212100</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -4175,7 +4177,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4195,8 +4197,8 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.19/10/26 - 17:00HRS.
-</t>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS.
+(1ST CFS 21/10/26 WO/RENT)</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
@@ -4230,22 +4232,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901759</t>
+          <t>HASLS22260901761</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4266,7 +4268,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261023</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4286,8 +4288,8 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS.
-(1ST CFS 21/10/26 WO/RENT)</t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/10/26 CLS TIME CFS DD.23/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
@@ -4321,22 +4323,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901760</t>
+          <t>HASLS22260901816</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4347,48 +4349,47 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS.
-(1ST CFS 21/10/26 WO/RENT)</t>
+          <t>Pickup : 2026-10-12, Return : 2026-10-14 CONSOL</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>0</v>
@@ -4412,22 +4413,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901761</t>
+          <t>HASLS22260901878</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4438,7 +4439,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4448,28 +4449,27 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261023</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>SIAM BROTHERS CORP.,LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>FISHING NETS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.23/10/26 CLS TIME CFS DD.23/10/26 - 17:00HRS.
-</t>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21CONSOL</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
@@ -4503,22 +4503,22 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901816</t>
+          <t>HASLS22260901979</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4534,17 +4534,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>STAR CONCORD (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -4554,22 +4554,23 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CONSOL GOOD AND CLEAN CONTAINER /</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-12, Return : 2026-10-14 CONSOL</t>
+          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>0</v>
@@ -4593,12 +4594,12 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901878</t>
+          <t>HASLS22260901980</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4608,7 +4609,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610281100</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4629,12 +4630,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4644,12 +4645,13 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-21, Return : 2026-10-21CONSOL</t>
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
@@ -4683,12 +4685,12 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901979</t>
+          <t>HASLS22260902015</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4698,7 +4700,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4709,48 +4711,47 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :08-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="2" t="n">
         <v>0</v>
@@ -4774,12 +4775,12 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901980</t>
+          <t>HASLS22260902097</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4789,7 +4790,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4800,7 +4801,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4815,23 +4816,22 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
@@ -4865,7 +4865,7 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902015</t>
+          <t>HASLS22260902112</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4901,17 +4901,17 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>UNITED MARINE LOGISTIC CO., LTD.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>MIX CARGO CONSOL</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
+          <t>Pickup : 2026-10-19, Return : 2026-10-20 CONSOL</t>
         </is>
       </c>
       <c r="N49" s="2" t="n">
@@ -4955,22 +4955,22 @@
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902097</t>
+          <t>HASLS22260902130</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
@@ -5045,22 +5045,22 @@
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902112</t>
+          <t>HASLS22260902131</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -5071,27 +5071,27 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>UNITED MARINE LOGISTIC CO., LTD.</t>
+          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>MIX CARGO CONSOL</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-19, Return : 2026-10-20 CONSOL</t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
         </is>
       </c>
       <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902130</t>
+          <t>HASLS22260902170</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -5166,42 +5166,42 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>FOOD STUFFS</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-15 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="2" t="n">
         <v>0</v>
@@ -5225,22 +5225,22 @@
     <row r="53" ht="13" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902131</t>
+          <t>HASLS22260902198</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>202610281100</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -5251,27 +5251,27 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>ACCORD PILOT LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
+          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
         </is>
       </c>
       <c r="N53" s="2" t="n">
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="2" t="n">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902170</t>
+          <t>HASLS22260902253</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -5341,229 +5341,230 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPMIZ</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x30 </t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>KUANG PEI SAN FOOD PRODUCTS PUBLIC CO., LTD.</t>
+          <t>THAI QUALITY STARCH CO.,LTD.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>FOOD STUFFS</t>
+          <t>NATIVE TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.12/10/26 *CLS TIME CFS DD.12/10/26 - 17:00HRS.* </t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902198</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>202610140800</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>CY-RTN : 08-09/10/2026 (CONSOL)</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902253</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>202610212100</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>JPMIZ</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x30 </t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>THAI QUALITY STARCH CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>NATIVE TAPIOCA STARCH</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>STUFFING DD.19/10/2026 @ PAT (SPORTLIGHT TOWER NO.2)
 CLS TIME DD.20/10/2026 @ 17.00
 REQUEST CRANE &amp; FORKLIFT /FOOD GRADE / SMOOTH FLOOR / NO SMELL / UNDER DECK</t>
         </is>
       </c>
+      <c r="N54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902264</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902282</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>202610230100</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
+        </is>
+      </c>
       <c r="N56" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="2" t="n">
         <v>0</v>
@@ -5587,22 +5588,22 @@
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902264</t>
+          <t>HASLS22260902316</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -5613,1131 +5614,1131 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-19 CONSOL </t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902317</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>202610241500</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902319</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>202610291300</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261023</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-23, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902324</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>202610200200</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
           <t>HKHKG</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902327</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902404</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>202610241900</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x8 </t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>BALL CLAY</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 19/10/26 CLS TIME 19/10/26 @17.00HRS 
+</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902419</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>202610301400</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902431</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFF</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
+ CARGO G.W. : 4.5 TONS </t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902434</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>202610301400</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902453</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902454</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>202610200200</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
+ CLS TIME 15/10 @23.59 </t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902455</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>202610230100</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902510</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>202610170100</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>JPKCZ</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>20261012</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFFS</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>THAI EASTSUN FOOD INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SALTED GINGER</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Good and clean container for food grade</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
-      <c r="N57" s="2" t="n">
+      <c r="N69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902282</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>202610221330</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-16, Return : 2026-09-16 CONSOL </t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902316</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>202610212100</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-19 CONSOL </t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902317</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>202610241500</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902319</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SWSP</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>202610280100</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>20261023</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-23, Return : 2026-10-23 CONSOL</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902324</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>202610200200</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902327</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SWDN</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>202610281100</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902404</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>202610212100</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x8 </t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>BALL CLAY</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 19/10/26 CLS TIME 19/10/26 @17.00HRS 
-</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902419</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>202610290800</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>20261022</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902431</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>202610170100</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>SOUTHEAST ASIAN PACKAGING AND CANNING LIMITED</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFF</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 09/10/26 CLS TIME 09/10 @17.00HRS 
- CARGO G.W. : 4.5 TONS </t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902434</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>202610290800</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902453</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>202610170100</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="13" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902454</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>202610200200</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-14, Return : 2026-10-15 CONSOL 
- CLS TIME 15/10 @23.59 </t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="O69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="2" t="n">
         <v>0</v>
@@ -6761,22 +6762,22 @@
     <row r="70" ht="13" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902455</t>
+          <t>HASLS22260902769</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -6787,47 +6788,47 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL (CY IN PAT)</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONSOL (CY IN PAT)</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="2" t="n">
         <v>0</v>
@@ -6851,22 +6852,22 @@
     <row r="71" ht="13" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902510</t>
+          <t>HASLS22260902771</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -6877,7 +6878,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>JPKCZ</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -6887,28 +6888,27 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>THAI EASTSUN FOOD INDUSTRY CO., LTD.</t>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>SALTED GINGER</t>
+          <t>GENERAL CARGO</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Good and clean container for food grade</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.12/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
-</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
         </is>
       </c>
       <c r="N71" s="2" t="n">
@@ -6942,12 +6942,12 @@
     <row r="72" ht="13" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902769</t>
+          <t>HASLS22260902815</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610202130</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -6973,42 +6973,42 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL (CY IN PAT)</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>CONSOL (CY IN PAT)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)</t>
+          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q72" s="2" t="n">
         <v>0</v>
@@ -7032,12 +7032,12 @@
     <row r="73" ht="13" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902771</t>
+          <t>HASLS22260902823</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -7068,27 +7068,28 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>POLAR STAR CO., LTD.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.20/10/26 - 17:00HRS.
+</t>
         </is>
       </c>
       <c r="N73" s="2" t="n">
@@ -7122,12 +7123,12 @@
     <row r="74" ht="13" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902815</t>
+          <t>HASLS22260902826</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -7137,7 +7138,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -7148,7 +7149,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -7158,17 +7159,17 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>GENERAL CARGO CONSOL</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7178,7 +7179,8 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-16, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
+ (1ST CY : 22/10 W/O RENT) </t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
@@ -7212,22 +7214,22 @@
     <row r="75" ht="13" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902823</t>
+          <t>HASLS22260902833</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>202610212100</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -7248,17 +7250,17 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>POLAR STAR CO., LTD.</t>
+          <t>SOMPHOL BEDDING AND MATTRESS INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>NOODLE</t>
+          <t>MATTRESS</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -7268,7 +7270,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.20/10/26 CLS TIME CFS DD.20/10/26 - 17:00HRS.
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
@@ -7303,22 +7305,22 @@
     <row r="76" ht="13" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902826</t>
+          <t>HASLS22261000030</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>202610281100</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -7329,7 +7331,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -7339,28 +7341,28 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>THAI ARROW PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL</t>
+          <t>RAW MATERIAL</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>CONTAINER GRADE A</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
- (1ST CY : 22/10 W/O RENT) </t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 16/10/26 CLS TIME 16/10 @17.00HRS 
+</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
@@ -7394,22 +7396,22 @@
     <row r="77" ht="13" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902833</t>
+          <t>HASLS22261000043</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -7420,7 +7422,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -7430,17 +7432,17 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>SOMPHOL BEDDING AND MATTRESS INDUSTRY CO., LTD.</t>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>MATTRESS</t>
+          <t>NOODLE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -7450,8 +7452,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
-</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.15/10/26 *CLS TIME CFS DD.16/10/26 - 17:00HRS.* </t>
         </is>
       </c>
       <c r="N77" s="2" t="n">
@@ -7485,22 +7486,22 @@
     <row r="78" ht="13" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000030</t>
+          <t>HASLS22261000088</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -7511,48 +7512,47 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>THAI ARROW PRODUCTS CO., LTD.</t>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>RAW MATERIAL</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER GRADE A</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 16/10/26 CLS TIME 16/10 @17.00HRS 
-</t>
+          <t>Pickup : 2026-10-12, Return : 2026-10-14 CONSOL (CY IN PAT)</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="2" t="n">
         <v>0</v>
@@ -7576,22 +7576,22 @@
     <row r="79" ht="13" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000043</t>
+          <t>HASLS22261000148</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610202130</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -7632,7 +7632,8 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.15/10/26 *CLS TIME CFS DD.16/10/26 - 17:00HRS.* </t>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.19/10/26 CLS TIME CFS DD.19/10/26 - 12:00HRS.
+</t>
         </is>
       </c>
       <c r="N79" s="2" t="n">
@@ -7666,12 +7667,12 @@
     <row r="80" ht="13" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000088</t>
+          <t>HASLS22261000165</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -7681,7 +7682,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -7692,47 +7693,47 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-12, Return : 2026-10-14 CONSOL (CY IN PAT)</t>
+          <t>Pickup : 2026-10-14, Return : 2026-10-15 CONSOL</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="2" t="n">
         <v>0</v>
@@ -7756,12 +7757,12 @@
     <row r="81" ht="13" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000148</t>
+          <t>HASLS22261000250</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7771,7 +7772,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -7792,7 +7793,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -7812,7 +7813,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.19/10/26 CLS TIME CFS DD.19/10/26 - 12:00HRS.
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.16/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
 </t>
         </is>
       </c>
@@ -7847,22 +7848,22 @@
     <row r="82" ht="13" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000165</t>
+          <t>HASLS22261000271</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -7878,42 +7879,43 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+          <t>KONGSIRI TANNERY CO., LTD.</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t xml:space="preserve">LETHER HIDE </t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-15 CONSOL</t>
+          <t>STUFFING DD.09/10/2026  @ PAT (SPORTLIGHT TOWER NO.2)
+CLS TIME DD.12/10/2026 @ 17.00</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="2" t="n">
         <v>0</v>
@@ -8013,10 +8015,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" ht="13" customHeight="1">
@@ -8026,10 +8028,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" ht="13" customHeight="1">

--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="94" customWidth="1" min="13" max="13"/>
+    <col width="206" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -613,12 +613,12 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900789</t>
+          <t>HASLS22260900207</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610181900</t>
+          <t>202610231600</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>MIX-LOAD</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-09 CONSOL</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -703,12 +703,12 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901980</t>
+          <t>HASLS22260900691</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610181900</t>
+          <t>202610290600</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,7 +729,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -754,13 +754,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
@@ -794,22 +793,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902434</t>
+          <t>HASLS22260901133</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202611010400</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -820,7 +819,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -830,12 +829,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -845,12 +844,13 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
@@ -884,22 +884,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902769</t>
+          <t>HASLS22260901134</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610181900</t>
+          <t>202610231400</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -910,48 +910,48 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO CONSOL (CY IN PAT)</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CONSOL (CY IN PAT)</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)
-1ST CY CNTR 12/10/2026</t>
+          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
@@ -975,22 +975,22 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902833</t>
+          <t>HASLS22260901159</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610150600</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1001,48 +1001,47 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>SOMPHOL BEDDING AND MATTRESS INDUSTRY CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>MATTRESS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.09/10/26 CLS TIME CFS DD.12/10/26 - 17:00HRS.
-</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1066,12 +1065,12 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000271</t>
+          <t>HASLS22260901507</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1081,7 +1080,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610141200</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1092,48 +1091,47 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>KONGSIRI TANNERY CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LETHER HIDE </t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>STUFFING DD.09/10/2026  @ PAT (SPORTLIGHT TOWER NO.2)
-CLS TIME DD.12/10/2026 @ 17.00</t>
+          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
@@ -1157,22 +1155,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000765</t>
+          <t>HASLS22260901980</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610141200</t>
+          <t>202610191100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1188,7 +1186,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1198,32 +1196,33 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-09, Return : 2026-10-12 CONSOL </t>
+          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
+</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0</v>
@@ -1245,105 +1244,1114 @@
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3">
-        <f>SUM(N2:N8)</f>
-        <v/>
-      </c>
-      <c r="O9" s="3">
-        <f>SUM(O2:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="3">
-        <f>SUM(P2:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="3">
-        <f>SUM(Q2:Q8)</f>
-        <v/>
-      </c>
-      <c r="R9" s="3">
-        <f>SUM(R2:R8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="3">
-        <f>SUM(S2:S8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="3">
-        <f>SUM(T2:T8)</f>
-        <v/>
-      </c>
-      <c r="U9" s="3">
-        <f>SUM(U2:U8)</f>
-        <v/>
-      </c>
-      <c r="V9" s="3">
-        <f>SUM(V2:V8)</f>
-        <v/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902264</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>FOOD STUFFS</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 16/10 @17.00HRS 
+ 1ST CFS : 15/10 W/O RENT</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902324</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902434</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>202611020100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902769</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ASIA FORWARDING (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL (CY IN PAT)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)
+1ST CY CNTR 12/10/2026</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>8</v>
+          <t>HASLS22260902815</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202610231600</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000043</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610230100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.15/10/26 *CLS TIME CFS DD.16/10/26 - 17:00HRS.* </t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000165</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-15 CONSOL</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000218</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>202610231600</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>KANOKWAN FOOD PRODUCTS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRY PASTE </t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>CFS 2 SHIPPER1. Kanokwan Food = 518 cartons / 2.Opal Lime And Lemon Co.,ltd.  420 cartons</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING DD.15/10/2026@ PAT (SPORTLIGHT TOWER NO.2) *1ST CFS DD.15/10/2026* CLS TIME DD.16/10/2026 @ 17.00
+1. Kanokwan Food Products Co.,Ltd. (518 cartons)
+2. Opal Lime And Lemon Co.,ltd.  (420 cartons)
+ </t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000250</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>CHAI SAN SAN TRADING LIMITED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>NOODLE</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000413</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-15, Return : 2026-10-15  CONSOL</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000548</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202610191100</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3">
+        <f>SUM(N2:N19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="3">
+        <f>SUM(O2:O19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="3">
+        <f>SUM(P2:P19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="3">
+        <f>SUM(Q2:Q19)</f>
+        <v/>
+      </c>
+      <c r="R20" s="3">
+        <f>SUM(R2:R19)</f>
+        <v/>
+      </c>
+      <c r="S20" s="3">
+        <f>SUM(S2:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="3">
+        <f>SUM(T2:T19)</f>
+        <v/>
+      </c>
+      <c r="U20" s="3">
+        <f>SUM(U2:U19)</f>
+        <v/>
+      </c>
+      <c r="V20" s="3">
+        <f>SUM(V2:V19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>8</v>
+      <c r="B26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V8"/>
+  <autoFilter ref="A1:V19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,12 +481,12 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="206" customWidth="1" min="13" max="13"/>
+    <col width="220" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -613,12 +613,12 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900207</t>
+          <t>HASLS22260900691</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610231600</t>
+          <t>202610312100</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -703,22 +703,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900691</t>
+          <t>HASLS22260900901</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610290600</t>
+          <t>202610250030</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,17 +729,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-10-19, Return : 2026-10-20 CONSOL</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610230100</t>
+          <t>202610240100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -884,22 +884,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901134</t>
+          <t>HASLS22260901135</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610231400</t>
+          <t>202610260700</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
+          <t xml:space="preserve">CY-RTN :19-20/10/20206 (CONSOL)
 </t>
         </is>
       </c>
@@ -975,22 +975,22 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901159</t>
+          <t>HASLS22260901264</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610230100</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16 CONSOL </t>
+          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-20 CONSOL </t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901507</t>
+          <t>HASLS22260902253</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610262300</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1091,47 +1091,51 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPMIZ</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x30 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>THAI QUALITY STARCH CO.,LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NATIVE TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-15, Return : 2026-10-16  CONSOL </t>
+          <t xml:space="preserve">STUFFING DD.20/10/2026 @ PAT (SPORTLIGHT TOWER NO.2) CLS TIME DD.20/10/2026 @ 17.00
+CFS : 20 OCT 2026  12X20’DC (LOAD CARGO : 10X20’DC / STORGE PALLET : 2X20’DC)
+CFS : 21 OCT 2026  WAITING
+CFS : 22 OCT 2026  WAITING
+</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
@@ -1155,12 +1159,12 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901980</t>
+          <t>HASLS22260902434</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1170,7 +1174,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610191100</t>
+          <t>202611040500</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1191,12 +1195,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1206,13 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :09-09/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
@@ -1246,12 +1249,12 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902264</t>
+          <t>HASLS22260902815</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1261,7 +1264,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610191100</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1277,7 +1280,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1287,33 +1290,32 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>THAI WORLD FOODS AND FRUITS CO., LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>FOOD STUFFS</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>STUFFING @PAT (SPORT LIGHT TOWER 2) DD 15/10/26 CLS TIME 16/10 @17.00HRS 
- 1ST CFS : 15/10 W/O RENT</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -1337,12 +1339,12 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902324</t>
+          <t>HASLS22260902826</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1352,7 +1354,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610191100</t>
+          <t>202610312100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1363,22 +1365,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1393,17 +1395,18 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-14 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
+ (1ST CY : 22/10 W/O RENT) </t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1427,22 +1430,22 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902434</t>
+          <t>HASLS22261000736</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202611020100</t>
+          <t>202610250030</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1453,7 +1456,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1463,12 +1466,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GRANDLINK LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1483,7 +1486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-20 CONSOL </t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
@@ -1515,843 +1518,118 @@
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902769</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>202610191100</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>ASIA FORWARDING (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL (CY IN PAT)</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-09, Return : 2026-10-10 CONSOL (CY IN PAT)
-1ST CY CNTR 12/10/2026</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902815</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>KMGY</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>202610231600</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000043</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SKOR</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>202610230100</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>NOODLE</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD.15/10/26 *CLS TIME CFS DD.16/10/26 - 17:00HRS.* </t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>0</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3">
+        <f>SUM(N2:N11)</f>
+        <v/>
+      </c>
+      <c r="O12" s="3">
+        <f>SUM(O2:O11)</f>
+        <v/>
+      </c>
+      <c r="P12" s="3">
+        <f>SUM(P2:P11)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="3">
+        <f>SUM(Q2:Q11)</f>
+        <v/>
+      </c>
+      <c r="R12" s="3">
+        <f>SUM(R2:R11)</f>
+        <v/>
+      </c>
+      <c r="S12" s="3">
+        <f>SUM(S2:S11)</f>
+        <v/>
+      </c>
+      <c r="T12" s="3">
+        <f>SUM(T2:T11)</f>
+        <v/>
+      </c>
+      <c r="U12" s="3">
+        <f>SUM(U2:U11)</f>
+        <v/>
+      </c>
+      <c r="V12" s="3">
+        <f>SUM(V2:V11)</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000165</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>202610191100</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>PILOT CONSOLIDATOR CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL CLEAN &amp; GOOD CONTAINERS</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-15 CONSOL</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>0</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000218</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>KMGY</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>202610231600</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>KANOKWAN FOOD PRODUCTS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CURRY PASTE </t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>CFS 2 SHIPPER1. Kanokwan Food = 518 cartons / 2.Opal Lime And Lemon Co.,ltd.  420 cartons</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING DD.15/10/2026@ PAT (SPORTLIGHT TOWER NO.2) *1ST CFS DD.15/10/2026* CLS TIME DD.16/10/2026 @ 17.00
-1. Kanokwan Food Products Co.,Ltd. (518 cartons)
-2. Opal Lime And Lemon Co.,ltd.  (420 cartons)
- </t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>0</v>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000250</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>202610191100</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>CHAI SAN SAN TRADING LIMITED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>NOODLE</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.15/10/26 CLS TIME CFS DD.15/10/26 - 17:00HRS.
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="n">
-        <v>0</v>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000413</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>202610191100</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>PROFREIGHT INTERNATIONAL CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-15  CONSOL</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000548</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>202610191100</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>HANDLE INTER CONSOLIDATION CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-14, Return : 2026-10-16 CONSOL</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3">
-        <f>SUM(N2:N19)</f>
-        <v/>
-      </c>
-      <c r="O20" s="3">
-        <f>SUM(O2:O19)</f>
-        <v/>
-      </c>
-      <c r="P20" s="3">
-        <f>SUM(P2:P19)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="3">
-        <f>SUM(Q2:Q19)</f>
-        <v/>
-      </c>
-      <c r="R20" s="3">
-        <f>SUM(R2:R19)</f>
-        <v/>
-      </c>
-      <c r="S20" s="3">
-        <f>SUM(S2:S19)</f>
-        <v/>
-      </c>
-      <c r="T20" s="3">
-        <f>SUM(T2:T19)</f>
-        <v/>
-      </c>
-      <c r="U20" s="3">
-        <f>SUM(U2:U19)</f>
-        <v/>
-      </c>
-      <c r="V20" s="3">
-        <f>SUM(V2:V19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>21</v>
+      <c r="B18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V19"/>
+  <autoFilter ref="A1:V11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="220" customWidth="1" min="13" max="13"/>
+    <col width="247" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610312100</t>
+          <t>202611010800</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -703,22 +703,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900901</t>
+          <t>HASLS22260902253</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610250030</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,47 +729,51 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPMIZ</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x30 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>THAI QUALITY STARCH CO.,LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>NATIVE TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-19, Return : 2026-10-20 CONSOL</t>
+          <t xml:space="preserve">STUFFING DD.20/10/2026 @ PAT (SPORTLIGHT TOWER NO.2) CLS TIME DD.20/10/2026 @ 17.00
+CFS : 20 OCT 2026 → 12 x 20’DC (Load Cargo: 10 x 20’DC / Storage Pallet: 2 x 20’DC)
+CFS : 21 OCT 2026 → 8 x 20’DC
+CFS : 22 OCT 2026 → 10 x 20’DC (Total Loaded Ca
+</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -793,12 +797,12 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901133</t>
+          <t>HASLS22260902317</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610240100</t>
+          <t>202610260700</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -819,22 +823,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -844,13 +848,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 12-14/10/20206 (CONSOL)
-</t>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
@@ -860,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
@@ -884,12 +887,12 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901135</t>
+          <t>HASLS22260902404</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -899,7 +902,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610260700</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -910,48 +913,48 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x8 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>BALL CLAY</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>(CONSOL)</t>
+          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN :19-20/10/20206 (CONSOL)
+          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.21/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS. 
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
@@ -975,12 +978,12 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901264</t>
+          <t>HASLS22260902434</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -990,7 +993,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202611032300</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1001,22 +1004,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>CARGOPORT (THAILAND) LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1031,17 +1034,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-19, Return : 2026-10-20 CONSOL </t>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1065,22 +1068,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902253</t>
+          <t>HASLS22260902815</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610271500</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1091,51 +1094,47 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>JPMIZ</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x30 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>THAI QUALITY STARCH CO.,LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>NATIVE TAPIOCA STARCH</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING DD.20/10/2026 @ PAT (SPORTLIGHT TOWER NO.2) CLS TIME DD.20/10/2026 @ 17.00
-CFS : 20 OCT 2026  12X20’DC (LOAD CARGO : 10X20’DC / STORGE PALLET : 2X20’DC)
-CFS : 21 OCT 2026  WAITING
-CFS : 22 OCT 2026  WAITING
-</t>
+          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
@@ -1159,12 +1158,12 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902434</t>
+          <t>HASLS22260902826</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1174,7 +1173,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202611040500</t>
+          <t>202611010800</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1185,7 +1184,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1195,12 +1194,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1215,7 +1214,8 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
+ (1ST CY : 22/10 W/O RENT) </t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
@@ -1249,7 +1249,7 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902815</t>
+          <t>HASLS22261001120</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1280,42 +1280,43 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>SUMITOMO ELECTRIC WINTEC (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>GENERAL CARGO (CONSOL)</t>
+          <t>ENAMELLED COPPER WIRE</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 21/10/26 CLS TIME 21/10 @17.00HRS 
+</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -1339,22 +1340,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902826</t>
+          <t>HASLS22261001666</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610312100</t>
+          <t>202610242200</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1365,22 +1366,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1395,18 +1396,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
- (1ST CY : 22/10 W/O RENT) </t>
+          <t>Pickup : 2026-10-21, Return : 2026-10-22 CONSOL</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1428,208 +1428,118 @@
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000736</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>202610250030</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>GRANDLINK LOGISTICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-20 CONSOL </t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>0</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3">
+        <f>SUM(N2:N10)</f>
+        <v/>
+      </c>
+      <c r="O11" s="3">
+        <f>SUM(O2:O10)</f>
+        <v/>
+      </c>
+      <c r="P11" s="3">
+        <f>SUM(P2:P10)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="3">
+        <f>SUM(Q2:Q10)</f>
+        <v/>
+      </c>
+      <c r="R11" s="3">
+        <f>SUM(R2:R10)</f>
+        <v/>
+      </c>
+      <c r="S11" s="3">
+        <f>SUM(S2:S10)</f>
+        <v/>
+      </c>
+      <c r="T11" s="3">
+        <f>SUM(T2:T10)</f>
+        <v/>
+      </c>
+      <c r="U11" s="3">
+        <f>SUM(U2:U10)</f>
+        <v/>
+      </c>
+      <c r="V11" s="3">
+        <f>SUM(V2:V10)</f>
+        <v/>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3">
-        <f>SUM(N2:N11)</f>
-        <v/>
-      </c>
-      <c r="O12" s="3">
-        <f>SUM(O2:O11)</f>
-        <v/>
-      </c>
-      <c r="P12" s="3">
-        <f>SUM(P2:P11)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="3">
-        <f>SUM(Q2:Q11)</f>
-        <v/>
-      </c>
-      <c r="R12" s="3">
-        <f>SUM(R2:R11)</f>
-        <v/>
-      </c>
-      <c r="S12" s="3">
-        <f>SUM(S2:S11)</f>
-        <v/>
-      </c>
-      <c r="T12" s="3">
-        <f>SUM(T2:T11)</f>
-        <v/>
-      </c>
-      <c r="U12" s="3">
-        <f>SUM(U2:U11)</f>
-        <v/>
-      </c>
-      <c r="V12" s="3">
-        <f>SUM(V2:V11)</f>
-        <v/>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>39</v>
+      <c r="B17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V11"/>
+  <autoFilter ref="A1:V10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
+++ b/output/bkg pending - PAT TERMINAL 1 & 2 (PORT AUTHORITY OF THAILAND).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$V$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -613,22 +613,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900691</t>
+          <t>HASLS22260901136</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202611010800</t>
+          <t>202610282000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>CARGOPORT (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -664,12 +664,13 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CONSOL</t>
+          <t>(CONSOL)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>CY-RTN :22-22/10/20206 (CONSOL)
+1ST CY CNTR DD.26/10/2026</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -703,22 +704,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902253</t>
+          <t>HASLS22260901294</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610271500</t>
+          <t>202611010800</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -729,35 +730,307 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>THE M CORP GLOBAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-24 CONSOL</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901558</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>202611041600</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>PILOT CONSOLIDATOR CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL 
+CLEAN &amp; GOOD CONTAINERS</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901760</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>202610260700</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>SIAM BROTHERS CORP.,LTD.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>FISHING NETS</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>REQ: GOOD &amp; CLEAN CONTAINER,NO LEAK,NO RUST,NO SMELL,NO BURR,NOT WET,GOOD FLOOR.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.22/10/26 *CLS TIME CFS DD.22/10/26 - 17:00HRS.*
+[1ST CFS DATE : 22/10/2026 W/O RENT]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902253</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610271500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>JPMIZ</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x30 </t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20261020</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>THAI QUALITY STARCH CO.,LTD.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>NATIVE TAPIOCA STARCH</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>REQUEST CRANE &amp; FORKLIFT / FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK /</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">STUFFING DD.20/10/2026 @ PAT (SPORTLIGHT TOWER NO.2) CLS TIME DD.20/10/2026 @ 17.00
 CFS : 20 OCT 2026 → 12 x 20’DC (Load Cargo: 10 x 20’DC / Storage Pallet: 2 x 20’DC)
@@ -766,285 +1039,14 @@
 </t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902317</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>202610260700</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902404</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>202610271500</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x8 </t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>SIBELCO MINERALS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>BALL CLAY</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>RQST CONTAINER 30 TONS. // REQUEST CONTAINER GOOD GRADE</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STUFFING CARGO @PAT (SPORTLIGHT TOWER NO.2) DD.21/10/26 CLS TIME CFS DD.22/10/26 - 17:00HRS. 
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902434</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SWAT</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>202611032300</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL CARGO (CONSOL)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>CONSOL</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1068,22 +1070,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902815</t>
+          <t>HASLS22260902317</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202610260700</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1094,22 +1096,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>QUANTERM LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1124,7 +1126,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-15, Return : 2026-10-16 CONSOL</t>
+          <t>Pickup : 2026-10-21, Return : 2026-10-21 CONSOL</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
@@ -1134,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
@@ -1158,12 +1160,12 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902826</t>
+          <t>HASLS22260902419</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1173,7 +1175,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202611010800</t>
+          <t>202611041600</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1184,22 +1186,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1214,8 +1216,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
- (1ST CY : 22/10 W/O RENT) </t>
+          <t>Pickup : 2026-10-22, Return : 2026-10-23 CONSOL</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
@@ -1225,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0</v>
@@ -1249,12 +1250,12 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001120</t>
+          <t>HASLS22260902434</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1264,7 +1265,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202611041600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1280,43 +1281,42 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>SUMITOMO ELECTRIC WINTEC (THAILAND) CO.,LTD.</t>
+          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>ENAMELLED COPPER WIRE</t>
+          <t>GENERAL CARGO (CONSOL)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>CONSOL</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 21/10/26 CLS TIME 21/10 @17.00HRS 
-</t>
+          <t>Pickup : 2026-09-23, Return : 2026-09-23 CONSOL</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -1340,22 +1340,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001666</t>
+          <t>HASLS22260902826</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610242200</t>
+          <t>202611010800</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1366,22 +1366,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+          <t>GATEWAY CONTAINER LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1396,17 +1396,18 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Pickup : 2026-10-21, Return : 2026-10-22 CONSOL</t>
+          <t xml:space="preserve">Pickup : 2026-10-20, Return : 2026-10-22 CONSOL
+ (1ST CY : 22/10 W/O RENT) </t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1428,118 +1429,299 @@
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001595</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>KMBK</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>202610260700</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>SADESA (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>COW LEATHER</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STUFFING @PAT (SPORT LIGHT TOWER 2) DD 22/10/26 CLS TIME 23/10 @17.00HRS 
+ </t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001719</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610271500</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ECU WORLDWIDE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL CARGO (CONSOL)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>CONSOL</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-10-22, Return : 2026-10-22 CONSOL</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3">
-        <f>SUM(N2:N10)</f>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3">
+        <f>SUM(N2:N12)</f>
         <v/>
       </c>
-      <c r="O11" s="3">
-        <f>SUM(O2:O10)</f>
+      <c r="O13" s="3">
+        <f>SUM(O2:O12)</f>
         <v/>
       </c>
-      <c r="P11" s="3">
-        <f>SUM(P2:P10)</f>
+      <c r="P13" s="3">
+        <f>SUM(P2:P12)</f>
         <v/>
       </c>
-      <c r="Q11" s="3">
-        <f>SUM(Q2:Q10)</f>
+      <c r="Q13" s="3">
+        <f>SUM(Q2:Q12)</f>
         <v/>
       </c>
-      <c r="R11" s="3">
-        <f>SUM(R2:R10)</f>
+      <c r="R13" s="3">
+        <f>SUM(R2:R12)</f>
         <v/>
       </c>
-      <c r="S11" s="3">
-        <f>SUM(S2:S10)</f>
+      <c r="S13" s="3">
+        <f>SUM(S2:S12)</f>
         <v/>
       </c>
-      <c r="T11" s="3">
-        <f>SUM(T2:T10)</f>
+      <c r="T13" s="3">
+        <f>SUM(T2:T12)</f>
         <v/>
       </c>
-      <c r="U11" s="3">
-        <f>SUM(U2:U10)</f>
+      <c r="U13" s="3">
+        <f>SUM(U2:U12)</f>
         <v/>
       </c>
-      <c r="V11" s="3">
-        <f>SUM(V2:V10)</f>
+      <c r="V13" s="3">
+        <f>SUM(V2:V12)</f>
         <v/>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>32</v>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 1 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PAT TERMINAL 2 (PORT AUTHORITY OF THAILAND)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>37</v>
+      <c r="B19" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V10"/>
+  <autoFilter ref="A1:V12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>